--- a/support/specifications/hl7/HL7v2.to.FHIR.Conversion.Spec.xlsx
+++ b/support/specifications/hl7/HL7v2.to.FHIR.Conversion.Spec.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="19200" windowHeight="8000" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="438">
   <si>
     <t>FHIR Resources</t>
   </si>
@@ -507,7 +507,12 @@
   <si>
     <t>"meta" : {
     "lastUpdated" : "2024-02-23T00:00:00Z",
-    "profile" : ["http://shinny.org/us/ny/hrsn/StructureDefinition/SHINNYBundleProfile"]
+    "profile" : ["http://shinny.org/us/ny/hrsn/StructureDefinition/SHINNYBundleProfile"],
+    "security": [ {
+                  "code": "ETH",
+                  "system": "http://terminology.hl7.org/CodeSystem/v3-ActCode",
+                  "display": "Substance abuse information sensitivity"
+              } ]
   },</t>
   </si>
   <si>
@@ -517,6 +522,56 @@
     <t>"http://shinny.org/us/ny/hrsn/StructureDefinition/SHINNYBundleProfile"</t>
   </si>
   <si>
+    <t>meta -&gt; security</t>
+  </si>
+  <si>
+    <r>
+      <t>If the header variable `</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X-TechBD-Part2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>` has the value '</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>True</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>', then only the meta -&gt; security will be added.</t>
+    </r>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
@@ -533,6 +588,31 @@
   </si>
   <si>
     <t>Resources - Patient, Encounter, Organization, Consent, Sexual orientation, Observation, Grouper Observation</t>
+  </si>
+  <si>
+    <t>PID</t>
+  </si>
+  <si>
+    <t>PV1</t>
+  </si>
+  <si>
+    <t>ORC</t>
+  </si>
+  <si>
+    <t>OBX</t>
+  </si>
+  <si>
+    <t>The OBX segment in which OBX-3.1 (Observation Identifier)  had the value '105511-0' or OBX.3.2 has the value 'AHC-HRSN Patient Consent' can be taken as the Consent resource.
+If there is NO OBX segment in which (OBX-3.1 = '105511-0' or OBX.3.2 = 'AHC-HRSN Patient Consent' ) AND  OBX.5.2 is having Observation Value  then, the Consent resource will be generated with 'provision.type' as 'deny' and the 'Consent Source' will be 'TechBD Generated'.</t>
+  </si>
+  <si>
+    <t>OBX where OBX.3.1 = '76690-7' and OBX.5.1 &gt; 0</t>
+  </si>
+  <si>
+    <t>OBX where OBX.3.1 != '76690-7' and OBX.5.1 has some value</t>
+  </si>
+  <si>
+    <t>Observation (Observation Grouper)</t>
   </si>
   <si>
     <t>Procedure</t>
@@ -1605,62 +1685,6 @@
     <t>The HL7 file shared does not contain the NK1 segment.</t>
   </si>
   <si>
-    <t>communication -&gt; language -&gt; coding -&gt; system</t>
-  </si>
-  <si>
-    <t>PID.15.3, LAN.2.3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"communication" : [{
-"language" : {
-"coding" : [{
-"system" :</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> "urn:ietf:bcp:47"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,
-"code" : "en"
-}]
-},
-"preferred" : true
-}]</t>
-    </r>
-  </si>
-  <si>
-    <t>communication -&gt; language -&gt; coding -&gt; code</t>
-  </si>
-  <si>
-    <t>PID.15.1, LAN.2.1</t>
-  </si>
-  <si>
-    <t>communication -&gt; preferred</t>
-  </si>
-  <si>
-    <t>PID-15, LAN-2</t>
-  </si>
-  <si>
     <t>request -&gt; method</t>
   </si>
   <si>
@@ -1811,7 +1835,64 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> OBX segment in which OBX-3.1 = '105511-0' or OBX.3.2 = 'AHC-HRSN Patient Consent'  then, the Consent resource will be generated with 'provision.type' as '</t>
+      <t xml:space="preserve"> OBX segment in which (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">OBX-3.1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">= '105511-0' or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">OBX.3.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">= 'AHC-HRSN Patient Consent' ) AND  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">OBX.5.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>is having Observation Value  then, the Consent resource will be generated with 'provision.type' as '</t>
     </r>
     <r>
       <rPr>
@@ -2114,7 +2195,8 @@
     <t>provision -&gt; type</t>
   </si>
   <si>
-    <t>"permit" or "deny"</t>
+    <t>OBX.5.2 
+"permit" or "deny"</t>
   </si>
   <si>
     <r>
@@ -2166,7 +2248,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>OBX.5</t>
+      <t>OBX.5.2</t>
     </r>
     <r>
       <rPr>
@@ -2271,8 +2353,84 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>:
-If there is NO OBX segment in which OBX-3.1 = '105511-0' or OBX.3.2 = 'AHC-HRSN Patient Consent'  then, the Consent resource will be generated with 'provision.type' as '</t>
+      <t xml:space="preserve">:
+If there is NO OBX segment in which </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(OBX-3.1 =</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> '105511-0' or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">OBX.3.2 = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>'AHC-HRSN Patient Consent'</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> ) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>AND</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  OBX.5.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> is having Observation Value then, the Consent resource will be generated with 'provision.type' as '</t>
     </r>
     <r>
       <rPr>
@@ -5219,21 +5377,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -5241,13 +5384,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color indexed="10"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="10"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -5272,6 +5409,27 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="40">
@@ -5799,7 +5957,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5980,6 +6138,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -5990,6 +6151,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -6068,7 +6244,7 @@
     <cellStyle name="Warning" xfId="59"/>
   </cellStyles>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{AADC0999-BA12-42CC-B1B0-98753EE1D3E7}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{238349B5-1BB3-4751-9B4E-71FF109ADF5E}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -6337,23 +6513,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="11.8571428571429" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="11.8545454545455" defaultRowHeight="14.5" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="14.2857142857143" style="64" customWidth="1"/>
+    <col min="1" max="1" width="14.2818181818182" style="70" customWidth="1"/>
     <col min="2" max="2" width="47" customWidth="1"/>
-    <col min="3" max="3" width="123.571428571429" customWidth="1"/>
+    <col min="3" max="3" width="123.572727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="60"/>
-      <c r="B2" s="60" t="s">
+      <c r="A2" s="61"/>
+      <c r="B2" s="61" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="53" t="s">
@@ -6361,8 +6537,8 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="60"/>
-      <c r="B3" s="60" t="s">
+      <c r="A3" s="61"/>
+      <c r="B3" s="61" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="53" t="s">
@@ -6370,26 +6546,26 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="60"/>
-      <c r="B4" s="60" t="s">
+      <c r="A4" s="61"/>
+      <c r="B4" s="61" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="53" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="45" spans="1:3">
-      <c r="A5" s="60"/>
-      <c r="B5" s="60" t="s">
+    <row r="5" ht="43.5" spans="1:3">
+      <c r="A5" s="61"/>
+      <c r="B5" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="64" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="60"/>
-      <c r="B6" s="63" t="s">
+      <c r="A6" s="61"/>
+      <c r="B6" s="64" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="53" t="s">
@@ -6397,8 +6573,8 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="60"/>
-      <c r="B7" s="60" t="s">
+      <c r="A7" s="61"/>
+      <c r="B7" s="61" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="10" t="s">
@@ -6406,8 +6582,8 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="60"/>
-      <c r="B8" s="60"/>
+      <c r="A8" s="61"/>
+      <c r="B8" s="61"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1.39370078740157" bottom="1.39370078740157" header="1" footer="1"/>
@@ -6420,15 +6596,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" style="2" customWidth="1"/>
-    <col min="2" max="2" width="33.5714285714286" style="2" customWidth="1"/>
-    <col min="3" max="3" width="49.6666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="56.552380952381" style="2" customWidth="1"/>
-    <col min="5" max="5" width="53.2857142857143" style="2" customWidth="1"/>
-    <col min="6" max="6" width="47.5714285714286" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.14285714285714" style="2"/>
+    <col min="1" max="1" width="14.7181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="33.5727272727273" style="2" customWidth="1"/>
+    <col min="3" max="3" width="49.6636363636364" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.5545454545455" style="2" customWidth="1"/>
+    <col min="5" max="5" width="53.2818181818182" style="2" customWidth="1"/>
+    <col min="6" max="6" width="47.5727272727273" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9.14545454545454" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -6439,16 +6615,16 @@
         <v>14</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="17" customHeight="1" spans="1:6">
@@ -6467,7 +6643,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:4">
@@ -6479,7 +6655,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:6">
@@ -6488,18 +6664,18 @@
         <v>23</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="30" spans="2:6">
+    <row r="6" s="2" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -6507,175 +6683,175 @@
     </row>
     <row r="7" s="2" customFormat="1" spans="2:6">
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="150" spans="2:5">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="145" spans="2:5">
       <c r="B8" s="6" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="409" customHeight="1" spans="2:5">
       <c r="B9" s="6" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="5" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="150" spans="2:5">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="145" spans="2:5">
       <c r="B10" s="6" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="180" spans="2:5">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="159.5" spans="2:5">
       <c r="B11" s="6" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="2"/>
       <c r="E11" s="9" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="150" spans="2:5">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="145" spans="2:5">
       <c r="B12" s="6" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="2"/>
       <c r="E12" s="9" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="75" spans="2:4">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="58" spans="2:4">
       <c r="B13" s="6" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="30" spans="2:3">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" ht="29" spans="2:3">
       <c r="B14" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" ht="45" spans="2:4">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" ht="43.5" spans="2:4">
       <c r="B15" s="6" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="30" spans="2:5">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" ht="29" spans="2:5">
       <c r="B16" s="6" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" ht="45" spans="2:4">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="43.5" spans="2:4">
       <c r="B17" s="6" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" spans="2:6">
       <c r="B18" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="13" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" ht="165" spans="2:5">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="159.5" spans="2:5">
       <c r="B19" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="2:4">
       <c r="B20" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" ht="46" customHeight="1" spans="2:4">
       <c r="B21" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D21" s="14"/>
     </row>
@@ -6692,149 +6868,200 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="3"/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" style="60" customWidth="1"/>
-    <col min="2" max="2" width="28.2857142857143" style="60" customWidth="1"/>
-    <col min="3" max="3" width="66.4285714285714" style="60" customWidth="1"/>
-    <col min="4" max="4" width="46.2857142857143" style="60" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" style="61" customWidth="1"/>
+    <col min="2" max="2" width="28.2818181818182" style="61" customWidth="1"/>
+    <col min="3" max="3" width="62.7272727272727" style="61" customWidth="1"/>
+    <col min="4" max="4" width="54.5454545454545" style="61" customWidth="1"/>
+    <col min="5" max="5" width="11.1818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="62" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="62"/>
-      <c r="B3" s="60" t="s">
+      <c r="A3" s="63"/>
+      <c r="B3" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="60" t="s">
+      <c r="C3" s="61" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="62"/>
-      <c r="B4" s="60" t="s">
+      <c r="A4" s="63"/>
+      <c r="B4" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="60" t="s">
+      <c r="C4" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="60" t="s">
+      <c r="D4" s="61" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" ht="90" spans="2:4">
-      <c r="B5" s="60" t="s">
+    <row r="5" ht="61" customHeight="1" spans="2:4">
+      <c r="B5" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="60" t="s">
+      <c r="C5" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="63" t="s">
+      <c r="D5" s="64" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
-      <c r="B6" s="60" t="s">
+    <row r="6" ht="49" customHeight="1" spans="2:4">
+      <c r="B6" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="63"/>
-    </row>
-    <row r="7" spans="2:4">
-      <c r="B7" s="60" t="s">
+      <c r="D6" s="64"/>
+    </row>
+    <row r="7" ht="71" customHeight="1" spans="2:4">
+      <c r="B7" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="60" t="s">
+      <c r="C7" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="63"/>
-    </row>
-    <row r="8" spans="2:3">
-      <c r="B8" s="60" t="s">
+      <c r="D7" s="64"/>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="60" t="s">
+      <c r="C8" s="61" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="9" ht="30" spans="2:3">
-      <c r="B9" s="60" t="s">
+      <c r="D8" s="64"/>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="63" t="s">
+      <c r="C9" s="61" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14"/>
-      <c r="B14"/>
-      <c r="C14"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15"/>
-      <c r="B15"/>
-      <c r="C15"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16"/>
-      <c r="B16"/>
-      <c r="C16"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17"/>
-      <c r="B17"/>
-      <c r="C17"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18"/>
-      <c r="B18"/>
-      <c r="C18"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19"/>
-      <c r="B19"/>
-      <c r="C19"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20"/>
-      <c r="B20"/>
-      <c r="C20"/>
+    <row r="10" ht="29" spans="2:3">
+      <c r="B10" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="64" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" s="60" customFormat="1" spans="1:1">
+      <c r="A13" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" s="60" customFormat="1" spans="2:3">
+      <c r="B14" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="60" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" s="60" customFormat="1" spans="2:3">
+      <c r="B15" s="60" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="67" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" s="60" customFormat="1" spans="2:3">
+      <c r="B16" s="60" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="60" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" s="60" customFormat="1" ht="129" customHeight="1" spans="2:7">
+      <c r="B17" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="60" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+    </row>
+    <row r="18" s="60" customFormat="1" spans="2:5">
+      <c r="B18" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="67"/>
+    </row>
+    <row r="19" s="60" customFormat="1" spans="2:5">
+      <c r="B19" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="67"/>
+    </row>
+    <row r="20" s="60" customFormat="1" ht="29" spans="2:5">
+      <c r="B20" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="60"/>
+      <c r="E20" s="69"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21"/>
       <c r="B21"/>
       <c r="C21"/>
     </row>
-    <row r="22" hidden="1" spans="2:3">
-      <c r="B22" s="60" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="63" t="s">
-        <v>35</v>
+    <row r="22" spans="1:3">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+    </row>
+    <row r="23" hidden="1" spans="2:3">
+      <c r="B23" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="64" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D5:D7"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" display="&quot;http://shinny.org/us/ny/hrsn/StructureDefinition/SHINNYBundleProfile&quot;"/>
   </hyperlinks>
@@ -6846,15 +7073,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E68"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <dimension ref="A1:E65"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.1142857142857" customWidth="1"/>
-    <col min="2" max="2" width="39.1428571428571" style="11" customWidth="1"/>
-    <col min="3" max="3" width="61.5714285714286" style="11" customWidth="1"/>
-    <col min="4" max="4" width="66.8571428571429" style="11" customWidth="1"/>
-    <col min="5" max="5" width="64.5714285714286" style="11" customWidth="1"/>
-    <col min="6" max="256" width="11.8571428571429" customWidth="1"/>
+    <col min="1" max="1" width="13.1181818181818" customWidth="1"/>
+    <col min="2" max="2" width="39.1454545454545" style="11" customWidth="1"/>
+    <col min="3" max="3" width="61.5727272727273" style="11" customWidth="1"/>
+    <col min="4" max="4" width="66.8545454545455" style="11" customWidth="1"/>
+    <col min="5" max="5" width="64.5727272727273" style="11" customWidth="1"/>
+    <col min="6" max="256" width="11.8545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="17" customFormat="1" spans="1:5">
@@ -6871,7 +7098,7 @@
         <v>16</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -6886,7 +7113,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E3" s="23"/>
     </row>
@@ -6898,7 +7125,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E4" s="23"/>
     </row>
@@ -6908,660 +7135,630 @@
         <v>23</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E5" s="23"/>
     </row>
-    <row r="6" ht="30" spans="2:5">
+    <row r="6" spans="2:5">
       <c r="B6" s="19" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E6" s="23"/>
     </row>
-    <row r="7" ht="60" spans="2:5">
+    <row r="7" ht="58" spans="2:5">
       <c r="B7" s="11" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E7" s="47" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" ht="60" spans="2:5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" ht="58" spans="2:5">
       <c r="B8" s="11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E8" s="23"/>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="11" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E9" s="23"/>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="11" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E10" s="23"/>
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="19" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E11" s="23"/>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>46</v>
-      </c>
       <c r="D12" s="11" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E12" s="23"/>
     </row>
-    <row r="13" ht="60" spans="2:5">
+    <row r="13" ht="58" spans="2:5">
       <c r="B13" s="11" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E13" s="23"/>
     </row>
-    <row r="14" ht="30" spans="2:5">
+    <row r="14" ht="29" spans="2:5">
       <c r="B14" s="11" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E14" s="23"/>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="19" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="E15" s="23"/>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="19" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E16" s="23"/>
     </row>
-    <row r="17" ht="120" spans="2:5">
+    <row r="17" ht="116" spans="2:5">
       <c r="B17" s="11" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E17" s="23"/>
     </row>
-    <row r="18" ht="30" spans="2:5">
+    <row r="18" ht="29" spans="2:5">
       <c r="B18" s="11" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E18" s="23"/>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E19" s="23"/>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="11" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E20" s="23"/>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" s="11" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E21" s="23"/>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="11" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E22" s="23"/>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="11" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E23" s="23"/>
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="11" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E24" s="23"/>
     </row>
-    <row r="25" ht="75" spans="2:5">
+    <row r="25" ht="72.5" spans="2:5">
       <c r="B25" s="11" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E25" s="23"/>
     </row>
-    <row r="26" ht="45" spans="2:5">
+    <row r="26" ht="29" spans="2:5">
       <c r="B26" s="27" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D26" s="56" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" ht="30" spans="2:5">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" ht="29" spans="2:5">
       <c r="B27" s="27" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D27" s="56"/>
       <c r="E27" s="57"/>
     </row>
-    <row r="28" ht="30" spans="2:5">
+    <row r="28" spans="2:5">
       <c r="B28" s="27" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D28" s="56"/>
       <c r="E28" s="57"/>
     </row>
-    <row r="29" ht="30" spans="2:5">
+    <row r="29" ht="29" spans="2:5">
       <c r="B29" s="27" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D29" s="56"/>
       <c r="E29" s="57"/>
     </row>
     <row r="30" spans="2:5">
       <c r="B30" s="27" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D30" s="56"/>
       <c r="E30" s="8"/>
     </row>
-    <row r="31" ht="30" spans="2:5">
+    <row r="31" ht="29" spans="2:5">
       <c r="B31" s="27" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D31" s="56" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" ht="30" spans="2:5">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" ht="29" spans="2:5">
       <c r="B32" s="27" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D32" s="56"/>
       <c r="E32" s="57"/>
     </row>
-    <row r="33" ht="30" spans="2:5">
+    <row r="33" spans="2:5">
       <c r="B33" s="27" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="D33" s="56"/>
       <c r="E33" s="57"/>
     </row>
-    <row r="34" ht="30" spans="2:5">
+    <row r="34" ht="29" spans="2:5">
       <c r="B34" s="27" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D34" s="56"/>
       <c r="E34" s="57"/>
     </row>
     <row r="35" spans="2:5">
       <c r="B35" s="27" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D35" s="56"/>
       <c r="E35" s="57"/>
     </row>
     <row r="36" spans="2:5">
       <c r="B36" s="27" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D36" s="56" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E36" s="57"/>
     </row>
-    <row r="37" ht="45" spans="2:5">
+    <row r="37" ht="43.5" spans="2:5">
       <c r="B37" s="27" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="D37" s="56"/>
-      <c r="E37" s="65" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="38" ht="135" spans="2:5">
+      <c r="E37" s="71" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" ht="130.5" spans="2:5">
       <c r="B38" s="58" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C38" s="58"/>
       <c r="D38" s="58" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="39" ht="135" spans="2:5">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" ht="130.5" spans="2:5">
       <c r="B39" s="58" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C39" s="58"/>
       <c r="D39" s="58" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="2:5">
       <c r="B40" s="19" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E40" s="23"/>
     </row>
     <row r="41" spans="2:5">
       <c r="B41" s="19" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C41" s="24" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E41" s="23"/>
     </row>
     <row r="42" spans="2:5">
       <c r="B42" s="19" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E42" s="23"/>
     </row>
     <row r="43" spans="2:5">
       <c r="B43" s="11" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E43" s="23"/>
     </row>
-    <row r="44" ht="195" spans="2:5">
+    <row r="44" ht="188.5" spans="2:5">
       <c r="B44" s="19" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E44" s="23"/>
     </row>
-    <row r="45" ht="195" spans="2:5">
+    <row r="45" ht="188.5" spans="2:5">
       <c r="B45" s="19" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D45" s="53" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E45" s="47" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="46" ht="195" spans="2:5">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" ht="188.5" spans="2:5">
       <c r="B46" s="19" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E46" s="23"/>
     </row>
     <row r="47" spans="2:5">
       <c r="B47" s="11" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E47" s="23"/>
     </row>
     <row r="48" spans="2:5">
       <c r="B48" s="11" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E48" s="23"/>
     </row>
     <row r="49" spans="2:5">
       <c r="B49" s="11" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E49" s="23"/>
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="11" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E50" s="23"/>
     </row>
-    <row r="51" ht="150" spans="2:5">
+    <row r="51" ht="145" spans="2:5">
       <c r="B51" s="11" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="B52" s="11" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="E52" s="23"/>
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="11" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E53" s="23"/>
     </row>
     <row r="54" spans="2:5">
       <c r="B54" s="11" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E54" s="23"/>
     </row>
     <row r="55" spans="2:5">
       <c r="B55" s="11" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E55" s="23"/>
     </row>
     <row r="56" spans="2:5">
       <c r="B56" s="11" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E56" s="23"/>
     </row>
     <row r="57" spans="2:5">
       <c r="B57" s="11" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C57" s="24" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E57" s="23"/>
     </row>
-    <row r="58" ht="180" spans="2:5">
+    <row r="58" ht="174" spans="2:5">
       <c r="B58" s="11" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E58" s="23"/>
     </row>
-    <row r="59" ht="90" spans="2:5">
+    <row r="59" ht="72.5" spans="2:5">
       <c r="B59" s="27" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="C59" s="27"/>
       <c r="D59" s="27" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="E59" s="23"/>
     </row>
-    <row r="60" ht="255" spans="2:5">
+    <row r="60" ht="246.5" spans="2:5">
       <c r="B60" s="11" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="61" ht="135" spans="2:5">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5">
       <c r="B61" s="11" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="D61" s="11" t="s">
-        <v>165</v>
+        <v>174</v>
+      </c>
+      <c r="D61" s="59" t="s">
+        <v>175</v>
       </c>
       <c r="E61" s="23"/>
     </row>
-    <row r="62" ht="30" spans="2:5">
+    <row r="62" ht="42.95" customHeight="1" spans="2:5">
       <c r="B62" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>167</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="C62" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="D62" s="59"/>
       <c r="E62" s="23"/>
     </row>
-    <row r="63" spans="2:5">
-      <c r="B63" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="E63" s="23"/>
-    </row>
-    <row r="64" spans="2:5">
-      <c r="B64" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="D64" s="59" t="s">
-        <v>172</v>
-      </c>
-      <c r="E64" s="23"/>
-    </row>
-    <row r="65" ht="42.95" customHeight="1" spans="2:5">
-      <c r="B65" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="C65" s="55" t="s">
-        <v>174</v>
-      </c>
-      <c r="D65" s="59"/>
-      <c r="E65" s="23"/>
-    </row>
-    <row r="68" spans="3:3">
-      <c r="C68" s="55"/>
+    <row r="65" spans="3:3">
+      <c r="C65" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D26:D30"/>
     <mergeCell ref="D31:D35"/>
     <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="D61:D62"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C9" r:id="rId1" display="&quot;http://shinny.org/us/ny/hrsn/StructureDefinition/middle-name&quot;" tooltip="http://shinny.org/us/ny/hrsn/StructureDefinition/middle-name"/>
-    <hyperlink ref="C65" r:id="rId2" display="&quot;http://shinny.org/us/ny/hrsn/Patient/&lt;id&gt;&quot;" tooltip="http://shinny.org/us/ny/hrsn/Patient/PID.3.1"/>
+    <hyperlink ref="C62" r:id="rId2" display="&quot;http://shinny.org/us/ny/hrsn/Patient/&lt;id&gt;&quot;" tooltip="http://shinny.org/us/ny/hrsn/Patient/PID.3.1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1.39370078740157" bottom="1.39370078740157" header="1" footer="1"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
@@ -7573,14 +7770,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.14285714285714" customWidth="1"/>
-    <col min="2" max="2" width="40.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="61.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="57.4285714285714" customWidth="1"/>
-    <col min="5" max="5" width="54.8571428571429" customWidth="1"/>
-    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
+    <col min="1" max="1" width="9.14545454545454" customWidth="1"/>
+    <col min="2" max="2" width="40.8545454545455" customWidth="1"/>
+    <col min="3" max="3" width="61.5727272727273" customWidth="1"/>
+    <col min="4" max="4" width="57.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="54.8545454545455" customWidth="1"/>
+    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7597,15 +7794,15 @@
         <v>16</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" ht="31" customHeight="1" spans="1:5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1" spans="1:5">
       <c r="A2" s="17" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="49" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C2" s="49"/>
       <c r="D2" s="49"/>
@@ -7616,7 +7813,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E3" s="23"/>
     </row>
@@ -7634,7 +7831,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E5" s="23"/>
     </row>
@@ -7643,206 +7840,206 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E6" s="23"/>
     </row>
-    <row r="7" ht="45" spans="2:5">
+    <row r="7" ht="29" spans="2:5">
       <c r="B7" s="18" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C7" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D7" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E7" s="50" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="8" ht="135" spans="2:5">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="8" ht="130.5" spans="2:5">
       <c r="B8" s="51" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="51" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D9" s="26"/>
       <c r="E9" s="23"/>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="51" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D10" s="26"/>
       <c r="E10" s="23" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="11" ht="225" spans="2:5">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="11" ht="217.5" spans="2:5">
       <c r="B11" s="18" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D11" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="E11" s="23" t="s">
         <v>194</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="18" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="18" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="14" ht="30" spans="2:5">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" ht="29" spans="2:5">
       <c r="B14" s="18" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C14" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="15" ht="120" spans="2:5">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15" ht="116" spans="2:5">
       <c r="B15" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>204</v>
+        <v>206</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>207</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E15" s="50" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="16" ht="45" spans="2:5">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" ht="43.5" spans="2:5">
       <c r="B16" s="18" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E16" s="23"/>
     </row>
-    <row r="17" ht="60" spans="2:5">
+    <row r="17" ht="58" spans="2:5">
       <c r="B17" s="51" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C17" s="54" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E17" s="23"/>
     </row>
-    <row r="18" ht="60" spans="2:5">
+    <row r="18" ht="58" spans="2:5">
       <c r="B18" s="54" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C18" s="54" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="6" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="6" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D20" s="27"/>
       <c r="E20" s="8" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" ht="77" customHeight="1" spans="2:5">
       <c r="B21" s="11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E21" s="23"/>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="23"/>
@@ -7862,14 +8059,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="43.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="57.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
+    <col min="4" max="4" width="43.5727272727273" customWidth="1"/>
+    <col min="5" max="5" width="57.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7886,7 +8083,7 @@
         <v>16</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7900,7 +8097,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E3" s="23"/>
     </row>
@@ -7913,7 +8110,7 @@
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E4" s="23"/>
     </row>
@@ -7923,275 +8120,275 @@
         <v>23</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="23"/>
     </row>
-    <row r="6" ht="30" spans="2:5">
+    <row r="6" ht="29" spans="2:5">
       <c r="B6" s="19" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="23"/>
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="18" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" ht="75" spans="2:5">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" ht="72.5" spans="2:5">
       <c r="B8" s="18" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="E8" s="66" t="s">
-        <v>230</v>
+        <v>232</v>
+      </c>
+      <c r="E8" s="72" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="18" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="23"/>
     </row>
-    <row r="10" ht="75" spans="2:5">
+    <row r="10" ht="72.5" spans="2:5">
       <c r="B10" s="18" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D10" s="11"/>
-      <c r="E10" s="66" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="11" ht="120" spans="2:5">
+      <c r="E10" s="72" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="11" ht="116" spans="2:5">
       <c r="B11" s="18" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E11" s="47" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="12" ht="60" spans="2:5">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="12" ht="43.5" spans="2:5">
       <c r="B12" s="18" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E12" s="48" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="18" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E13" s="23"/>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C14" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E14" s="23"/>
     </row>
-    <row r="15" ht="75" spans="2:5">
+    <row r="15" ht="72.5" spans="2:5">
       <c r="B15" s="18" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C15" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E15" s="23"/>
     </row>
-    <row r="16" ht="30" spans="2:5">
+    <row r="16" ht="29" spans="2:5">
       <c r="B16" s="18" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E16" s="23"/>
     </row>
-    <row r="17" ht="60" spans="2:5">
+    <row r="17" ht="58" spans="2:5">
       <c r="B17" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E17" s="23"/>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E18" s="23"/>
     </row>
-    <row r="19" ht="30" spans="2:5">
+    <row r="19" ht="29" spans="2:5">
       <c r="B19" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="23" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="23" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="23" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="23" ht="30" spans="2:5">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="23" ht="29" spans="2:5">
       <c r="B23" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D23" s="11"/>
       <c r="E23" s="23" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="24" ht="75" spans="2:5">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="24" ht="72.5" spans="2:5">
       <c r="B24" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E24" s="23"/>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D25" s="11"/>
       <c r="E25" s="23"/>
     </row>
-    <row r="26" ht="60" spans="2:5">
+    <row r="26" ht="58" spans="2:5">
       <c r="B26" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D27" s="11"/>
       <c r="E27" s="23" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="2:5">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="2:5">
       <c r="B28" s="11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E28" s="23"/>
     </row>
-    <row r="29" ht="30" spans="2:5">
+    <row r="29" ht="29" spans="2:5">
       <c r="B29" s="11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="23"/>
@@ -8211,15 +8408,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="19.4285714285714" style="29" customWidth="1"/>
+    <col min="1" max="1" width="19.4272727272727" style="29" customWidth="1"/>
     <col min="2" max="2" width="37" style="29" customWidth="1"/>
-    <col min="3" max="3" width="50.5714285714286" style="29" customWidth="1"/>
-    <col min="4" max="4" width="39.1428571428571" style="29" customWidth="1"/>
-    <col min="5" max="5" width="54.1428571428571" style="29" customWidth="1"/>
-    <col min="6" max="6" width="51.1428571428571" style="29" customWidth="1"/>
-    <col min="7" max="16384" width="9.14285714285714" style="29"/>
+    <col min="3" max="3" width="50.5727272727273" style="29" customWidth="1"/>
+    <col min="4" max="4" width="39.1454545454545" style="29" customWidth="1"/>
+    <col min="5" max="5" width="54.1454545454545" style="29" customWidth="1"/>
+    <col min="6" max="6" width="51.1454545454545" style="29" customWidth="1"/>
+    <col min="7" max="16384" width="9.14545454545454" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8236,10 +8433,10 @@
         <v>16</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F1" s="31" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8253,7 +8450,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E3" s="32"/>
     </row>
@@ -8272,298 +8469,298 @@
         <v>23</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D5" s="33"/>
       <c r="E5" s="32"/>
     </row>
-    <row r="6" ht="30" spans="2:5">
+    <row r="6" ht="29" spans="2:5">
       <c r="B6" s="33" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="32"/>
     </row>
-    <row r="7" ht="30" spans="2:6">
+    <row r="7" ht="29" spans="2:6">
       <c r="B7" s="34" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C7" s="35"/>
       <c r="D7" s="35" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F7" s="36"/>
     </row>
-    <row r="8" ht="195" spans="2:5">
+    <row r="8" ht="188.5" spans="2:5">
       <c r="B8" s="29" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="29" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="32"/>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="33" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="32"/>
     </row>
-    <row r="11" ht="30" spans="2:5">
+    <row r="11" spans="2:5">
       <c r="B11" s="33" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="D11" s="33"/>
       <c r="E11" s="32"/>
     </row>
-    <row r="12" ht="30" spans="2:5">
+    <row r="12" spans="2:5">
       <c r="B12" s="33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="32"/>
     </row>
-    <row r="13" ht="225" spans="2:5">
+    <row r="13" ht="217.5" spans="2:5">
       <c r="B13" s="29" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E13" s="38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="29" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D14" s="33"/>
       <c r="E14" s="32"/>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="33" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="32"/>
     </row>
-    <row r="16" ht="30" spans="2:5">
+    <row r="16" spans="2:5">
       <c r="B16" s="33" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="32"/>
     </row>
-    <row r="17" ht="30" spans="2:5">
+    <row r="17" spans="2:5">
       <c r="B17" s="33" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="32"/>
     </row>
-    <row r="18" ht="30" spans="2:5">
+    <row r="18" ht="29" spans="2:5">
       <c r="B18" s="39" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="19" ht="135" spans="2:5">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="19" ht="130.5" spans="2:5">
       <c r="B19" s="35" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="42" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="20" ht="60" spans="2:5">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="20" ht="58" spans="2:5">
       <c r="B20" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>318</v>
+      </c>
+      <c r="D20" s="33"/>
+      <c r="E20" s="73" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="21" ht="174" spans="2:5">
+      <c r="B21" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>320</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>321</v>
+      </c>
+      <c r="E21" s="32"/>
+    </row>
+    <row r="22" ht="72.5" spans="2:6">
+      <c r="B22" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>322</v>
+      </c>
+      <c r="D22" s="33"/>
+      <c r="E22" s="73" t="s">
+        <v>323</v>
+      </c>
+      <c r="F22" s="44"/>
+    </row>
+    <row r="23" ht="29" spans="2:5">
+      <c r="B23" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="45" t="s">
+        <v>324</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>325</v>
+      </c>
+      <c r="E23" s="32"/>
+    </row>
+    <row r="24" ht="72.5" spans="2:6">
+      <c r="B24" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="C24" s="43" t="s">
+        <v>327</v>
+      </c>
+      <c r="D24" s="33"/>
+      <c r="E24" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="F24" s="44"/>
+    </row>
+    <row r="25" ht="43.5" spans="2:5">
+      <c r="B25" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="43" t="s">
-        <v>315</v>
-      </c>
-      <c r="D20" s="33"/>
-      <c r="E20" s="67" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="21" ht="180" spans="2:5">
-      <c r="B21" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" s="43" t="s">
-        <v>317</v>
-      </c>
-      <c r="D21" s="33" t="s">
-        <v>318</v>
-      </c>
-      <c r="E21" s="32"/>
-    </row>
-    <row r="22" ht="75" spans="2:6">
-      <c r="B22" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="43" t="s">
-        <v>319</v>
-      </c>
-      <c r="D22" s="33"/>
-      <c r="E22" s="67" t="s">
-        <v>320</v>
-      </c>
-      <c r="F22" s="44"/>
-    </row>
-    <row r="23" ht="30" spans="2:5">
-      <c r="B23" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="45" t="s">
-        <v>321</v>
-      </c>
-      <c r="D23" s="33" t="s">
-        <v>322</v>
-      </c>
-      <c r="E23" s="32"/>
-    </row>
-    <row r="24" ht="75" spans="2:6">
-      <c r="B24" s="33" t="s">
-        <v>323</v>
-      </c>
-      <c r="C24" s="43" t="s">
-        <v>324</v>
-      </c>
-      <c r="D24" s="33"/>
-      <c r="E24" s="67" t="s">
-        <v>325</v>
-      </c>
-      <c r="F24" s="44"/>
-    </row>
-    <row r="25" ht="45" spans="2:5">
-      <c r="B25" s="33" t="s">
-        <v>73</v>
-      </c>
       <c r="C25" s="45" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D25" s="33"/>
       <c r="E25" s="32"/>
     </row>
     <row r="26" spans="2:5">
       <c r="B26" s="33" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C26" s="43" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D26" s="33"/>
       <c r="E26" s="32"/>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="33" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D27" s="33"/>
       <c r="E27" s="32"/>
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="33" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C28" s="43" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D28" s="33"/>
       <c r="E28" s="32"/>
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="33" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D29" s="33"/>
       <c r="E29" s="32"/>
     </row>
-    <row r="30" customHeight="1" spans="2:5">
+    <row r="30" ht="15" customHeight="1" spans="2:5">
       <c r="B30" s="33" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C30" s="43" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E30" s="32"/>
     </row>
-    <row r="31" ht="30" spans="2:5">
+    <row r="31" ht="29" spans="2:5">
       <c r="B31" s="33" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D31" s="33"/>
       <c r="E31" s="32"/>
@@ -8585,14 +8782,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.2190476190476" customWidth="1"/>
-    <col min="2" max="2" width="26.2857142857143" customWidth="1"/>
-    <col min="3" max="3" width="43.7142857142857" customWidth="1"/>
-    <col min="4" max="4" width="47.2857142857143" customWidth="1"/>
-    <col min="5" max="5" width="80.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" customWidth="1"/>
+    <col min="2" max="2" width="26.2818181818182" customWidth="1"/>
+    <col min="3" max="3" width="43.7181818181818" customWidth="1"/>
+    <col min="4" max="4" width="47.2818181818182" customWidth="1"/>
+    <col min="5" max="5" width="80.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -8609,7 +8806,7 @@
         <v>16</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8623,7 +8820,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E3" s="11"/>
     </row>
@@ -8635,7 +8832,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E4" s="11"/>
     </row>
@@ -8644,267 +8841,267 @@
         <v>23</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" ht="30" spans="2:5">
+    <row r="6" ht="29" spans="2:5">
       <c r="B6" s="19" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E6" s="11"/>
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="19" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="8" ht="150" spans="2:5">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="8" ht="145" spans="2:5">
       <c r="B8" s="19" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="9" ht="120" spans="2:5">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="9" ht="116" spans="2:5">
       <c r="B9" s="25" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="27" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="10" ht="45" spans="1:5">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="10" ht="43.5" spans="1:5">
       <c r="A10" s="26"/>
       <c r="B10" s="6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D10" s="27"/>
       <c r="E10" s="8" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="11" ht="210" spans="1:5">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="11" ht="203" spans="1:5">
       <c r="A11" s="26"/>
       <c r="B11" s="6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="27"/>
       <c r="E11" s="9" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="12" ht="210" spans="1:5">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="12" ht="203" spans="1:5">
       <c r="A12" s="26"/>
       <c r="B12" s="6" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="27"/>
       <c r="E12" s="9" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="26"/>
       <c r="B13" s="6" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="27"/>
       <c r="E13" s="8" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="14" ht="150" spans="2:5">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="14" ht="130.5" spans="2:5">
       <c r="B14" s="11" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E14" s="11"/>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="19" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E15" s="11"/>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="19" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E16" s="11"/>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="11" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E17" s="11"/>
     </row>
-    <row r="18" ht="105" spans="2:5">
+    <row r="18" ht="101.5" spans="2:5">
       <c r="B18" s="11" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="19" ht="30" spans="2:5">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="19" ht="29" spans="2:5">
       <c r="B19" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>358</v>
-      </c>
       <c r="E19" s="11" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="20" ht="30" spans="2:5">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="20" ht="29" spans="2:5">
       <c r="B20" s="11" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="21" ht="75" spans="2:5">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="21" ht="72.5" spans="2:5">
       <c r="B21" s="19" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" ht="30" spans="2:5">
+    <row r="22" ht="29" spans="2:5">
       <c r="B22" s="19" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" ht="45" spans="2:5">
+    <row r="23" ht="43.5" spans="2:5">
       <c r="B23" s="25" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E23" s="11"/>
     </row>
-    <row r="24" ht="30" spans="2:5">
+    <row r="24" spans="2:5">
       <c r="B24" s="19" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="25" ht="60" spans="2:5">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="25" ht="58" spans="2:5">
       <c r="B25" s="11" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E25" s="11"/>
     </row>
-    <row r="26" ht="30" spans="2:5">
+    <row r="26" ht="29" spans="2:5">
       <c r="B26" s="11" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E26" s="11"/>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E27" s="11"/>
     </row>
     <row r="28" ht="78" customHeight="1" spans="2:5">
       <c r="B28" s="11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
@@ -8930,14 +9127,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="22.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="22.2818181818182" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="70.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="47.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="49.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
+    <col min="3" max="3" width="70.2818181818182" customWidth="1"/>
+    <col min="4" max="4" width="47.1454545454545" customWidth="1"/>
+    <col min="5" max="5" width="49.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -8954,12 +9151,12 @@
         <v>16</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" ht="30" spans="1:5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" ht="29" spans="1:5">
       <c r="A2" s="22" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E2" s="23"/>
     </row>
@@ -8969,7 +9166,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E3" s="23"/>
     </row>
@@ -8982,7 +9179,7 @@
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E4" s="23"/>
     </row>
@@ -8992,162 +9189,162 @@
         <v>23</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="23"/>
     </row>
-    <row r="6" ht="30" spans="2:5">
+    <row r="6" ht="29" spans="2:5">
       <c r="B6" s="19" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="23"/>
     </row>
-    <row r="7" ht="150" spans="2:5">
+    <row r="7" ht="145" spans="2:5">
       <c r="B7" s="18" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C7" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D7" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="B8" s="18" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C8" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="23"/>
     </row>
     <row r="9" ht="42.95" customHeight="1" spans="2:5">
       <c r="B9" s="18" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C9" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E9" s="23"/>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="18" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="23"/>
     </row>
     <row r="11" ht="60.95" customHeight="1" spans="2:5">
       <c r="B11" s="18" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="23"/>
     </row>
-    <row r="12" ht="30" spans="2:5">
+    <row r="12" ht="29" spans="2:5">
       <c r="B12" s="11" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E12" s="23"/>
     </row>
-    <row r="13" ht="30" spans="2:5">
+    <row r="13" ht="29" spans="2:5">
       <c r="B13" s="11" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="23"/>
     </row>
     <row r="14" ht="78" customHeight="1" spans="2:5">
       <c r="B14" s="11" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="23"/>
     </row>
-    <row r="15" ht="45" spans="2:5">
+    <row r="15" ht="43.5" spans="2:5">
       <c r="B15" s="18" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E15" s="23"/>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="18" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E16" s="23"/>
     </row>
-    <row r="17" ht="30" spans="2:5">
+    <row r="17" ht="29" spans="2:5">
       <c r="B17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C17" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D17" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="2:5">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="2:5">
       <c r="B18" s="11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E18" s="23"/>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="23"/>
@@ -9167,14 +9364,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.14285714285714" customWidth="1"/>
-    <col min="2" max="2" width="23.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="34.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="25.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="33.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
+    <col min="1" max="1" width="9.14545454545454" customWidth="1"/>
+    <col min="2" max="2" width="23.1454545454545" customWidth="1"/>
+    <col min="3" max="3" width="34.2818181818182" customWidth="1"/>
+    <col min="4" max="4" width="25.1454545454545" customWidth="1"/>
+    <col min="5" max="5" width="33.4272727272727" customWidth="1"/>
+    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9191,12 +9388,12 @@
         <v>16</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="17" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="2:3">
@@ -9204,7 +9401,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -9216,7 +9413,7 @@
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -9225,135 +9422,135 @@
         <v>23</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" ht="45" spans="2:5">
+    <row r="6" ht="29" spans="2:5">
       <c r="B6" s="19" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="18" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D7" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E7" s="20"/>
     </row>
-    <row r="8" ht="165" spans="2:5">
+    <row r="8" ht="159.5" spans="2:5">
       <c r="B8" s="18" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E8" s="21"/>
     </row>
     <row r="9" spans="2:3">
       <c r="B9" s="18" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="B10" s="18" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="B11" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="12" ht="90" spans="2:4">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="12" ht="87" spans="2:4">
       <c r="B12" s="18" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="13" ht="45" spans="2:3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" ht="29" spans="2:3">
       <c r="B13" s="18" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="14" ht="75" spans="2:4">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="14" ht="72.5" spans="2:4">
       <c r="B14" s="18" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="15" ht="90" spans="2:4">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="15" ht="87" spans="2:4">
       <c r="B15" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="B16" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="2:4">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="2:4">
       <c r="B17" s="11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="18" ht="30" spans="2:4">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="18" ht="29" spans="2:4">
       <c r="B18" s="11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D18" s="11"/>
     </row>

--- a/support/specifications/hl7/HL7v2.to.FHIR.Conversion.Spec.xlsx
+++ b/support/specifications/hl7/HL7v2.to.FHIR.Conversion.Spec.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8000" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12180" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="438">
   <si>
     <t>FHIR Resources</t>
   </si>
@@ -479,6 +479,9 @@
   </si>
   <si>
     <t>FHIR Example</t>
+  </si>
+  <si>
+    <t>Clarifications/Remarks</t>
   </si>
   <si>
     <t>Bundle</t>
@@ -526,6 +529,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>If the header variable `</t>
     </r>
     <r>
@@ -619,9 +629,6 @@
   </si>
   <si>
     <t>OBR and PID</t>
-  </si>
-  <si>
-    <t>Clarifications/Remarks</t>
   </si>
   <si>
     <t>"Patient"</t>
@@ -794,6 +801,7 @@
   </si>
   <si>
     <t>"address" : [{
+"use": "home",
 "text" : "115 Broadway Apt2 New York, NY 10032",
 "line" : ["115 Broadway Apt2"],
 "city" : "New York",
@@ -806,7 +814,7 @@
     <t>address -&gt; line</t>
   </si>
   <si>
-    <t>PID.11.1 + PID.11.2 (note: XAD.1 and XAD.2 have different meanings for a company address than for a person address)</t>
+    <t>PID.11.1 + PID.11.2</t>
   </si>
   <si>
     <t>address -&gt; city</t>
@@ -833,22 +841,46 @@
     <t>PID.11.5</t>
   </si>
   <si>
+    <t>address -&gt; use</t>
+  </si>
+  <si>
+    <t>PID.11.7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PID.11.7 -&gt; use Mapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+H, HP, HV -&gt; home
+WP -&gt; work
+BA -&gt; billing
+TMP -&gt; temp
+OLD, BAD -&gt; old
+All Others -&gt; home</t>
+    </r>
+  </si>
+  <si>
     <t>telecom -&gt; system</t>
   </si>
   <si>
     <t>PID.13.3, PID.14.3,PID.40.3</t>
-  </si>
-  <si>
-    <t>telecom -&gt; value</t>
-  </si>
-  <si>
-    <t>PID.13.1, PID.14.1,PID.40.1 (or XTN.12)</t>
-  </si>
-  <si>
-    <t>telecom -&gt; use</t>
-  </si>
-  <si>
-    <t>PID.13.2, PID.14.2, PID.40.2 - but often indicated by field</t>
   </si>
   <si>
     <t>"telecom" : [{
@@ -856,6 +888,48 @@
 "value" : "555-120-6047",
 "use" : "home"
 }],</t>
+  </si>
+  <si>
+    <t>telecom -&gt; value</t>
+  </si>
+  <si>
+    <t>PID.13.1, PID.14.1,PID.40.1 (or XTN.12)</t>
+  </si>
+  <si>
+    <t>telecom -&gt; use</t>
+  </si>
+  <si>
+    <t>PID.13.2, PID.14.2, PID.40.2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>telecom -&gt; use Mapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+AS, DIR, PUB, WP, WPN -&gt; work
+H, HP, HV, PRN, ORN, PRS -&gt; home
+MC, PG, NET -&gt; mobile
+TMP -&gt; temp
+BAD -&gt; old
+All others -&gt; home</t>
+    </r>
   </si>
   <si>
     <t>extension -&gt; extension -&gt; url</t>
@@ -1561,15 +1635,6 @@
     </r>
   </si>
   <si>
-    <t>text</t>
-  </si>
-  <si>
-    <t>"text" : {
-"status" : "generated",
-"div" : "&lt;div xmlns=\"http://www.w3.org/1999/xhtml\" xml:lang=\"en\" lang=\"en\"&gt;&lt;a name=\"Patient_PatientExample\"&gt; &lt;/a&gt; .................. &lt;/div&gt;"
-},</t>
-  </si>
-  <si>
     <t>contact</t>
   </si>
   <si>
@@ -3820,41 +3885,6 @@
     <t>ORC.23.2</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">WP'  - &gt; work
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>'H'  - &gt; home</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-'TMP'  - &gt; temp
-'MC' or 'PG' - &gt; mobile
-Otherwise -&gt; ORC.23.2</t>
-    </r>
-  </si>
-  <si>
     <t>ORC.22.1 + OR.C22.2 + ORC.22.3 + ORC.22.4 + ORC.22.5 + ORC.22.6</t>
   </si>
   <si>
@@ -3869,44 +3899,35 @@
       }]</t>
   </si>
   <si>
-    <t>address -&gt; use</t>
-  </si>
-  <si>
     <t>ORC.22.7</t>
   </si>
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">WP'  - &gt; work
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>'H' or 'HP' - &gt; home</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ORC.22.7 -&gt; use Mapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-'TMP'  - &gt; temp
-'OLD' or 'BAD' - &gt; old
-Otherwise -&gt; ORC.22.7</t>
+WP -&gt; work
+BA -&gt; billing
+TMP -&gt; temp
+OLD, BAD -&gt; old
+All Others -&gt; work</t>
     </r>
   </si>
   <si>
@@ -5160,12 +5181,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF333333"/>
-      <name val="Verdana"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <u/>
       <sz val="11"/>
@@ -5173,6 +5188,12 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Verdana"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -5377,21 +5398,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -5413,10 +5428,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -5428,6 +5442,13 @@
     <font>
       <sz val="11"/>
       <color indexed="10"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -5957,7 +5978,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6090,21 +6111,21 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -6138,9 +6159,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -6151,21 +6169,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -6244,7 +6247,7 @@
     <cellStyle name="Warning" xfId="59"/>
   </cellStyles>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{238349B5-1BB3-4751-9B4E-71FF109ADF5E}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{28044996-8122-42C6-83B6-FBCDF117356A}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -6513,23 +6516,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="11.8545454545455" defaultRowHeight="14.5" outlineLevelRow="7" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="11.8571428571429" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="14.2818181818182" style="70" customWidth="1"/>
+    <col min="1" max="1" width="14.2857142857143" style="64" customWidth="1"/>
     <col min="2" max="2" width="47" customWidth="1"/>
-    <col min="3" max="3" width="123.572727272727" customWidth="1"/>
+    <col min="3" max="3" width="123.571428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="61"/>
-      <c r="B2" s="61" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="60" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="53" t="s">
@@ -6537,8 +6540,8 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="61"/>
-      <c r="B3" s="61" t="s">
+      <c r="A3" s="60"/>
+      <c r="B3" s="60" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="53" t="s">
@@ -6546,26 +6549,26 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="61"/>
-      <c r="B4" s="61" t="s">
+      <c r="A4" s="60"/>
+      <c r="B4" s="60" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="53" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="43.5" spans="1:3">
-      <c r="A5" s="61"/>
-      <c r="B5" s="61" t="s">
+    <row r="5" ht="45" spans="1:3">
+      <c r="A5" s="60"/>
+      <c r="B5" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="64" t="s">
+      <c r="C5" s="63" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="61"/>
-      <c r="B6" s="64" t="s">
+      <c r="A6" s="60"/>
+      <c r="B6" s="63" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="53" t="s">
@@ -6573,8 +6576,8 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="61"/>
-      <c r="B7" s="61" t="s">
+      <c r="A7" s="60"/>
+      <c r="B7" s="60" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="10" t="s">
@@ -6582,8 +6585,8 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="61"/>
-      <c r="B8" s="61"/>
+      <c r="A8" s="60"/>
+      <c r="B8" s="60"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1.39370078740157" bottom="1.39370078740157" header="1" footer="1"/>
@@ -6596,15 +6599,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" style="2" customWidth="1"/>
-    <col min="2" max="2" width="33.5727272727273" style="2" customWidth="1"/>
-    <col min="3" max="3" width="49.6636363636364" style="2" customWidth="1"/>
-    <col min="4" max="4" width="56.5545454545455" style="2" customWidth="1"/>
-    <col min="5" max="5" width="53.2818181818182" style="2" customWidth="1"/>
-    <col min="6" max="6" width="47.5727272727273" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.14545454545454" style="2"/>
+    <col min="1" max="1" width="14.7142857142857" style="2" customWidth="1"/>
+    <col min="2" max="2" width="33.5714285714286" style="2" customWidth="1"/>
+    <col min="3" max="3" width="49.6666666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.552380952381" style="2" customWidth="1"/>
+    <col min="5" max="5" width="53.2857142857143" style="2" customWidth="1"/>
+    <col min="6" max="6" width="47.5714285714286" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9.14285714285714" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -6640,7 +6643,7 @@
     <row r="3" s="2" customFormat="1" spans="1:3">
       <c r="A3" s="1"/>
       <c r="B3" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>336</v>
@@ -6649,10 +6652,10 @@
     <row r="4" s="2" customFormat="1" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>337</v>
@@ -6661,7 +6664,7 @@
     <row r="5" s="2" customFormat="1" spans="1:6">
       <c r="A5" s="1"/>
       <c r="B5" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>49</v>
@@ -6670,9 +6673,9 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="29" spans="2:6">
+    <row r="6" s="2" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>419</v>
@@ -6696,9 +6699,9 @@
         <v>421</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" ht="145" spans="2:5">
+    <row r="8" s="2" customFormat="1" ht="150" spans="2:5">
       <c r="B8" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>340</v>
@@ -6722,7 +6725,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="145" spans="2:5">
+    <row r="10" s="2" customFormat="1" ht="150" spans="2:5">
       <c r="B10" s="6" t="s">
         <v>352</v>
       </c>
@@ -6736,7 +6739,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="159.5" spans="2:5">
+    <row r="11" s="2" customFormat="1" ht="180" spans="2:5">
       <c r="B11" s="6" t="s">
         <v>355</v>
       </c>
@@ -6746,7 +6749,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" ht="145" spans="2:5">
+    <row r="12" s="2" customFormat="1" ht="150" spans="2:5">
       <c r="B12" s="6" t="s">
         <v>357</v>
       </c>
@@ -6756,9 +6759,9 @@
         <v>428</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" ht="58" spans="2:4">
+    <row r="13" s="2" customFormat="1" ht="75" spans="2:4">
       <c r="B13" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>366</v>
@@ -6767,15 +6770,15 @@
         <v>429</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" ht="29" spans="2:3">
+    <row r="14" s="2" customFormat="1" ht="30" spans="2:3">
       <c r="B14" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" ht="43.5" spans="2:4">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" ht="45" spans="2:4">
       <c r="B15" s="6" t="s">
         <v>368</v>
       </c>
@@ -6786,7 +6789,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" ht="29" spans="2:5">
+    <row r="16" s="2" customFormat="1" ht="30" spans="2:5">
       <c r="B16" s="6" t="s">
         <v>371</v>
       </c>
@@ -6800,12 +6803,12 @@
         <v>374</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" ht="43.5" spans="2:4">
+    <row r="17" s="2" customFormat="1" ht="45" spans="2:4">
       <c r="B17" s="6" t="s">
         <v>431</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>432</v>
@@ -6824,7 +6827,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" ht="159.5" spans="2:5">
+    <row r="19" s="2" customFormat="1" ht="165" spans="2:5">
       <c r="B19" s="2" t="s">
         <v>434</v>
       </c>
@@ -6837,10 +6840,10 @@
     </row>
     <row r="20" s="2" customFormat="1" spans="2:4">
       <c r="B20" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>437</v>
@@ -6848,7 +6851,7 @@
     </row>
     <row r="21" s="2" customFormat="1" ht="46" customHeight="1" spans="2:4">
       <c r="B21" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>381</v>
@@ -6869,176 +6872,178 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" style="61" customWidth="1"/>
-    <col min="2" max="2" width="28.2818181818182" style="61" customWidth="1"/>
-    <col min="3" max="3" width="62.7272727272727" style="61" customWidth="1"/>
-    <col min="4" max="4" width="54.5454545454545" style="61" customWidth="1"/>
-    <col min="5" max="5" width="11.1818181818182" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" style="60" customWidth="1"/>
+    <col min="2" max="2" width="28.2857142857143" style="60" customWidth="1"/>
+    <col min="3" max="3" width="62.7238095238095" style="60" customWidth="1"/>
+    <col min="4" max="4" width="54.5428571428571" style="60" customWidth="1"/>
+    <col min="5" max="5" width="57" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="62" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="62" t="s">
+      <c r="D1" s="61" t="s">
         <v>16</v>
       </c>
+      <c r="E1" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="63" t="s">
-        <v>17</v>
+      <c r="A2" s="62" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="63"/>
-      <c r="B3" s="61" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="61" t="s">
+      <c r="A3" s="62"/>
+      <c r="B3" s="60" t="s">
         <v>19</v>
       </c>
+      <c r="C3" s="60" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="63"/>
-      <c r="B4" s="61" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="61" t="s">
+      <c r="A4" s="62"/>
+      <c r="B4" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="61" t="s">
+      <c r="C4" s="60" t="s">
         <v>22</v>
       </c>
+      <c r="D4" s="60" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="5" ht="61" customHeight="1" spans="2:4">
-      <c r="B5" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="61" t="s">
+      <c r="B5" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="64" t="s">
+      <c r="C5" s="60" t="s">
         <v>25</v>
       </c>
+      <c r="D5" s="63" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="6" ht="49" customHeight="1" spans="2:4">
-      <c r="B6" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="65" t="s">
+      <c r="B6" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="64"/>
+      <c r="C6" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="63"/>
     </row>
     <row r="7" ht="71" customHeight="1" spans="2:4">
-      <c r="B7" s="61" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="66" t="s">
+      <c r="B7" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="64"/>
+      <c r="C7" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="63"/>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="61" t="s">
+      <c r="B8" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="64"/>
+      <c r="C8" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="63"/>
     </row>
     <row r="9" spans="2:3">
-      <c r="B9" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="61" t="s">
+      <c r="B9" s="60" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="10" ht="29" spans="2:3">
-      <c r="B10" s="61" t="s">
+      <c r="C9" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="64" t="s">
+    </row>
+    <row r="10" ht="30" spans="2:3">
+      <c r="B10" s="60" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" s="60" customFormat="1" spans="1:1">
+      <c r="C10" s="63" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="1:1">
       <c r="A13" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="14" s="60" customFormat="1" spans="2:3">
-      <c r="B14" s="60" t="s">
+    <row r="14" s="2" customFormat="1" spans="2:3">
+      <c r="B14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="60" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" s="60" customFormat="1" spans="2:3">
-      <c r="B15" s="60" t="s">
+      <c r="C14" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="2:3">
+      <c r="B15" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="67" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" s="60" customFormat="1" spans="2:3">
-      <c r="B16" s="60" t="s">
+      <c r="C15" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="2:3">
+      <c r="B16" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="60" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" s="60" customFormat="1" ht="129" customHeight="1" spans="2:7">
-      <c r="B17" s="60" t="s">
+      <c r="C16" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="129" customHeight="1" spans="2:7">
+      <c r="B17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="47" t="s">
+      <c r="C17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
-    </row>
-    <row r="18" s="60" customFormat="1" spans="2:5">
-      <c r="B18" s="68" t="s">
+      <c r="E17" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+    </row>
+    <row r="18" s="2" customFormat="1" ht="30" spans="2:5">
+      <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="67"/>
-    </row>
-    <row r="19" s="60" customFormat="1" spans="2:5">
-      <c r="B19" s="60" t="s">
+      <c r="C18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="2:5">
+      <c r="B19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" s="67"/>
-    </row>
-    <row r="20" s="60" customFormat="1" ht="29" spans="2:5">
-      <c r="B20" s="68" t="s">
+      <c r="C19" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="60"/>
-      <c r="E20" s="69"/>
+      <c r="E19" s="5"/>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="30" spans="2:5">
+      <c r="B20" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="E20" s="8"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21"/>
@@ -7051,11 +7056,11 @@
       <c r="C22"/>
     </row>
     <row r="23" hidden="1" spans="2:3">
-      <c r="B23" s="61" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="64" t="s">
+      <c r="B23" s="60" t="s">
         <v>45</v>
+      </c>
+      <c r="C23" s="63" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -7074,14 +7079,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E65"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.1181818181818" customWidth="1"/>
-    <col min="2" max="2" width="39.1454545454545" style="11" customWidth="1"/>
-    <col min="3" max="3" width="61.5727272727273" style="11" customWidth="1"/>
-    <col min="4" max="4" width="66.8545454545455" style="11" customWidth="1"/>
-    <col min="5" max="5" width="64.5727272727273" style="11" customWidth="1"/>
-    <col min="6" max="256" width="11.8545454545455" customWidth="1"/>
+    <col min="1" max="1" width="13.1142857142857" customWidth="1"/>
+    <col min="2" max="2" width="39.1428571428571" style="11" customWidth="1"/>
+    <col min="3" max="3" width="61.5714285714286" style="11" customWidth="1"/>
+    <col min="4" max="4" width="66.8571428571429" style="11" customWidth="1"/>
+    <col min="5" max="5" width="64.5714285714286" style="11" customWidth="1"/>
+    <col min="6" max="256" width="11.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="17" customFormat="1" spans="1:5">
@@ -7098,7 +7103,7 @@
         <v>16</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7110,7 +7115,7 @@
     <row r="3" spans="1:5">
       <c r="A3" s="17"/>
       <c r="B3" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>47</v>
@@ -7119,10 +7124,10 @@
     </row>
     <row r="4" spans="2:5">
       <c r="B4" s="19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>48</v>
@@ -7132,23 +7137,23 @@
     <row r="5" spans="1:5">
       <c r="A5" s="17"/>
       <c r="B5" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>49</v>
       </c>
       <c r="E5" s="23"/>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" ht="30" spans="2:5">
       <c r="B6" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>50</v>
       </c>
       <c r="E6" s="23"/>
     </row>
-    <row r="7" ht="58" spans="2:5">
+    <row r="7" ht="60" spans="2:5">
       <c r="B7" s="11" t="s">
         <v>51</v>
       </c>
@@ -7158,11 +7163,11 @@
       <c r="D7" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="48" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" ht="58" spans="2:5">
+    <row r="8" ht="60" spans="2:5">
       <c r="B8" s="11" t="s">
         <v>55</v>
       </c>
@@ -7219,7 +7224,7 @@
       </c>
       <c r="E12" s="23"/>
     </row>
-    <row r="13" ht="58" spans="2:5">
+    <row r="13" ht="60" spans="2:5">
       <c r="B13" s="11" t="s">
         <v>68</v>
       </c>
@@ -7231,7 +7236,7 @@
       </c>
       <c r="E13" s="23"/>
     </row>
-    <row r="14" ht="29" spans="2:5">
+    <row r="14" ht="30" spans="2:5">
       <c r="B14" s="11" t="s">
         <v>71</v>
       </c>
@@ -7267,7 +7272,7 @@
       </c>
       <c r="E16" s="23"/>
     </row>
-    <row r="17" ht="116" spans="2:5">
+    <row r="17" ht="135" spans="2:5">
       <c r="B17" s="11" t="s">
         <v>80</v>
       </c>
@@ -7279,7 +7284,7 @@
       </c>
       <c r="E17" s="23"/>
     </row>
-    <row r="18" ht="29" spans="2:5">
+    <row r="18" spans="2:5">
       <c r="B18" s="11" t="s">
         <v>83</v>
       </c>
@@ -7324,424 +7329,427 @@
       </c>
       <c r="E22" s="23"/>
     </row>
-    <row r="23" spans="2:5">
+    <row r="23" ht="105" spans="2:5">
       <c r="B23" s="11" t="s">
         <v>93</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="23"/>
+      <c r="E23" s="44" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>98</v>
       </c>
       <c r="E24" s="23"/>
     </row>
-    <row r="25" ht="72.5" spans="2:5">
+    <row r="25" spans="2:5">
       <c r="B25" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E25" s="23"/>
     </row>
-    <row r="26" ht="29" spans="2:5">
-      <c r="B26" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="C26" s="27" t="s">
+    <row r="26" ht="105" spans="2:5">
+      <c r="B26" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D26" s="56" t="s">
+      <c r="C26" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="44" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="27" ht="29" spans="2:5">
+    <row r="27" ht="45" spans="2:5">
       <c r="B27" s="27" t="s">
         <v>104</v>
       </c>
       <c r="C27" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="D27" s="56"/>
-      <c r="E27" s="57"/>
-    </row>
-    <row r="28" spans="2:5">
+      <c r="D27" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" ht="30" spans="2:5">
       <c r="B28" s="27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D28" s="56"/>
       <c r="E28" s="57"/>
     </row>
-    <row r="29" ht="29" spans="2:5">
+    <row r="29" ht="30" spans="2:5">
       <c r="B29" s="27" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D29" s="56"/>
       <c r="E29" s="57"/>
     </row>
-    <row r="30" spans="2:5">
+    <row r="30" ht="30" spans="2:5">
       <c r="B30" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="D30" s="56"/>
-      <c r="E30" s="8"/>
-    </row>
-    <row r="31" ht="29" spans="2:5">
+      <c r="E30" s="57"/>
+    </row>
+    <row r="31" spans="2:5">
       <c r="B31" s="27" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D31" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" ht="29" spans="2:5">
+        <v>115</v>
+      </c>
+      <c r="D31" s="56"/>
+      <c r="E31" s="8"/>
+    </row>
+    <row r="32" ht="30" spans="2:5">
       <c r="B32" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="C32" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="D32" s="56"/>
-      <c r="E32" s="57"/>
-    </row>
-    <row r="33" spans="2:5">
+      <c r="C32" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D32" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" ht="30" spans="2:5">
       <c r="B33" s="27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D33" s="56"/>
       <c r="E33" s="57"/>
     </row>
-    <row r="34" ht="29" spans="2:5">
+    <row r="34" ht="30" spans="2:5">
       <c r="B34" s="27" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D34" s="56"/>
       <c r="E34" s="57"/>
     </row>
-    <row r="35" spans="2:5">
+    <row r="35" ht="30" spans="2:5">
       <c r="B35" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>118</v>
       </c>
       <c r="D35" s="56"/>
       <c r="E35" s="57"/>
     </row>
     <row r="36" spans="2:5">
       <c r="B36" s="27" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D36" s="56" t="s">
-        <v>118</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="D36" s="56"/>
       <c r="E36" s="57"/>
     </row>
-    <row r="37" ht="43.5" spans="2:5">
+    <row r="37" spans="2:5">
       <c r="B37" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="C37" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D37" s="56"/>
-      <c r="E37" s="71" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="38" ht="130.5" spans="2:5">
-      <c r="B38" s="58" t="s">
+      <c r="D37" s="56" t="s">
         <v>122</v>
       </c>
-      <c r="C38" s="58"/>
-      <c r="D38" s="58" t="s">
+      <c r="E37" s="57"/>
+    </row>
+    <row r="38" ht="45" spans="2:5">
+      <c r="B38" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="E38" s="23" t="s">
+      <c r="C38" s="27" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="39" ht="130.5" spans="2:5">
+      <c r="D38" s="56"/>
+      <c r="E38" s="65" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="39" ht="135" spans="2:5">
       <c r="B39" s="58" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C39" s="58"/>
       <c r="D39" s="58" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5">
-      <c r="B40" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="C40" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="E40" s="23"/>
+    </row>
+    <row r="40" ht="135" spans="2:5">
+      <c r="B40" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="41" spans="2:5">
       <c r="B41" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>132</v>
       </c>
       <c r="E41" s="23"/>
     </row>
     <row r="42" spans="2:5">
       <c r="B42" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>134</v>
       </c>
       <c r="E42" s="23"/>
     </row>
     <row r="43" spans="2:5">
-      <c r="B43" s="11" t="s">
-        <v>133</v>
+      <c r="B43" s="19" t="s">
+        <v>135</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E43" s="23"/>
     </row>
-    <row r="44" ht="188.5" spans="2:5">
-      <c r="B44" s="19" t="s">
-        <v>134</v>
+    <row r="44" spans="2:5">
+      <c r="B44" s="11" t="s">
+        <v>137</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D44" s="11" t="s">
         <v>136</v>
       </c>
       <c r="E44" s="23"/>
     </row>
-    <row r="45" ht="188.5" spans="2:5">
+    <row r="45" ht="195" spans="2:5">
       <c r="B45" s="19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="D45" s="53" t="s">
         <v>139</v>
       </c>
-      <c r="E45" s="47" t="s">
+      <c r="D45" s="11" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="46" ht="188.5" spans="2:5">
+      <c r="E45" s="23"/>
+    </row>
+    <row r="46" ht="195" spans="2:5">
       <c r="B46" s="19" t="s">
         <v>141</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="E46" s="23"/>
-    </row>
-    <row r="47" spans="2:5">
-      <c r="B47" s="11" t="s">
+      <c r="E46" s="48" t="s">
         <v>144</v>
       </c>
+    </row>
+    <row r="47" ht="195" spans="2:5">
+      <c r="B47" s="19" t="s">
+        <v>145</v>
+      </c>
       <c r="C47" s="11" t="s">
-        <v>128</v>
+        <v>146</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>147</v>
       </c>
       <c r="E47" s="23"/>
     </row>
     <row r="48" spans="2:5">
       <c r="B48" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="C48" s="24" t="s">
-        <v>146</v>
+        <v>148</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>132</v>
       </c>
       <c r="E48" s="23"/>
     </row>
     <row r="49" spans="2:5">
       <c r="B49" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>150</v>
       </c>
       <c r="E49" s="23"/>
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E50" s="23"/>
     </row>
-    <row r="51" ht="145" spans="2:5">
+    <row r="51" spans="2:5">
       <c r="B51" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D51" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C51" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="E51" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5">
+      <c r="E51" s="23"/>
+    </row>
+    <row r="52" ht="150" spans="2:5">
       <c r="B52" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="C52" s="24" t="s">
+      <c r="C52" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="E52" s="23"/>
+      <c r="D52" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>128</v>
+        <v>158</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>159</v>
       </c>
       <c r="E53" s="23"/>
     </row>
     <row r="54" spans="2:5">
       <c r="B54" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C54" s="24" t="s">
-        <v>158</v>
+        <v>160</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>132</v>
       </c>
       <c r="E54" s="23"/>
     </row>
     <row r="55" spans="2:5">
       <c r="B55" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
+      </c>
+      <c r="C55" s="24" t="s">
+        <v>162</v>
       </c>
       <c r="E55" s="23"/>
     </row>
     <row r="56" spans="2:5">
       <c r="B56" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E56" s="23"/>
     </row>
     <row r="57" spans="2:5">
       <c r="B57" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="C57" s="24" t="s">
-        <v>163</v>
+        <v>165</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>164</v>
       </c>
       <c r="E57" s="23"/>
     </row>
-    <row r="58" ht="174" spans="2:5">
+    <row r="58" spans="2:5">
       <c r="B58" s="11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E58" s="23"/>
     </row>
-    <row r="59" ht="72.5" spans="2:5">
-      <c r="B59" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27" t="s">
+    <row r="59" ht="180" spans="2:5">
+      <c r="B59" s="11" t="s">
         <v>168</v>
       </c>
+      <c r="C59" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>170</v>
+      </c>
       <c r="E59" s="23"/>
     </row>
-    <row r="60" ht="246.5" spans="2:5">
+    <row r="60" ht="255" spans="2:5">
       <c r="B60" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="2:5">
       <c r="B61" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D61" s="59" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E61" s="23"/>
     </row>
     <row r="62" ht="42.95" customHeight="1" spans="2:5">
       <c r="B62" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C62" s="55" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D62" s="59"/>
       <c r="E62" s="23"/>
@@ -7750,10 +7758,11 @@
       <c r="C65" s="55"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D26:D30"/>
-    <mergeCell ref="D31:D35"/>
-    <mergeCell ref="D36:D37"/>
+  <mergeCells count="5">
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D27:D31"/>
+    <mergeCell ref="D32:D36"/>
+    <mergeCell ref="D37:D38"/>
     <mergeCell ref="D61:D62"/>
   </mergeCells>
   <hyperlinks>
@@ -7770,14 +7779,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.14545454545454" customWidth="1"/>
-    <col min="2" max="2" width="40.8545454545455" customWidth="1"/>
-    <col min="3" max="3" width="61.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="57.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="54.8545454545455" customWidth="1"/>
-    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
+    <col min="1" max="1" width="9.14285714285714" customWidth="1"/>
+    <col min="2" max="2" width="40.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="61.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="57.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="54.8571428571429" customWidth="1"/>
+    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7794,7 +7803,7 @@
         <v>16</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1" spans="1:5">
@@ -7802,7 +7811,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="49" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C2" s="49"/>
       <c r="D2" s="49"/>
@@ -7810,236 +7819,236 @@
     </row>
     <row r="3" spans="2:5">
       <c r="B3" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E3" s="23"/>
     </row>
     <row r="4" spans="2:5">
       <c r="B4" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="23"/>
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E5" s="23"/>
     </row>
     <row r="6" spans="2:5">
       <c r="B6" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E6" s="23"/>
     </row>
-    <row r="7" ht="29" spans="2:5">
+    <row r="7" ht="45" spans="2:5">
       <c r="B7" s="18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D7" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E7" s="50" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="8" ht="130.5" spans="2:5">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" ht="135" spans="2:5">
       <c r="B8" s="51" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="51" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D9" s="26"/>
       <c r="E9" s="23"/>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="51" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D10" s="26"/>
       <c r="E10" s="23" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="11" ht="217.5" spans="2:5">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" ht="225" spans="2:5">
       <c r="B11" s="18" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D11" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="E11" s="23" t="s">
         <v>196</v>
-      </c>
-      <c r="D11" s="53" t="s">
-        <v>197</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="18" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="14" ht="29" spans="2:5">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="14" ht="30" spans="2:5">
       <c r="B14" s="18" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C14" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="15" ht="116" spans="2:5">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="15" ht="135" spans="2:5">
       <c r="B15" s="18" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E15" s="50" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="16" ht="43.5" spans="2:5">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="16" ht="45" spans="2:5">
       <c r="B16" s="18" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E16" s="23"/>
     </row>
-    <row r="17" ht="58" spans="2:5">
+    <row r="17" ht="60" spans="2:5">
       <c r="B17" s="51" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C17" s="54" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E17" s="23"/>
     </row>
-    <row r="18" ht="58" spans="2:5">
+    <row r="18" ht="60" spans="2:5">
       <c r="B18" s="54" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C18" s="54" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D20" s="27"/>
       <c r="E20" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" ht="77" customHeight="1" spans="2:5">
       <c r="B21" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E21" s="23"/>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="23"/>
@@ -8059,14 +8068,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="43.5727272727273" customWidth="1"/>
-    <col min="5" max="5" width="57.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
+    <col min="4" max="4" width="43.5714285714286" customWidth="1"/>
+    <col min="5" max="5" width="57.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -8083,7 +8092,7 @@
         <v>16</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8094,30 +8103,30 @@
     </row>
     <row r="3" spans="2:5">
       <c r="B3" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E3" s="23"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E4" s="23"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="17"/>
       <c r="B5" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>49</v>
@@ -8125,270 +8134,270 @@
       <c r="D5" s="11"/>
       <c r="E5" s="23"/>
     </row>
-    <row r="6" ht="29" spans="2:5">
+    <row r="6" ht="30" spans="2:5">
       <c r="B6" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="23"/>
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="8" ht="72.5" spans="2:5">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="8" ht="75" spans="2:5">
       <c r="B8" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="C8" s="46" t="s">
-        <v>231</v>
+        <v>232</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>233</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="E8" s="72" t="s">
-        <v>233</v>
+        <v>234</v>
+      </c>
+      <c r="E8" s="66" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="C9" s="46" t="s">
-        <v>235</v>
+        <v>236</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>237</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="23"/>
     </row>
-    <row r="10" ht="72.5" spans="2:5">
+    <row r="10" ht="75" spans="2:5">
       <c r="B10" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="C10" s="46" t="s">
-        <v>237</v>
+        <v>238</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>239</v>
       </c>
       <c r="D10" s="11"/>
-      <c r="E10" s="72" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="11" ht="116" spans="2:5">
+      <c r="E10" s="66" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" ht="120" spans="2:5">
       <c r="B11" s="18" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="E11" s="47" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="12" ht="43.5" spans="2:5">
+        <v>243</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="12" ht="60" spans="2:5">
       <c r="B12" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>244</v>
+        <v>245</v>
+      </c>
+      <c r="E12" s="44" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="18" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E13" s="23"/>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C14" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E14" s="23"/>
     </row>
-    <row r="15" ht="72.5" spans="2:5">
+    <row r="15" ht="75" spans="2:5">
       <c r="B15" s="18" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E15" s="23"/>
     </row>
-    <row r="16" ht="29" spans="2:5">
+    <row r="16" ht="30" spans="2:5">
       <c r="B16" s="18" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E16" s="23"/>
     </row>
-    <row r="17" ht="58" spans="2:5">
+    <row r="17" ht="60" spans="2:5">
       <c r="B17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E17" s="23"/>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E18" s="23"/>
     </row>
-    <row r="19" ht="29" spans="2:5">
+    <row r="19" ht="30" spans="2:5">
       <c r="B19" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="23" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="23" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="23" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="23" ht="29" spans="2:5">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="23" ht="30" spans="2:5">
       <c r="B23" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D23" s="11"/>
       <c r="E23" s="23" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="24" ht="72.5" spans="2:5">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="24" ht="75" spans="2:5">
       <c r="B24" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E24" s="23"/>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D25" s="11"/>
       <c r="E25" s="23"/>
     </row>
-    <row r="26" ht="58" spans="2:5">
+    <row r="26" ht="60" spans="2:5">
       <c r="B26" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D27" s="11"/>
       <c r="E27" s="23" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" spans="2:5">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="2:5">
       <c r="B28" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E28" s="23"/>
     </row>
-    <row r="29" ht="29" spans="2:5">
+    <row r="29" ht="30" spans="2:5">
       <c r="B29" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="23"/>
@@ -8408,15 +8417,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="19.4272727272727" style="29" customWidth="1"/>
+    <col min="1" max="1" width="19.4285714285714" style="29" customWidth="1"/>
     <col min="2" max="2" width="37" style="29" customWidth="1"/>
-    <col min="3" max="3" width="50.5727272727273" style="29" customWidth="1"/>
-    <col min="4" max="4" width="39.1454545454545" style="29" customWidth="1"/>
-    <col min="5" max="5" width="54.1454545454545" style="29" customWidth="1"/>
-    <col min="6" max="6" width="51.1454545454545" style="29" customWidth="1"/>
-    <col min="7" max="16384" width="9.14545454545454" style="29"/>
+    <col min="3" max="3" width="50.5714285714286" style="29" customWidth="1"/>
+    <col min="4" max="4" width="39.1428571428571" style="29" customWidth="1"/>
+    <col min="5" max="5" width="54.1428571428571" style="29" customWidth="1"/>
+    <col min="6" max="6" width="51.1428571428571" style="29" customWidth="1"/>
+    <col min="7" max="16384" width="9.14285714285714" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8433,10 +8442,10 @@
         <v>16</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F1" s="31" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8447,26 +8456,26 @@
     </row>
     <row r="3" spans="2:5">
       <c r="B3" s="33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E3" s="32"/>
     </row>
     <row r="4" spans="2:5">
       <c r="B4" s="29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="32"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="31"/>
       <c r="B5" s="33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="33" t="s">
         <v>49</v>
@@ -8474,230 +8483,230 @@
       <c r="D5" s="33"/>
       <c r="E5" s="32"/>
     </row>
-    <row r="6" ht="29" spans="2:5">
+    <row r="6" ht="30" spans="2:5">
       <c r="B6" s="33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D6" s="33"/>
       <c r="E6" s="32"/>
     </row>
-    <row r="7" ht="29" spans="2:6">
+    <row r="7" ht="30" spans="2:6">
       <c r="B7" s="34" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C7" s="35"/>
       <c r="D7" s="35" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F7" s="36"/>
     </row>
-    <row r="8" ht="188.5" spans="2:5">
+    <row r="8" ht="195" spans="2:5">
       <c r="B8" s="29" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="29" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="32"/>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D10" s="33"/>
       <c r="E10" s="32"/>
     </row>
-    <row r="11" spans="2:5">
+    <row r="11" ht="30" spans="2:5">
       <c r="B11" s="33" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D11" s="33"/>
       <c r="E11" s="32"/>
     </row>
-    <row r="12" spans="2:5">
+    <row r="12" ht="30" spans="2:5">
       <c r="B12" s="33" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="32"/>
     </row>
-    <row r="13" ht="217.5" spans="2:5">
+    <row r="13" ht="225" spans="2:5">
       <c r="B13" s="29" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E13" s="38" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="29" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D14" s="33"/>
       <c r="E14" s="32"/>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="33" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="32"/>
     </row>
-    <row r="16" spans="2:5">
+    <row r="16" ht="30" spans="2:5">
       <c r="B16" s="33" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="32"/>
     </row>
-    <row r="17" spans="2:5">
+    <row r="17" ht="30" spans="2:5">
       <c r="B17" s="33" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="32"/>
     </row>
-    <row r="18" ht="29" spans="2:5">
+    <row r="18" ht="30" spans="2:5">
       <c r="B18" s="39" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="19" ht="130.5" spans="2:5">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="19" ht="135" spans="2:5">
       <c r="B19" s="35" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="42" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="20" ht="58" spans="2:5">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="20" ht="60" spans="2:5">
       <c r="B20" s="33" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D20" s="33"/>
-      <c r="E20" s="73" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="21" ht="174" spans="2:5">
+      <c r="E20" s="67" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="21" ht="180" spans="2:5">
       <c r="B21" s="33" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E21" s="32"/>
     </row>
-    <row r="22" ht="72.5" spans="2:6">
+    <row r="22" ht="105" spans="2:6">
       <c r="B22" s="33" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C22" s="43" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D22" s="33"/>
-      <c r="E22" s="73" t="s">
-        <v>323</v>
-      </c>
-      <c r="F22" s="44"/>
-    </row>
-    <row r="23" ht="29" spans="2:5">
+      <c r="E22" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" s="45"/>
+    </row>
+    <row r="23" ht="30" spans="2:5">
       <c r="B23" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="45" t="s">
-        <v>324</v>
+      <c r="C23" s="46" t="s">
+        <v>325</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E23" s="32"/>
     </row>
-    <row r="24" ht="72.5" spans="2:6">
+    <row r="24" ht="90" spans="2:6">
       <c r="B24" s="33" t="s">
-        <v>326</v>
+        <v>93</v>
       </c>
       <c r="C24" s="43" t="s">
         <v>327</v>
       </c>
       <c r="D24" s="33"/>
-      <c r="E24" s="73" t="s">
+      <c r="E24" s="44" t="s">
         <v>328</v>
       </c>
-      <c r="F24" s="44"/>
-    </row>
-    <row r="25" ht="43.5" spans="2:5">
+      <c r="F24" s="45"/>
+    </row>
+    <row r="25" ht="45" spans="2:5">
       <c r="B25" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="45" t="s">
+      <c r="C25" s="46" t="s">
         <v>329</v>
       </c>
       <c r="D25" s="33"/>
@@ -8743,23 +8752,23 @@
       <c r="D29" s="33"/>
       <c r="E29" s="32"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="2:5">
+    <row r="30" customHeight="1" spans="2:5">
       <c r="B30" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C30" s="43" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D30" s="33" t="s">
         <v>334</v>
       </c>
       <c r="E30" s="32"/>
     </row>
-    <row r="31" ht="29" spans="2:5">
+    <row r="31" ht="30" spans="2:5">
       <c r="B31" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="C31" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="C31" s="46" t="s">
         <v>335</v>
       </c>
       <c r="D31" s="33"/>
@@ -8782,14 +8791,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.2181818181818" customWidth="1"/>
-    <col min="2" max="2" width="26.2818181818182" customWidth="1"/>
-    <col min="3" max="3" width="43.7181818181818" customWidth="1"/>
-    <col min="4" max="4" width="47.2818181818182" customWidth="1"/>
-    <col min="5" max="5" width="80.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
+    <col min="1" max="1" width="13.2190476190476" customWidth="1"/>
+    <col min="2" max="2" width="26.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="43.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="47.2857142857143" customWidth="1"/>
+    <col min="5" max="5" width="80.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -8806,7 +8815,7 @@
         <v>16</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8817,7 +8826,7 @@
     </row>
     <row r="3" spans="2:5">
       <c r="B3" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>336</v>
@@ -8826,10 +8835,10 @@
     </row>
     <row r="4" spans="2:5">
       <c r="B4" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>337</v>
@@ -8838,16 +8847,16 @@
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>49</v>
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" ht="29" spans="2:5">
+    <row r="6" ht="30" spans="2:5">
       <c r="B6" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>338</v>
@@ -8866,9 +8875,9 @@
         <v>339</v>
       </c>
     </row>
-    <row r="8" ht="145" spans="2:5">
+    <row r="8" ht="150" spans="2:5">
       <c r="B8" s="19" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>340</v>
@@ -8880,7 +8889,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="9" ht="116" spans="2:5">
+    <row r="9" ht="120" spans="2:5">
       <c r="B9" s="25" t="s">
         <v>343</v>
       </c>
@@ -8892,10 +8901,10 @@
         <v>345</v>
       </c>
     </row>
-    <row r="10" ht="43.5" spans="1:5">
+    <row r="10" ht="45" spans="1:5">
       <c r="A10" s="26"/>
       <c r="B10" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>346</v>
@@ -8905,10 +8914,10 @@
         <v>347</v>
       </c>
     </row>
-    <row r="11" ht="203" spans="1:5">
+    <row r="11" ht="210" spans="1:5">
       <c r="A11" s="26"/>
       <c r="B11" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="27"/>
@@ -8916,10 +8925,10 @@
         <v>348</v>
       </c>
     </row>
-    <row r="12" ht="203" spans="1:5">
+    <row r="12" ht="210" spans="1:5">
       <c r="A12" s="26"/>
       <c r="B12" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="27"/>
@@ -8938,7 +8947,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="14" ht="130.5" spans="2:5">
+    <row r="14" ht="150" spans="2:5">
       <c r="B14" s="11" t="s">
         <v>352</v>
       </c>
@@ -8964,7 +8973,7 @@
         <v>357</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E16" s="11"/>
     </row>
@@ -8977,7 +8986,7 @@
       </c>
       <c r="E17" s="11"/>
     </row>
-    <row r="18" ht="101.5" spans="2:5">
+    <row r="18" ht="105" spans="2:5">
       <c r="B18" s="11" t="s">
         <v>360</v>
       </c>
@@ -8991,7 +9000,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="19" ht="29" spans="2:5">
+    <row r="19" ht="30" spans="2:5">
       <c r="B19" s="11" t="s">
         <v>364</v>
       </c>
@@ -9002,7 +9011,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="20" ht="29" spans="2:5">
+    <row r="20" ht="30" spans="2:5">
       <c r="B20" s="11" t="s">
         <v>365</v>
       </c>
@@ -9013,9 +9022,9 @@
         <v>363</v>
       </c>
     </row>
-    <row r="21" ht="72.5" spans="2:5">
+    <row r="21" ht="75" spans="2:5">
       <c r="B21" s="19" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>366</v>
@@ -9025,16 +9034,16 @@
       </c>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" ht="29" spans="2:5">
+    <row r="22" ht="30" spans="2:5">
       <c r="B22" s="19" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" ht="43.5" spans="2:5">
+    <row r="23" ht="45" spans="2:5">
       <c r="B23" s="25" t="s">
         <v>368</v>
       </c>
@@ -9046,7 +9055,7 @@
       </c>
       <c r="E23" s="11"/>
     </row>
-    <row r="24" spans="2:5">
+    <row r="24" ht="30" spans="2:5">
       <c r="B24" s="19" t="s">
         <v>371</v>
       </c>
@@ -9060,19 +9069,19 @@
         <v>374</v>
       </c>
     </row>
-    <row r="25" ht="58" spans="2:5">
+    <row r="25" ht="60" spans="2:5">
       <c r="B25" s="11" t="s">
         <v>375</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>376</v>
       </c>
       <c r="E25" s="11"/>
     </row>
-    <row r="26" ht="29" spans="2:5">
+    <row r="26" ht="30" spans="2:5">
       <c r="B26" s="11" t="s">
         <v>377</v>
       </c>
@@ -9086,10 +9095,10 @@
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>380</v>
@@ -9098,7 +9107,7 @@
     </row>
     <row r="28" ht="78" customHeight="1" spans="2:5">
       <c r="B28" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C28" s="28" t="s">
         <v>381</v>
@@ -9127,14 +9136,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="22.2818181818182" customWidth="1"/>
+    <col min="1" max="1" width="22.2857142857143" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="70.2818181818182" customWidth="1"/>
-    <col min="4" max="4" width="47.1454545454545" customWidth="1"/>
-    <col min="5" max="5" width="49.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
+    <col min="3" max="3" width="70.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="47.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="49.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9151,10 +9160,10 @@
         <v>16</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" ht="29" spans="1:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" ht="30" spans="1:5">
       <c r="A2" s="22" t="s">
         <v>382</v>
       </c>
@@ -9163,7 +9172,7 @@
     <row r="3" spans="1:5">
       <c r="A3" s="17"/>
       <c r="B3" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>336</v>
@@ -9173,10 +9182,10 @@
     <row r="4" spans="1:5">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
         <v>383</v>
@@ -9186,7 +9195,7 @@
     <row r="5" spans="1:5">
       <c r="A5" s="17"/>
       <c r="B5" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>49</v>
@@ -9194,9 +9203,9 @@
       <c r="D5" s="11"/>
       <c r="E5" s="23"/>
     </row>
-    <row r="6" ht="29" spans="2:5">
+    <row r="6" ht="30" spans="2:5">
       <c r="B6" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>384</v>
@@ -9204,9 +9213,9 @@
       <c r="D6" s="11"/>
       <c r="E6" s="23"/>
     </row>
-    <row r="7" ht="145" spans="2:5">
+    <row r="7" ht="150" spans="2:5">
       <c r="B7" s="18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C7" t="s">
         <v>385</v>
@@ -9245,7 +9254,7 @@
         <v>357</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="23"/>
@@ -9260,7 +9269,7 @@
       <c r="D11" s="11"/>
       <c r="E11" s="23"/>
     </row>
-    <row r="12" ht="29" spans="2:5">
+    <row r="12" ht="30" spans="2:5">
       <c r="B12" s="11" t="s">
         <v>360</v>
       </c>
@@ -9272,7 +9281,7 @@
       </c>
       <c r="E12" s="23"/>
     </row>
-    <row r="13" ht="29" spans="2:5">
+    <row r="13" ht="30" spans="2:5">
       <c r="B13" s="11" t="s">
         <v>364</v>
       </c>
@@ -9292,9 +9301,9 @@
       <c r="D14" s="11"/>
       <c r="E14" s="23"/>
     </row>
-    <row r="15" ht="43.5" spans="2:5">
+    <row r="15" ht="45" spans="2:5">
       <c r="B15" s="18" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>366</v>
@@ -9306,14 +9315,14 @@
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="18" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E16" s="23"/>
     </row>
-    <row r="17" ht="29" spans="2:5">
+    <row r="17" ht="30" spans="2:5">
       <c r="B17" t="s">
         <v>371</v>
       </c>
@@ -9327,12 +9336,12 @@
         <v>396</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="2:5">
+    <row r="18" customHeight="1" spans="2:5">
       <c r="B18" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>397</v>
@@ -9341,7 +9350,7 @@
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>381</v>
@@ -9364,14 +9373,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.14545454545454" customWidth="1"/>
-    <col min="2" max="2" width="23.1454545454545" customWidth="1"/>
-    <col min="3" max="3" width="34.2818181818182" customWidth="1"/>
-    <col min="4" max="4" width="25.1454545454545" customWidth="1"/>
-    <col min="5" max="5" width="33.4272727272727" customWidth="1"/>
-    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
+    <col min="1" max="1" width="9.14285714285714" customWidth="1"/>
+    <col min="2" max="2" width="23.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="34.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="25.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="33.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9388,17 +9397,17 @@
         <v>16</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>398</v>
@@ -9407,10 +9416,10 @@
     <row r="4" spans="1:4">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
         <v>399</v>
@@ -9419,7 +9428,7 @@
     <row r="5" spans="1:5">
       <c r="A5" s="17"/>
       <c r="B5" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>49</v>
@@ -9427,9 +9436,9 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" ht="29" spans="2:5">
+    <row r="6" ht="45" spans="2:5">
       <c r="B6" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>400</v>
@@ -9439,7 +9448,7 @@
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>401</v>
@@ -9449,7 +9458,7 @@
       </c>
       <c r="E7" s="20"/>
     </row>
-    <row r="8" ht="159.5" spans="2:5">
+    <row r="8" ht="165" spans="2:5">
       <c r="B8" s="18" t="s">
         <v>352</v>
       </c>
@@ -9457,7 +9466,7 @@
         <v>403</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E8" s="21"/>
     </row>
@@ -9485,26 +9494,26 @@
         <v>406</v>
       </c>
     </row>
-    <row r="12" ht="87" spans="2:4">
+    <row r="12" ht="90" spans="2:4">
       <c r="B12" s="18" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>407</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="13" ht="29" spans="2:3">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" ht="45" spans="2:3">
       <c r="B13" s="18" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="14" ht="72.5" spans="2:4">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="14" ht="75" spans="2:4">
       <c r="B14" s="18" t="s">
         <v>368</v>
       </c>
@@ -9515,7 +9524,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="15" ht="87" spans="2:4">
+    <row r="15" ht="90" spans="2:4">
       <c r="B15" t="s">
         <v>409</v>
       </c>
@@ -9534,20 +9543,20 @@
         <v>413</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="2:4">
+    <row r="17" customHeight="1" spans="2:4">
       <c r="B17" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="18" ht="29" spans="2:4">
+    <row r="18" ht="30" spans="2:4">
       <c r="B18" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>415</v>

--- a/support/specifications/hl7/HL7v2.to.FHIR.Conversion.Spec.xlsx
+++ b/support/specifications/hl7/HL7v2.to.FHIR.Conversion.Spec.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" firstSheet="1" activeTab="5"/>
+    <workbookView windowWidth="28800" windowHeight="12180" firstSheet="1" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="441">
   <si>
     <t>FHIR Resources</t>
   </si>
@@ -870,9 +870,8 @@
       <t xml:space="preserve">
 H, HP, HV -&gt; home
 WP -&gt; work
-BA -&gt; billing
 TMP -&gt; temp
-OLD, BAD -&gt; old
+BAD -&gt; old
 All Others -&gt; home</t>
     </r>
   </si>
@@ -923,9 +922,9 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-AS, DIR, PUB, WP, WPN -&gt; work
-H, HP, HV, PRN, ORN, PRS -&gt; home
-MC, PG, NET -&gt; mobile
+AS, DIR, PUB, WP -&gt; work
+H, HP, HV, EC -&gt; home
+MC, PG -&gt; mobile
 TMP -&gt; temp
 BAD -&gt; old
 All others -&gt; home</t>
@@ -3885,6 +3884,35 @@
     <t>ORC.23.2</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>telecom -&gt; use Mapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+AS, DIR, PUB, WP -&gt; work
+MC, PG -&gt; mobile
+TMP -&gt; temp
+BAD -&gt; old
+All others -&gt; work</t>
+    </r>
+  </si>
+  <si>
     <t>ORC.22.1 + OR.C22.2 + ORC.22.3 + ORC.22.4 + ORC.22.5 + ORC.22.6</t>
   </si>
   <si>
@@ -3926,7 +3954,7 @@
 WP -&gt; work
 BA -&gt; billing
 TMP -&gt; temp
-OLD, BAD -&gt; old
+BAD -&gt; old
 All Others -&gt; work</t>
     </r>
   </si>
@@ -3974,33 +4002,30 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>statusCode.code -&gt; status Mapping</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+      <t>OBX.11 → status Mapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
-completed -&gt; final 
-final -&gt; final 
-active -&gt; preliminary
-aborted -&gt; cancelled 
-cancelled -&gt; cancelled 
-held -&gt; registered 
-suspended -&gt; registered 
-nullified -&gt; entered-in-error 
-All Others -&gt; unknown</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F, U -&gt; final
+C -&gt; corrected
+D -&gt; entered-in-error
+All others -&gt; unknown</t>
     </r>
   </si>
   <si>
@@ -4549,6 +4574,38 @@
   </si>
   <si>
     <t>Path to get the language</t>
+  </si>
+  <si>
+    <t>OBX.11 OR OBR.25
+If there are no OBX with OBX.11 filled, the status will be taken from OBR.25.</t>
+  </si>
+  <si>
+    <r>
+      <t>OBX.11/OBR.25 → status Mapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F, U -&gt; final
+C -&gt; corrected
+D -&gt; entered-in-error
+All others -&gt; unknown</t>
+    </r>
   </si>
   <si>
     <t>"category": [
@@ -5048,7 +5105,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="56">
+  <fonts count="58">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -5089,6 +5146,20 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF00B050"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10.5"/>
+      <color rgb="FF00B050"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -5404,9 +5475,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -5416,14 +5487,6 @@
       <color indexed="8"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -5446,11 +5509,19 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF00B050"/>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="40">
@@ -5815,170 +5886,170 @@
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6006,7 +6077,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -6018,43 +6095,43 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
@@ -6063,76 +6140,76 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6144,7 +6221,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -6180,7 +6257,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6247,7 +6324,7 @@
     <cellStyle name="Warning" xfId="59"/>
   </cellStyles>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{28044996-8122-42C6-83B6-FBCDF117356A}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{074BE817-8BFB-4996-A254-5BEA51FB84F7}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -6518,75 +6595,75 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="11.8571428571429" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="14.2857142857143" style="64" customWidth="1"/>
+    <col min="1" max="1" width="14.2857142857143" style="66" customWidth="1"/>
     <col min="2" max="2" width="47" customWidth="1"/>
     <col min="3" max="3" width="123.571428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="60"/>
-      <c r="B2" s="60" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="55" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="60"/>
-      <c r="B3" s="60" t="s">
+      <c r="A3" s="62"/>
+      <c r="B3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="55" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="60"/>
-      <c r="B4" s="60" t="s">
+      <c r="A4" s="62"/>
+      <c r="B4" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="55" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:3">
-      <c r="A5" s="60"/>
-      <c r="B5" s="60" t="s">
+      <c r="A5" s="62"/>
+      <c r="B5" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="65" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="60"/>
-      <c r="B6" s="63" t="s">
+      <c r="A6" s="62"/>
+      <c r="B6" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="55" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="60"/>
-      <c r="B7" s="60" t="s">
+      <c r="A7" s="62"/>
+      <c r="B7" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="12" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="60"/>
-      <c r="B8" s="60"/>
+      <c r="A8" s="62"/>
+      <c r="B8" s="62"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1.39370078740157" bottom="1.39370078740157" header="1" footer="1"/>
@@ -6618,16 +6695,16 @@
         <v>14</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="17" customHeight="1" spans="1:6">
@@ -6646,7 +6723,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:4">
@@ -6658,7 +6735,7 @@
         <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:6">
@@ -6678,7 +6755,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -6693,149 +6770,149 @@
         <v>53</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="150" spans="2:5">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="74.25" spans="2:5">
       <c r="B8" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>340</v>
+      <c r="C8" s="9" t="s">
+        <v>423</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="E8" s="9" t="s">
         <v>342</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="409" customHeight="1" spans="2:5">
       <c r="B9" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="5" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="150" spans="2:5">
       <c r="B10" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="180" spans="2:5">
       <c r="B11" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="9" t="s">
-        <v>427</v>
+      <c r="E11" s="11" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="150" spans="2:5">
       <c r="B12" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="9" t="s">
-        <v>428</v>
+      <c r="E12" s="11" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="75" spans="2:4">
       <c r="B13" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>366</v>
+      <c r="C13" s="12" t="s">
+        <v>367</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" ht="30" spans="2:3">
       <c r="B14" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="13" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="45" spans="2:4">
       <c r="B15" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="30" spans="2:5">
       <c r="B16" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="E16" s="12" t="s">
         <v>374</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="45" spans="2:4">
       <c r="B17" s="6" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>216</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" spans="2:6">
       <c r="B18" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E18" s="8"/>
-      <c r="F18" s="13" t="s">
-        <v>433</v>
+      <c r="F18" s="15" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="165" spans="2:5">
       <c r="B19" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="2:4">
@@ -6845,8 +6922,8 @@
       <c r="C20" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>437</v>
+      <c r="D20" s="16" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" ht="46" customHeight="1" spans="2:4">
@@ -6854,9 +6931,9 @@
         <v>178</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="D21" s="14"/>
+        <v>382</v>
+      </c>
+      <c r="D21" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6874,24 +6951,24 @@
   <dimension ref="A1:G23"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" style="60" customWidth="1"/>
-    <col min="2" max="2" width="28.2857142857143" style="60" customWidth="1"/>
-    <col min="3" max="3" width="62.7238095238095" style="60" customWidth="1"/>
-    <col min="4" max="4" width="54.5428571428571" style="60" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" style="62" customWidth="1"/>
+    <col min="2" max="2" width="28.2857142857143" style="62" customWidth="1"/>
+    <col min="3" max="3" width="62.7238095238095" style="62" customWidth="1"/>
+    <col min="4" max="4" width="54.5428571428571" style="62" customWidth="1"/>
     <col min="5" max="5" width="57" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="63" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -6899,82 +6976,82 @@
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="64" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="62"/>
-      <c r="B3" s="60" t="s">
+      <c r="A3" s="64"/>
+      <c r="B3" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="60" t="s">
+      <c r="C3" s="62" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="62"/>
-      <c r="B4" s="60" t="s">
+      <c r="A4" s="64"/>
+      <c r="B4" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="60" t="s">
+      <c r="C4" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="60" t="s">
+      <c r="D4" s="62" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" ht="61" customHeight="1" spans="2:4">
-      <c r="B5" s="60" t="s">
+      <c r="B5" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="60" t="s">
+      <c r="C5" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="63" t="s">
+      <c r="D5" s="65" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" ht="49" customHeight="1" spans="2:4">
-      <c r="B6" s="60" t="s">
+      <c r="B6" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="C6" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="63"/>
+      <c r="D6" s="65"/>
     </row>
     <row r="7" ht="71" customHeight="1" spans="2:4">
-      <c r="B7" s="60" t="s">
+      <c r="B7" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="63"/>
+      <c r="D7" s="65"/>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="60" t="s">
+      <c r="B8" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="60" t="s">
+      <c r="C8" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="63"/>
+      <c r="D8" s="65"/>
     </row>
     <row r="9" spans="2:3">
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="60" t="s">
+      <c r="C9" s="62" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10" ht="30" spans="2:3">
-      <c r="B10" s="60" t="s">
+      <c r="B10" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="65" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7014,11 +7091,11 @@
       <c r="C17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="48" t="s">
+      <c r="E17" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="30" spans="2:5">
       <c r="B18" s="5" t="s">
@@ -7056,10 +7133,10 @@
       <c r="C22"/>
     </row>
     <row r="23" hidden="1" spans="2:3">
-      <c r="B23" s="60" t="s">
+      <c r="B23" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="63" t="s">
+      <c r="C23" s="65" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7082,304 +7159,304 @@
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="13.1142857142857" customWidth="1"/>
-    <col min="2" max="2" width="39.1428571428571" style="11" customWidth="1"/>
-    <col min="3" max="3" width="61.5714285714286" style="11" customWidth="1"/>
-    <col min="4" max="4" width="66.8571428571429" style="11" customWidth="1"/>
-    <col min="5" max="5" width="64.5714285714286" style="11" customWidth="1"/>
+    <col min="2" max="2" width="39.1428571428571" style="13" customWidth="1"/>
+    <col min="3" max="3" width="61.5714285714286" style="13" customWidth="1"/>
+    <col min="4" max="4" width="66.8571428571429" style="13" customWidth="1"/>
+    <col min="5" max="5" width="64.5714285714286" style="13" customWidth="1"/>
     <col min="6" max="256" width="11.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="17" customFormat="1" spans="1:5">
-      <c r="A1" s="15" t="s">
+    <row r="1" s="19" customFormat="1" spans="1:5">
+      <c r="A1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="18" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="23"/>
+      <c r="E2" s="25"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="17"/>
-      <c r="B3" s="11" t="s">
+      <c r="A3" s="19"/>
+      <c r="B3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="23"/>
+      <c r="E3" s="25"/>
     </row>
     <row r="4" spans="2:5">
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="25"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="17"/>
-      <c r="B5" s="19" t="s">
+      <c r="A5" s="19"/>
+      <c r="B5" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="23"/>
+      <c r="E5" s="25"/>
     </row>
     <row r="6" ht="30" spans="2:5">
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="23"/>
+      <c r="E6" s="25"/>
     </row>
     <row r="7" ht="60" spans="2:5">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="50" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="8" ht="60" spans="2:5">
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="23"/>
+      <c r="E8" s="25"/>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="55" t="s">
+      <c r="C9" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="23"/>
+      <c r="E9" s="25"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="23"/>
+      <c r="E10" s="25"/>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="23"/>
+      <c r="E11" s="25"/>
     </row>
     <row r="12" spans="2:5">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="23"/>
+      <c r="E12" s="25"/>
     </row>
     <row r="13" ht="60" spans="2:5">
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="23"/>
+      <c r="E13" s="25"/>
     </row>
     <row r="14" ht="30" spans="2:5">
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="23"/>
+      <c r="E14" s="25"/>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="E15" s="23"/>
+      <c r="E15" s="25"/>
     </row>
     <row r="16" spans="2:5">
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="23"/>
+      <c r="E16" s="25"/>
     </row>
     <row r="17" ht="135" spans="2:5">
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="23"/>
+      <c r="E17" s="25"/>
     </row>
     <row r="18" spans="2:5">
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="E18" s="23"/>
+      <c r="E18" s="25"/>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="E19" s="23"/>
+      <c r="E19" s="25"/>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="23"/>
+      <c r="E20" s="25"/>
     </row>
     <row r="21" spans="2:5">
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="E21" s="23"/>
+      <c r="E21" s="25"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="E22" s="23"/>
-    </row>
-    <row r="23" ht="105" spans="2:5">
-      <c r="B23" s="11" t="s">
+      <c r="E22" s="25"/>
+    </row>
+    <row r="23" ht="90" spans="2:5">
+      <c r="B23" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="44" t="s">
+      <c r="E23" s="46" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="E24" s="23"/>
+      <c r="E24" s="25"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="E25" s="23"/>
+      <c r="E25" s="25"/>
     </row>
     <row r="26" ht="105" spans="2:5">
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="E26" s="44" t="s">
+      <c r="E26" s="46" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="27" ht="45" spans="2:5">
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="C27" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="D27" s="56" t="s">
+      <c r="D27" s="58" t="s">
         <v>106</v>
       </c>
       <c r="E27" s="8" t="s">
@@ -7387,53 +7464,53 @@
       </c>
     </row>
     <row r="28" ht="30" spans="2:5">
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="C28" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="D28" s="56"/>
-      <c r="E28" s="57"/>
+      <c r="D28" s="58"/>
+      <c r="E28" s="59"/>
     </row>
     <row r="29" ht="30" spans="2:5">
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="D29" s="56"/>
-      <c r="E29" s="57"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="59"/>
     </row>
     <row r="30" ht="30" spans="2:5">
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="C30" s="27" t="s">
+      <c r="C30" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="D30" s="56"/>
-      <c r="E30" s="57"/>
+      <c r="D30" s="58"/>
+      <c r="E30" s="59"/>
     </row>
     <row r="31" spans="2:5">
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="29" t="s">
         <v>114</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D31" s="56"/>
+      <c r="D31" s="58"/>
       <c r="E31" s="8"/>
     </row>
     <row r="32" ht="30" spans="2:5">
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="29" t="s">
         <v>104</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="56" t="s">
+      <c r="D32" s="58" t="s">
         <v>116</v>
       </c>
       <c r="E32" s="8" t="s">
@@ -7441,211 +7518,211 @@
       </c>
     </row>
     <row r="33" ht="30" spans="2:5">
-      <c r="B33" s="27" t="s">
+      <c r="B33" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="C33" s="27" t="s">
+      <c r="C33" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="D33" s="56"/>
-      <c r="E33" s="57"/>
+      <c r="D33" s="58"/>
+      <c r="E33" s="59"/>
     </row>
     <row r="34" ht="30" spans="2:5">
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C34" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="D34" s="56"/>
-      <c r="E34" s="57"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="59"/>
     </row>
     <row r="35" ht="30" spans="2:5">
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="C35" s="27" t="s">
+      <c r="C35" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="56"/>
-      <c r="E35" s="57"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="59"/>
     </row>
     <row r="36" spans="2:5">
-      <c r="B36" s="27" t="s">
+      <c r="B36" s="29" t="s">
         <v>114</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="D36" s="56"/>
-      <c r="E36" s="57"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="59"/>
     </row>
     <row r="37" spans="2:5">
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="29" t="s">
         <v>114</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D37" s="56" t="s">
+      <c r="D37" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="E37" s="57"/>
+      <c r="E37" s="59"/>
     </row>
     <row r="38" ht="45" spans="2:5">
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="C38" s="27" t="s">
+      <c r="C38" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="D38" s="56"/>
-      <c r="E38" s="65" t="s">
+      <c r="D38" s="58"/>
+      <c r="E38" s="67" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="39" ht="135" spans="2:5">
-      <c r="B39" s="58" t="s">
+      <c r="B39" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="C39" s="58"/>
-      <c r="D39" s="58" t="s">
+      <c r="C39" s="60"/>
+      <c r="D39" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="E39" s="23" t="s">
+      <c r="E39" s="25" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="40" ht="135" spans="2:5">
-      <c r="B40" s="58" t="s">
+      <c r="B40" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="C40" s="58"/>
-      <c r="D40" s="58" t="s">
+      <c r="C40" s="60"/>
+      <c r="D40" s="60" t="s">
         <v>130</v>
       </c>
-      <c r="E40" s="23" t="s">
+      <c r="E40" s="25" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="41" spans="2:5">
-      <c r="B41" s="19" t="s">
+      <c r="B41" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="E41" s="23"/>
+      <c r="E41" s="25"/>
     </row>
     <row r="42" spans="2:5">
-      <c r="B42" s="19" t="s">
+      <c r="B42" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="E42" s="23"/>
+      <c r="E42" s="25"/>
     </row>
     <row r="43" spans="2:5">
-      <c r="B43" s="19" t="s">
+      <c r="B43" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E43" s="23"/>
+      <c r="E43" s="25"/>
     </row>
     <row r="44" spans="2:5">
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="E44" s="23"/>
+      <c r="E44" s="25"/>
     </row>
     <row r="45" ht="195" spans="2:5">
-      <c r="B45" s="19" t="s">
+      <c r="B45" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D45" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="E45" s="23"/>
+      <c r="E45" s="25"/>
     </row>
     <row r="46" ht="195" spans="2:5">
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D46" s="53" t="s">
+      <c r="D46" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="E46" s="48" t="s">
+      <c r="E46" s="50" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="47" ht="195" spans="2:5">
-      <c r="B47" s="19" t="s">
+      <c r="B47" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="E47" s="23"/>
+      <c r="E47" s="25"/>
     </row>
     <row r="48" spans="2:5">
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="E48" s="23"/>
+      <c r="E48" s="25"/>
     </row>
     <row r="49" spans="2:5">
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="C49" s="24" t="s">
+      <c r="C49" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="E49" s="23"/>
+      <c r="E49" s="25"/>
     </row>
     <row r="50" spans="2:5">
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="E50" s="23"/>
+      <c r="E50" s="25"/>
     </row>
     <row r="51" spans="2:5">
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="E51" s="23"/>
+      <c r="E51" s="25"/>
     </row>
     <row r="52" ht="150" spans="2:5">
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D52" s="13" t="s">
         <v>156</v>
       </c>
       <c r="E52" s="8" t="s">
@@ -7653,109 +7730,109 @@
       </c>
     </row>
     <row r="53" spans="2:5">
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C53" s="24" t="s">
+      <c r="C53" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="E53" s="23"/>
+      <c r="E53" s="25"/>
     </row>
     <row r="54" spans="2:5">
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="E54" s="23"/>
+      <c r="E54" s="25"/>
     </row>
     <row r="55" spans="2:5">
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="C55" s="24" t="s">
+      <c r="C55" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="E55" s="23"/>
+      <c r="E55" s="25"/>
     </row>
     <row r="56" spans="2:5">
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="E56" s="23"/>
+      <c r="E56" s="25"/>
     </row>
     <row r="57" spans="2:5">
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="E57" s="23"/>
+      <c r="E57" s="25"/>
     </row>
     <row r="58" spans="2:5">
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="C58" s="24" t="s">
+      <c r="C58" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="E58" s="23"/>
+      <c r="E58" s="25"/>
     </row>
     <row r="59" ht="180" spans="2:5">
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="C59" s="24" t="s">
+      <c r="C59" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D59" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="E59" s="23"/>
+      <c r="E59" s="25"/>
     </row>
     <row r="60" ht="255" spans="2:5">
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C60" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D60" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="E60" s="23" t="s">
+      <c r="E60" s="25" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="61" spans="2:5">
-      <c r="B61" s="11" t="s">
+      <c r="B61" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C61" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D61" s="59" t="s">
+      <c r="D61" s="61" t="s">
         <v>177</v>
       </c>
-      <c r="E61" s="23"/>
+      <c r="E61" s="25"/>
     </row>
     <row r="62" ht="42.95" customHeight="1" spans="2:5">
-      <c r="B62" s="11" t="s">
+      <c r="B62" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C62" s="55" t="s">
+      <c r="C62" s="57" t="s">
         <v>179</v>
       </c>
-      <c r="D62" s="59"/>
-      <c r="E62" s="23"/>
+      <c r="D62" s="61"/>
+      <c r="E62" s="25"/>
     </row>
     <row r="65" spans="3:3">
-      <c r="C65" s="55"/>
+      <c r="C65" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7790,71 +7867,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="17" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1" spans="1:5">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="51" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
     </row>
     <row r="3" spans="2:5">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="E3" s="23"/>
+      <c r="E3" s="25"/>
     </row>
     <row r="4" spans="2:5">
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="20" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="25"/>
     </row>
     <row r="5" spans="2:5">
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="20" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
         <v>182</v>
       </c>
-      <c r="E5" s="23"/>
+      <c r="E5" s="25"/>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="20" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
         <v>183</v>
       </c>
-      <c r="E6" s="23"/>
+      <c r="E6" s="25"/>
     </row>
     <row r="7" ht="45" spans="2:5">
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>184</v>
       </c>
       <c r="C7" t="s">
@@ -7863,18 +7940,18 @@
       <c r="D7" t="s">
         <v>186</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="52" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="8" ht="135" spans="2:5">
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="53" t="s">
         <v>188</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" s="54" t="s">
         <v>190</v>
       </c>
       <c r="E8" s="8" t="s">
@@ -7882,43 +7959,43 @@
       </c>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="53" t="s">
         <v>192</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D9" s="26"/>
-      <c r="E9" s="23"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="25"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="53" t="s">
         <v>194</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="D10" s="26"/>
-      <c r="E10" s="23" t="s">
+      <c r="D10" s="28"/>
+      <c r="E10" s="25" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="11" ht="225" spans="2:5">
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="20" t="s">
         <v>197</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D11" s="53" t="s">
+      <c r="D11" s="55" t="s">
         <v>199</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="25" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="12" spans="2:5">
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="20" t="s">
         <v>200</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -7929,7 +8006,7 @@
       </c>
     </row>
     <row r="13" spans="2:5">
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="20" t="s">
         <v>202</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -7940,7 +8017,7 @@
       </c>
     </row>
     <row r="14" ht="30" spans="2:5">
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="20" t="s">
         <v>204</v>
       </c>
       <c r="C14" t="s">
@@ -7949,53 +8026,53 @@
       <c r="D14" t="s">
         <v>206</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="25" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="15" ht="135" spans="2:5">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="E15" s="50" t="s">
+      <c r="E15" s="52" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="16" ht="45" spans="2:5">
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="20" t="s">
         <v>212</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="E16" s="23"/>
+      <c r="E16" s="25"/>
     </row>
     <row r="17" ht="60" spans="2:5">
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="53" t="s">
         <v>215</v>
       </c>
-      <c r="C17" s="54" t="s">
+      <c r="C17" s="56" t="s">
         <v>216</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="29" t="s">
         <v>217</v>
       </c>
-      <c r="E17" s="23"/>
+      <c r="E17" s="25"/>
     </row>
     <row r="18" ht="60" spans="2:5">
-      <c r="B18" s="54" t="s">
+      <c r="B18" s="56" t="s">
         <v>218</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="C18" s="56" t="s">
         <v>219</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -8012,7 +8089,7 @@
       <c r="C19" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="29" t="s">
         <v>223</v>
       </c>
       <c r="E19" s="8" t="s">
@@ -8026,32 +8103,32 @@
       <c r="C20" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="D20" s="27"/>
+      <c r="D20" s="29"/>
       <c r="E20" s="8" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="21" ht="77" customHeight="1" spans="2:5">
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="E21" s="23"/>
+      <c r="E21" s="25"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="23"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8079,76 +8156,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="17" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="23"/>
+      <c r="E2" s="25"/>
     </row>
     <row r="3" spans="2:5">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="E3" s="23"/>
+      <c r="E3" s="25"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="17"/>
-      <c r="B4" s="18" t="s">
+      <c r="A4" s="19"/>
+      <c r="B4" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="13" t="s">
         <v>22</v>
       </c>
       <c r="D4" t="s">
         <v>229</v>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="25"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="17"/>
-      <c r="B5" s="19" t="s">
+      <c r="A5" s="19"/>
+      <c r="B5" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="23"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="25"/>
     </row>
     <row r="6" ht="30" spans="2:5">
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="23"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="25"/>
     </row>
     <row r="7" spans="2:5">
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="C7" s="11"/>
+      <c r="C7" s="13"/>
       <c r="D7" t="s">
         <v>231</v>
       </c>
@@ -8157,71 +8234,71 @@
       </c>
     </row>
     <row r="8" ht="75" spans="2:5">
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="49" t="s">
         <v>233</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E8" s="66" t="s">
+      <c r="E8" s="68" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="49" t="s">
         <v>237</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="23"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="25"/>
     </row>
     <row r="10" ht="75" spans="2:5">
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="49" t="s">
         <v>239</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="66" t="s">
+      <c r="D10" s="13"/>
+      <c r="E10" s="68" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="11" ht="120" spans="2:5">
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="E11" s="48" t="s">
+      <c r="E11" s="50" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="12" ht="60" spans="2:5">
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="46" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="13" spans="2:5">
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="20" t="s">
         <v>247</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="E13" s="23"/>
+      <c r="E13" s="25"/>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" t="s">
@@ -8230,61 +8307,61 @@
       <c r="C14" t="s">
         <v>250</v>
       </c>
-      <c r="E14" s="23"/>
+      <c r="E14" s="25"/>
     </row>
     <row r="15" ht="75" spans="2:5">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="20" t="s">
         <v>251</v>
       </c>
       <c r="C15" t="s">
         <v>252</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="E15" s="23"/>
+      <c r="E15" s="25"/>
     </row>
     <row r="16" ht="30" spans="2:5">
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="E16" s="23"/>
+      <c r="E16" s="25"/>
     </row>
     <row r="17" ht="60" spans="2:5">
       <c r="B17" t="s">
         <v>256</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="E17" s="23"/>
+      <c r="E17" s="25"/>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" t="s">
         <v>259</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="E18" s="23"/>
+      <c r="E18" s="25"/>
     </row>
     <row r="19" ht="30" spans="2:5">
       <c r="B19" t="s">
         <v>261</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="E19" s="23" t="s">
+      <c r="E19" s="25" t="s">
         <v>264</v>
       </c>
     </row>
@@ -8292,11 +8369,11 @@
       <c r="B20" t="s">
         <v>265</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="23" t="s">
+      <c r="D20" s="13"/>
+      <c r="E20" s="25" t="s">
         <v>267</v>
       </c>
     </row>
@@ -8304,11 +8381,11 @@
       <c r="B21" t="s">
         <v>268</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="23" t="s">
+      <c r="D21" s="13"/>
+      <c r="E21" s="25" t="s">
         <v>267</v>
       </c>
     </row>
@@ -8316,9 +8393,9 @@
       <c r="B22" t="s">
         <v>270</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="23" t="s">
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="25" t="s">
         <v>267</v>
       </c>
     </row>
@@ -8326,11 +8403,11 @@
       <c r="B23" t="s">
         <v>271</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="23" t="s">
+      <c r="D23" s="13"/>
+      <c r="E23" s="25" t="s">
         <v>267</v>
       </c>
     </row>
@@ -8338,33 +8415,33 @@
       <c r="B24" t="s">
         <v>273</v>
       </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11" t="s">
+      <c r="C24" s="13"/>
+      <c r="D24" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="E24" s="23"/>
+      <c r="E24" s="25"/>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" t="s">
         <v>275</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="23"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="25"/>
     </row>
     <row r="26" ht="60" spans="2:5">
       <c r="B26" t="s">
         <v>277</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="E26" s="25" t="s">
         <v>280</v>
       </c>
     </row>
@@ -8372,35 +8449,35 @@
       <c r="B27" t="s">
         <v>281</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="23" t="s">
+      <c r="D27" s="13"/>
+      <c r="E27" s="25" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:5">
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="E28" s="23"/>
+      <c r="E28" s="25"/>
     </row>
     <row r="29" ht="30" spans="2:5">
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="23"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8419,360 +8496,360 @@
   <dimension ref="A1:F31"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="19.4285714285714" style="29" customWidth="1"/>
-    <col min="2" max="2" width="37" style="29" customWidth="1"/>
-    <col min="3" max="3" width="50.5714285714286" style="29" customWidth="1"/>
-    <col min="4" max="4" width="39.1428571428571" style="29" customWidth="1"/>
-    <col min="5" max="5" width="54.1428571428571" style="29" customWidth="1"/>
-    <col min="6" max="6" width="51.1428571428571" style="29" customWidth="1"/>
-    <col min="7" max="16384" width="9.14285714285714" style="29"/>
+    <col min="1" max="1" width="19.4285714285714" style="31" customWidth="1"/>
+    <col min="2" max="2" width="37" style="31" customWidth="1"/>
+    <col min="3" max="3" width="50.5714285714286" style="31" customWidth="1"/>
+    <col min="4" max="4" width="39.1428571428571" style="31" customWidth="1"/>
+    <col min="5" max="5" width="54.1428571428571" style="31" customWidth="1"/>
+    <col min="6" max="6" width="51.1428571428571" style="31" customWidth="1"/>
+    <col min="7" max="16384" width="9.14285714285714" style="31"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="32"/>
+      <c r="E2" s="34"/>
     </row>
     <row r="3" spans="2:5">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="35" t="s">
         <v>286</v>
       </c>
-      <c r="E3" s="32"/>
+      <c r="E3" s="34"/>
     </row>
     <row r="4" spans="2:5">
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="32"/>
+      <c r="E4" s="34"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="31"/>
-      <c r="B5" s="33" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="33"/>
-      <c r="E5" s="32"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="34"/>
     </row>
     <row r="6" ht="30" spans="2:5">
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="35" t="s">
         <v>287</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="32"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="34"/>
     </row>
     <row r="7" ht="30" spans="2:6">
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="36" t="s">
         <v>288</v>
       </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35" t="s">
+      <c r="C7" s="37"/>
+      <c r="D7" s="37" t="s">
         <v>289</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="F7" s="36"/>
+      <c r="F7" s="38"/>
     </row>
     <row r="8" ht="195" spans="2:5">
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="39" t="s">
         <v>292</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="14" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="31" t="s">
         <v>295</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="34"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="35" t="s">
         <v>297</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="32"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="34"/>
     </row>
     <row r="11" ht="30" spans="2:5">
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="35" t="s">
         <v>299</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="34"/>
     </row>
     <row r="12" ht="30" spans="2:5">
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="35" t="s">
         <v>300</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="32"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="34"/>
     </row>
     <row r="13" ht="225" spans="2:5">
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="31" t="s">
         <v>302</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="40" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="31" t="s">
         <v>306</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="32"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="34"/>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="35" t="s">
         <v>308</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="D15" s="33"/>
-      <c r="E15" s="32"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="34"/>
     </row>
     <row r="16" ht="30" spans="2:5">
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="35" t="s">
         <v>310</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="34"/>
     </row>
     <row r="17" ht="30" spans="2:5">
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="35" t="s">
         <v>311</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="34"/>
     </row>
     <row r="18" ht="30" spans="2:5">
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="41" t="s">
         <v>313</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="42" t="s">
         <v>314</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="E18" s="40" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="19" ht="135" spans="2:5">
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="42" t="s">
+      <c r="C19" s="43"/>
+      <c r="D19" s="44" t="s">
         <v>318</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="34" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="20" ht="60" spans="2:5">
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="45" t="s">
         <v>320</v>
       </c>
-      <c r="D20" s="33"/>
-      <c r="E20" s="67" t="s">
+      <c r="D20" s="35"/>
+      <c r="E20" s="69" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="21" ht="180" spans="2:5">
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="43" t="s">
+      <c r="C21" s="45" t="s">
         <v>322</v>
       </c>
-      <c r="D21" s="33" t="s">
+      <c r="D21" s="35" t="s">
         <v>323</v>
       </c>
-      <c r="E21" s="32"/>
-    </row>
-    <row r="22" ht="105" spans="2:6">
-      <c r="B22" s="33" t="s">
+      <c r="E21" s="34"/>
+    </row>
+    <row r="22" ht="90" spans="2:6">
+      <c r="B22" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="43" t="s">
+      <c r="C22" s="45" t="s">
         <v>324</v>
       </c>
-      <c r="D22" s="33"/>
-      <c r="E22" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="F22" s="45"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="46" t="s">
+        <v>325</v>
+      </c>
+      <c r="F22" s="47"/>
     </row>
     <row r="23" ht="30" spans="2:5">
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="46" t="s">
-        <v>325</v>
-      </c>
-      <c r="D23" s="33" t="s">
+      <c r="C23" s="48" t="s">
         <v>326</v>
       </c>
-      <c r="E23" s="32"/>
+      <c r="D23" s="35" t="s">
+        <v>327</v>
+      </c>
+      <c r="E23" s="34"/>
     </row>
     <row r="24" ht="90" spans="2:6">
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="43" t="s">
-        <v>327</v>
-      </c>
-      <c r="D24" s="33"/>
-      <c r="E24" s="44" t="s">
+      <c r="C24" s="45" t="s">
         <v>328</v>
       </c>
-      <c r="F24" s="45"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="46" t="s">
+        <v>329</v>
+      </c>
+      <c r="F24" s="47"/>
     </row>
     <row r="25" ht="45" spans="2:5">
-      <c r="B25" s="33" t="s">
+      <c r="B25" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="46" t="s">
-        <v>329</v>
-      </c>
-      <c r="D25" s="33"/>
-      <c r="E25" s="32"/>
+      <c r="C25" s="48" t="s">
+        <v>330</v>
+      </c>
+      <c r="D25" s="35"/>
+      <c r="E25" s="34"/>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="33" t="s">
+      <c r="B26" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="43" t="s">
-        <v>330</v>
-      </c>
-      <c r="D26" s="33"/>
-      <c r="E26" s="32"/>
+      <c r="C26" s="45" t="s">
+        <v>331</v>
+      </c>
+      <c r="D26" s="35"/>
+      <c r="E26" s="34"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="33" t="s">
+      <c r="B27" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="43" t="s">
-        <v>331</v>
-      </c>
-      <c r="D27" s="33"/>
-      <c r="E27" s="32"/>
+      <c r="C27" s="45" t="s">
+        <v>332</v>
+      </c>
+      <c r="D27" s="35"/>
+      <c r="E27" s="34"/>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="33" t="s">
+      <c r="B28" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="43" t="s">
-        <v>332</v>
-      </c>
-      <c r="D28" s="33"/>
-      <c r="E28" s="32"/>
+      <c r="C28" s="45" t="s">
+        <v>333</v>
+      </c>
+      <c r="D28" s="35"/>
+      <c r="E28" s="34"/>
     </row>
     <row r="29" spans="2:5">
-      <c r="B29" s="33" t="s">
+      <c r="B29" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="43" t="s">
-        <v>333</v>
-      </c>
-      <c r="D29" s="33"/>
-      <c r="E29" s="32"/>
+      <c r="C29" s="45" t="s">
+        <v>334</v>
+      </c>
+      <c r="D29" s="35"/>
+      <c r="E29" s="34"/>
     </row>
     <row r="30" customHeight="1" spans="2:5">
-      <c r="B30" s="33" t="s">
+      <c r="B30" s="35" t="s">
         <v>175</v>
       </c>
-      <c r="C30" s="43" t="s">
+      <c r="C30" s="45" t="s">
         <v>176</v>
       </c>
-      <c r="D30" s="33" t="s">
-        <v>334</v>
-      </c>
-      <c r="E30" s="32"/>
+      <c r="D30" s="35" t="s">
+        <v>335</v>
+      </c>
+      <c r="E30" s="34"/>
     </row>
     <row r="31" ht="30" spans="2:5">
-      <c r="B31" s="33" t="s">
+      <c r="B31" s="35" t="s">
         <v>178</v>
       </c>
-      <c r="C31" s="46" t="s">
-        <v>335</v>
-      </c>
-      <c r="D31" s="33"/>
-      <c r="E31" s="32"/>
+      <c r="C31" s="48" t="s">
+        <v>336</v>
+      </c>
+      <c r="D31" s="35"/>
+      <c r="E31" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8802,318 +8879,318 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="17" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="11"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="2:5">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="E3" s="11"/>
+      <c r="C3" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="E3" s="13"/>
     </row>
     <row r="4" spans="2:5">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="E4" s="11"/>
+      <c r="D4" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="E4" s="13"/>
     </row>
     <row r="5" spans="2:5">
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="11"/>
+      <c r="E5" s="13"/>
     </row>
     <row r="6" ht="30" spans="2:5">
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="E6" s="11"/>
+      <c r="C6" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="E6" s="13"/>
     </row>
     <row r="7" spans="2:5">
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11" t="s">
+      <c r="C7" s="13"/>
+      <c r="D7" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="20" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="8" ht="150" spans="2:5">
-      <c r="B8" s="19" t="s">
+      <c r="E7" s="22" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="8" ht="74.25" spans="2:5">
+      <c r="B8" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="D8" s="11" t="s">
+      <c r="C8" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="D8" s="13" t="s">
         <v>342</v>
       </c>
+      <c r="E8" s="10" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="9" ht="120" spans="2:5">
-      <c r="B9" s="25" t="s">
-        <v>343</v>
-      </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="27" t="s">
+      <c r="B9" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="C9" s="28"/>
+      <c r="D9" s="29" t="s">
         <v>345</v>
       </c>
+      <c r="E9" s="14" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="10" ht="45" spans="1:5">
-      <c r="A10" s="26"/>
+      <c r="A10" s="28"/>
       <c r="B10" s="6" t="s">
         <v>202</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="D10" s="27"/>
+        <v>347</v>
+      </c>
+      <c r="D10" s="29"/>
       <c r="E10" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" ht="210" spans="1:5">
-      <c r="A11" s="26"/>
+      <c r="A11" s="28"/>
       <c r="B11" s="6" t="s">
         <v>197</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="9" t="s">
-        <v>348</v>
+      <c r="D11" s="29"/>
+      <c r="E11" s="11" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="12" ht="210" spans="1:5">
-      <c r="A12" s="26"/>
+      <c r="A12" s="28"/>
       <c r="B12" s="6" t="s">
         <v>200</v>
       </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="9" t="s">
-        <v>349</v>
+      <c r="D12" s="29"/>
+      <c r="E12" s="11" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="26"/>
+      <c r="A13" s="28"/>
       <c r="B13" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="27"/>
+      <c r="D13" s="29"/>
       <c r="E13" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14" ht="150" spans="2:5">
-      <c r="B14" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="C14" s="11" t="s">
+      <c r="B14" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="C14" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="E14" s="11"/>
+      <c r="D14" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="E14" s="13"/>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="C15" s="11" t="s">
+      <c r="B15" s="21" t="s">
         <v>356</v>
       </c>
-      <c r="E15" s="11"/>
+      <c r="C15" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="E15" s="13"/>
     </row>
     <row r="16" spans="2:5">
-      <c r="B16" s="19" t="s">
-        <v>357</v>
-      </c>
-      <c r="C16" s="11" t="s">
+      <c r="B16" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="E16" s="11"/>
+      <c r="E16" s="13"/>
     </row>
     <row r="17" spans="2:5">
-      <c r="B17" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="C17" s="11" t="s">
+      <c r="B17" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="E17" s="11"/>
+      <c r="C17" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="E17" s="13"/>
     </row>
     <row r="18" ht="105" spans="2:5">
-      <c r="B18" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="C18" s="11" t="s">
+      <c r="B18" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="C18" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="D18" s="13" t="s">
         <v>363</v>
       </c>
+      <c r="E18" s="13" t="s">
+        <v>364</v>
+      </c>
     </row>
     <row r="19" ht="30" spans="2:5">
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>363</v>
-      </c>
     </row>
     <row r="20" ht="30" spans="2:5">
-      <c r="B20" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>363</v>
+      <c r="B20" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="21" ht="75" spans="2:5">
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="D21" s="11" t="s">
+      <c r="C21" s="12" t="s">
         <v>367</v>
       </c>
-      <c r="E21" s="11"/>
+      <c r="D21" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="E21" s="13"/>
     </row>
     <row r="22" ht="30" spans="2:5">
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="E22" s="11"/>
+      <c r="E22" s="13"/>
     </row>
     <row r="23" ht="45" spans="2:5">
-      <c r="B23" s="25" t="s">
-        <v>368</v>
+      <c r="B23" s="27" t="s">
+        <v>369</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D23" s="27" t="s">
         <v>370</v>
       </c>
-      <c r="E23" s="11"/>
+      <c r="D23" s="29" t="s">
+        <v>371</v>
+      </c>
+      <c r="E23" s="13"/>
     </row>
     <row r="24" ht="30" spans="2:5">
-      <c r="B24" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="C24" s="11" t="s">
+      <c r="B24" s="21" t="s">
         <v>372</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="C24" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="D24" s="13" t="s">
         <v>374</v>
       </c>
+      <c r="E24" s="13" t="s">
+        <v>375</v>
+      </c>
     </row>
     <row r="25" ht="60" spans="2:5">
-      <c r="B25" s="11" t="s">
-        <v>375</v>
+      <c r="B25" s="13" t="s">
+        <v>376</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="D25" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="E25" s="11"/>
+      <c r="D25" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="E25" s="13"/>
     </row>
     <row r="26" ht="30" spans="2:5">
-      <c r="B26" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="C26" s="11" t="s">
+      <c r="B26" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="C26" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="E26" s="11"/>
+      <c r="D26" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="E26" s="13"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D27" s="11" t="s">
-        <v>380</v>
-      </c>
-      <c r="E27" s="11"/>
+      <c r="D27" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="E27" s="13"/>
     </row>
     <row r="28" ht="78" customHeight="1" spans="2:5">
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="28" t="s">
-        <v>381</v>
-      </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
+      <c r="C28" s="30" t="s">
+        <v>382</v>
+      </c>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9147,216 +9224,216 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="17" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:5">
-      <c r="A2" s="22" t="s">
-        <v>382</v>
-      </c>
-      <c r="E2" s="23"/>
+      <c r="A2" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="E2" s="25"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="17"/>
-      <c r="B3" s="11" t="s">
+      <c r="A3" s="19"/>
+      <c r="B3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="E3" s="23"/>
+      <c r="C3" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="E3" s="25"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="17"/>
-      <c r="B4" s="18" t="s">
+      <c r="A4" s="19"/>
+      <c r="B4" s="20" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>383</v>
-      </c>
-      <c r="E4" s="23"/>
+        <v>384</v>
+      </c>
+      <c r="E4" s="25"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="17"/>
-      <c r="B5" s="19" t="s">
+      <c r="A5" s="19"/>
+      <c r="B5" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="23"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="25"/>
     </row>
     <row r="6" ht="30" spans="2:5">
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>384</v>
-      </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="23"/>
-    </row>
-    <row r="7" ht="150" spans="2:5">
-      <c r="B7" s="18" t="s">
+      <c r="C6" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="25"/>
+    </row>
+    <row r="7" ht="74.25" spans="2:5">
+      <c r="B7" s="20" t="s">
         <v>184</v>
       </c>
       <c r="C7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D7" t="s">
-        <v>341</v>
-      </c>
-      <c r="E7" s="9" t="s">
         <v>342</v>
       </c>
+      <c r="E7" s="10" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="8" spans="2:5">
-      <c r="B8" s="18" t="s">
-        <v>352</v>
+      <c r="B8" s="20" t="s">
+        <v>353</v>
       </c>
       <c r="C8" t="s">
-        <v>386</v>
-      </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="23"/>
+        <v>387</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="25"/>
     </row>
     <row r="9" ht="42.95" customHeight="1" spans="2:5">
-      <c r="B9" s="18" t="s">
-        <v>355</v>
+      <c r="B9" s="20" t="s">
+        <v>356</v>
       </c>
       <c r="C9" t="s">
-        <v>387</v>
-      </c>
-      <c r="D9" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="E9" s="23"/>
+      <c r="D9" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="E9" s="25"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="18" t="s">
-        <v>357</v>
-      </c>
-      <c r="C10" s="24" t="s">
+      <c r="B10" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="23"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="25"/>
     </row>
     <row r="11" ht="60.95" customHeight="1" spans="2:5">
-      <c r="B11" s="18" t="s">
-        <v>358</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>389</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="23"/>
+      <c r="B11" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="D11" s="13"/>
+      <c r="E11" s="25"/>
     </row>
     <row r="12" ht="30" spans="2:5">
-      <c r="B12" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="D12" s="11" t="s">
+      <c r="B12" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="E12" s="23"/>
+      <c r="D12" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="E12" s="25"/>
     </row>
     <row r="13" ht="30" spans="2:5">
-      <c r="B13" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>392</v>
-      </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="23"/>
+      <c r="B13" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="D13" s="13"/>
+      <c r="E13" s="25"/>
     </row>
     <row r="14" ht="78" customHeight="1" spans="2:5">
-      <c r="B14" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>393</v>
-      </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="23"/>
+      <c r="B14" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="D14" s="13"/>
+      <c r="E14" s="25"/>
     </row>
     <row r="15" ht="45" spans="2:5">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>394</v>
-      </c>
-      <c r="E15" s="23"/>
+      <c r="C15" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="E15" s="25"/>
     </row>
     <row r="16" spans="2:5">
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="E16" s="23"/>
+      <c r="E16" s="25"/>
     </row>
     <row r="17" ht="30" spans="2:5">
       <c r="B17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D17" t="s">
-        <v>373</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>396</v>
+        <v>374</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:5">
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="11" t="s">
-        <v>397</v>
-      </c>
-      <c r="E18" s="23"/>
+      <c r="D18" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="E18" s="25"/>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>381</v>
-      </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="23"/>
+      <c r="C19" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -9384,184 +9461,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="17" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="19" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>398</v>
+      <c r="C3" s="13" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="17"/>
-      <c r="B4" s="18" t="s">
+      <c r="A4" s="19"/>
+      <c r="B4" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="13" t="s">
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="17"/>
-      <c r="B5" s="19" t="s">
+      <c r="A5" s="19"/>
+      <c r="B5" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
     </row>
     <row r="6" ht="45" spans="2:5">
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>400</v>
-      </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
+      <c r="C6" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
     </row>
     <row r="7" spans="2:5">
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>401</v>
+      <c r="C7" s="13" t="s">
+        <v>402</v>
       </c>
       <c r="D7" t="s">
-        <v>402</v>
-      </c>
-      <c r="E7" s="20"/>
+        <v>403</v>
+      </c>
+      <c r="E7" s="22"/>
     </row>
     <row r="8" ht="165" spans="2:5">
-      <c r="B8" s="18" t="s">
-        <v>352</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>403</v>
-      </c>
-      <c r="D8" s="11" t="s">
+      <c r="B8" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="E8" s="21"/>
+      <c r="E8" s="23"/>
     </row>
     <row r="9" spans="2:3">
-      <c r="B9" s="18" t="s">
-        <v>355</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>404</v>
+      <c r="B9" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="2:3">
-      <c r="B10" s="18" t="s">
-        <v>357</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>405</v>
+      <c r="B10" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="B11" t="s">
-        <v>358</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>406</v>
+        <v>359</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="12" ht="90" spans="2:4">
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>407</v>
-      </c>
-      <c r="D12" s="11" t="s">
+      <c r="C12" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="D12" s="13" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="13" ht="45" spans="2:3">
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="13" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="14" ht="75" spans="2:4">
-      <c r="B14" s="18" t="s">
-        <v>368</v>
-      </c>
-      <c r="C14" s="11" t="s">
+      <c r="B14" s="20" t="s">
         <v>369</v>
       </c>
-      <c r="D14" s="11" t="s">
-        <v>408</v>
+      <c r="C14" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="15" ht="90" spans="2:4">
       <c r="B15" t="s">
-        <v>409</v>
-      </c>
-      <c r="C15" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="C15" s="13" t="s">
         <v>411</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="B16" t="s">
-        <v>412</v>
-      </c>
-      <c r="C16" s="11" t="s">
         <v>413</v>
       </c>
+      <c r="C16" s="13" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="17" customHeight="1" spans="2:4">
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>414</v>
+      <c r="D17" s="13" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="18" ht="30" spans="2:4">
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>415</v>
-      </c>
-      <c r="D18" s="11"/>
+      <c r="C18" s="13" t="s">
+        <v>416</v>
+      </c>
+      <c r="D18" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/support/specifications/hl7/HL7v2.to.FHIR.Conversion.Spec.xlsx
+++ b/support/specifications/hl7/HL7v2.to.FHIR.Conversion.Spec.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" firstSheet="1" activeTab="9"/>
+    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="753" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -848,15 +848,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>PID.11.7 -&gt; use Mapping</t>
     </r>
     <r>
@@ -869,10 +860,10 @@
       </rPr>
       <t xml:space="preserve">
 H, HP, HV -&gt; home
-WP -&gt; work
-TMP -&gt; temp
+WP, O -&gt; work
+TMP, C -&gt; temp
 BAD -&gt; old
-All Others -&gt; home</t>
+All Others (DIR, PUB, AS, EC, MC, PG) -&gt; home</t>
     </r>
   </si>
   <si>
@@ -902,15 +893,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>telecom -&gt; use Mapping</t>
     </r>
     <r>
@@ -926,8 +908,7 @@
 H, HP, HV, EC -&gt; home
 MC, PG -&gt; mobile
 TMP -&gt; temp
-BAD -&gt; old
-All others -&gt; home</t>
+BAD -&gt; old</t>
     </r>
   </si>
   <si>
@@ -3885,15 +3866,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>telecom -&gt; use Mapping</t>
     </r>
     <r>
@@ -3909,7 +3881,7 @@
 MC, PG -&gt; mobile
 TMP -&gt; temp
 BAD -&gt; old
-All others -&gt; work</t>
+All others (H, HP, HV, EC) -&gt; work</t>
     </r>
   </si>
   <si>
@@ -3931,15 +3903,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>ORC.22.7 -&gt; use Mapping</t>
     </r>
     <r>
@@ -3955,7 +3918,7 @@
 BA -&gt; billing
 TMP -&gt; temp
 BAD -&gt; old
-All Others -&gt; work</t>
+All Others (H, HP, HV, DIR, PUB, AS, EC, MC, PG) -&gt; work</t>
     </r>
   </si>
   <si>
@@ -4002,6 +3965,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10.5"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>OBX.11 → status Mapping</t>
     </r>
     <r>
@@ -4581,6 +4552,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10.5"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>OBX.11/OBR.25 → status Mapping</t>
     </r>
     <r>
@@ -5469,10 +5448,16 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -5487,13 +5472,7 @@
       <color indexed="8"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -5511,14 +5490,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color indexed="8"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -6324,7 +6303,7 @@
     <cellStyle name="Warning" xfId="59"/>
   </cellStyles>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{074BE817-8BFB-4996-A254-5BEA51FB84F7}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{5E6FBFC4-12AA-4B25-8E12-E7CF585DDB12}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -6593,11 +6572,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="11.8571428571429" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="11.8545454545455" defaultRowHeight="14.5" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="14.2857142857143" style="66" customWidth="1"/>
+    <col min="1" max="1" width="14.2818181818182" style="66" customWidth="1"/>
     <col min="2" max="2" width="47" customWidth="1"/>
-    <col min="3" max="3" width="123.571428571429" customWidth="1"/>
+    <col min="3" max="3" width="123.572727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6634,7 +6613,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="45" spans="1:3">
+    <row r="5" ht="43.5" spans="1:3">
       <c r="A5" s="62"/>
       <c r="B5" s="62" t="s">
         <v>7</v>
@@ -6676,15 +6655,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" style="2" customWidth="1"/>
-    <col min="2" max="2" width="33.5714285714286" style="2" customWidth="1"/>
-    <col min="3" max="3" width="49.6666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="56.552380952381" style="2" customWidth="1"/>
-    <col min="5" max="5" width="53.2857142857143" style="2" customWidth="1"/>
-    <col min="6" max="6" width="47.5714285714286" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.14285714285714" style="2"/>
+    <col min="1" max="1" width="14.7181818181818" style="2" customWidth="1"/>
+    <col min="2" max="2" width="33.5727272727273" style="2" customWidth="1"/>
+    <col min="3" max="3" width="49.6636363636364" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.5545454545455" style="2" customWidth="1"/>
+    <col min="5" max="5" width="53.2818181818182" style="2" customWidth="1"/>
+    <col min="6" max="6" width="47.5727272727273" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9.14545454545454" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -6750,7 +6729,7 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="30" spans="2:6">
+    <row r="6" s="2" customFormat="1" ht="29" spans="2:6">
       <c r="B6" s="7" t="s">
         <v>27</v>
       </c>
@@ -6776,7 +6755,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" ht="74.25" spans="2:5">
+    <row r="8" s="2" customFormat="1" ht="71.5" spans="2:5">
       <c r="B8" s="6" t="s">
         <v>184</v>
       </c>
@@ -6802,7 +6781,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="150" spans="2:5">
+    <row r="10" s="2" customFormat="1" ht="145" spans="2:5">
       <c r="B10" s="6" t="s">
         <v>353</v>
       </c>
@@ -6816,7 +6795,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="180" spans="2:5">
+    <row r="11" s="2" customFormat="1" ht="159.5" spans="2:5">
       <c r="B11" s="6" t="s">
         <v>356</v>
       </c>
@@ -6826,7 +6805,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" ht="150" spans="2:5">
+    <row r="12" s="2" customFormat="1" ht="145" spans="2:5">
       <c r="B12" s="6" t="s">
         <v>358</v>
       </c>
@@ -6836,7 +6815,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" ht="75" spans="2:4">
+    <row r="13" s="2" customFormat="1" ht="58" spans="2:4">
       <c r="B13" s="6" t="s">
         <v>251</v>
       </c>
@@ -6847,7 +6826,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" ht="30" spans="2:3">
+    <row r="14" s="2" customFormat="1" ht="29" spans="2:3">
       <c r="B14" s="6" t="s">
         <v>254</v>
       </c>
@@ -6855,7 +6834,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" ht="45" spans="2:4">
+    <row r="15" s="2" customFormat="1" ht="43.5" spans="2:4">
       <c r="B15" s="6" t="s">
         <v>369</v>
       </c>
@@ -6866,7 +6845,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" ht="30" spans="2:5">
+    <row r="16" s="2" customFormat="1" ht="29" spans="2:5">
       <c r="B16" s="6" t="s">
         <v>372</v>
       </c>
@@ -6880,7 +6859,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" ht="45" spans="2:4">
+    <row r="17" s="2" customFormat="1" ht="43.5" spans="2:4">
       <c r="B17" s="6" t="s">
         <v>434</v>
       </c>
@@ -6904,7 +6883,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" ht="165" spans="2:5">
+    <row r="19" s="2" customFormat="1" ht="159.5" spans="2:5">
       <c r="B19" s="2" t="s">
         <v>437</v>
       </c>
@@ -6949,12 +6928,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" style="62" customWidth="1"/>
-    <col min="2" max="2" width="28.2857142857143" style="62" customWidth="1"/>
-    <col min="3" max="3" width="62.7238095238095" style="62" customWidth="1"/>
-    <col min="4" max="4" width="54.5428571428571" style="62" customWidth="1"/>
+    <col min="1" max="1" width="14.7181818181818" style="62" customWidth="1"/>
+    <col min="2" max="2" width="28.2818181818182" style="62" customWidth="1"/>
+    <col min="3" max="3" width="62.7272727272727" style="62" customWidth="1"/>
+    <col min="4" max="4" width="54.5454545454545" style="62" customWidth="1"/>
     <col min="5" max="5" width="57" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7047,7 +7026,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" ht="30" spans="2:3">
+    <row r="10" ht="29" spans="2:3">
       <c r="B10" s="62" t="s">
         <v>35</v>
       </c>
@@ -7097,7 +7076,7 @@
       <c r="F17" s="50"/>
       <c r="G17" s="50"/>
     </row>
-    <row r="18" s="2" customFormat="1" ht="30" spans="2:5">
+    <row r="18" s="2" customFormat="1" spans="2:5">
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
@@ -7115,7 +7094,7 @@
       </c>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" s="2" customFormat="1" ht="30" spans="2:5">
+    <row r="20" s="2" customFormat="1" ht="29" spans="2:5">
       <c r="B20" s="5" t="s">
         <v>44</v>
       </c>
@@ -7156,14 +7135,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E65"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.1142857142857" customWidth="1"/>
-    <col min="2" max="2" width="39.1428571428571" style="13" customWidth="1"/>
-    <col min="3" max="3" width="61.5714285714286" style="13" customWidth="1"/>
-    <col min="4" max="4" width="66.8571428571429" style="13" customWidth="1"/>
-    <col min="5" max="5" width="64.5714285714286" style="13" customWidth="1"/>
-    <col min="6" max="256" width="11.8571428571429" customWidth="1"/>
+    <col min="1" max="1" width="13.1181818181818" customWidth="1"/>
+    <col min="2" max="2" width="39.1454545454545" style="13" customWidth="1"/>
+    <col min="3" max="3" width="61.5727272727273" style="13" customWidth="1"/>
+    <col min="4" max="4" width="66.8545454545455" style="13" customWidth="1"/>
+    <col min="5" max="5" width="64.5727272727273" style="13" customWidth="1"/>
+    <col min="6" max="256" width="11.8545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="19" customFormat="1" spans="1:5">
@@ -7221,7 +7200,7 @@
       </c>
       <c r="E5" s="25"/>
     </row>
-    <row r="6" ht="30" spans="2:5">
+    <row r="6" spans="2:5">
       <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
@@ -7230,7 +7209,7 @@
       </c>
       <c r="E6" s="25"/>
     </row>
-    <row r="7" ht="60" spans="2:5">
+    <row r="7" ht="58" spans="2:5">
       <c r="B7" s="13" t="s">
         <v>51</v>
       </c>
@@ -7244,7 +7223,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" ht="60" spans="2:5">
+    <row r="8" ht="58" spans="2:5">
       <c r="B8" s="13" t="s">
         <v>55</v>
       </c>
@@ -7301,7 +7280,7 @@
       </c>
       <c r="E12" s="25"/>
     </row>
-    <row r="13" ht="60" spans="2:5">
+    <row r="13" ht="58" spans="2:5">
       <c r="B13" s="13" t="s">
         <v>68</v>
       </c>
@@ -7313,7 +7292,7 @@
       </c>
       <c r="E13" s="25"/>
     </row>
-    <row r="14" ht="30" spans="2:5">
+    <row r="14" ht="29" spans="2:5">
       <c r="B14" s="13" t="s">
         <v>71</v>
       </c>
@@ -7349,7 +7328,7 @@
       </c>
       <c r="E16" s="25"/>
     </row>
-    <row r="17" ht="135" spans="2:5">
+    <row r="17" ht="130.5" spans="2:5">
       <c r="B17" s="13" t="s">
         <v>80</v>
       </c>
@@ -7406,7 +7385,7 @@
       </c>
       <c r="E22" s="25"/>
     </row>
-    <row r="23" ht="90" spans="2:5">
+    <row r="23" ht="87" spans="2:5">
       <c r="B23" s="13" t="s">
         <v>93</v>
       </c>
@@ -7438,7 +7417,7 @@
       </c>
       <c r="E25" s="25"/>
     </row>
-    <row r="26" ht="105" spans="2:5">
+    <row r="26" ht="87" spans="2:5">
       <c r="B26" s="13" t="s">
         <v>101</v>
       </c>
@@ -7449,7 +7428,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="27" ht="45" spans="2:5">
+    <row r="27" ht="29" spans="2:5">
       <c r="B27" s="29" t="s">
         <v>104</v>
       </c>
@@ -7463,7 +7442,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" ht="30" spans="2:5">
+    <row r="28" ht="29" spans="2:5">
       <c r="B28" s="29" t="s">
         <v>108</v>
       </c>
@@ -7473,7 +7452,7 @@
       <c r="D28" s="58"/>
       <c r="E28" s="59"/>
     </row>
-    <row r="29" ht="30" spans="2:5">
+    <row r="29" spans="2:5">
       <c r="B29" s="29" t="s">
         <v>110</v>
       </c>
@@ -7483,7 +7462,7 @@
       <c r="D29" s="58"/>
       <c r="E29" s="59"/>
     </row>
-    <row r="30" ht="30" spans="2:5">
+    <row r="30" ht="29" spans="2:5">
       <c r="B30" s="29" t="s">
         <v>112</v>
       </c>
@@ -7503,7 +7482,7 @@
       <c r="D31" s="58"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" ht="30" spans="2:5">
+    <row r="32" ht="29" spans="2:5">
       <c r="B32" s="29" t="s">
         <v>104</v>
       </c>
@@ -7517,7 +7496,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="33" ht="30" spans="2:5">
+    <row r="33" ht="29" spans="2:5">
       <c r="B33" s="29" t="s">
         <v>108</v>
       </c>
@@ -7527,7 +7506,7 @@
       <c r="D33" s="58"/>
       <c r="E33" s="59"/>
     </row>
-    <row r="34" ht="30" spans="2:5">
+    <row r="34" spans="2:5">
       <c r="B34" s="29" t="s">
         <v>110</v>
       </c>
@@ -7537,7 +7516,7 @@
       <c r="D34" s="58"/>
       <c r="E34" s="59"/>
     </row>
-    <row r="35" ht="30" spans="2:5">
+    <row r="35" ht="29" spans="2:5">
       <c r="B35" s="29" t="s">
         <v>112</v>
       </c>
@@ -7569,7 +7548,7 @@
       </c>
       <c r="E37" s="59"/>
     </row>
-    <row r="38" ht="45" spans="2:5">
+    <row r="38" ht="43.5" spans="2:5">
       <c r="B38" s="29" t="s">
         <v>123</v>
       </c>
@@ -7581,7 +7560,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="39" ht="135" spans="2:5">
+    <row r="39" ht="130.5" spans="2:5">
       <c r="B39" s="60" t="s">
         <v>126</v>
       </c>
@@ -7593,7 +7572,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="40" ht="135" spans="2:5">
+    <row r="40" ht="130.5" spans="2:5">
       <c r="B40" s="60" t="s">
         <v>129</v>
       </c>
@@ -7641,7 +7620,7 @@
       </c>
       <c r="E44" s="25"/>
     </row>
-    <row r="45" ht="195" spans="2:5">
+    <row r="45" ht="188.5" spans="2:5">
       <c r="B45" s="21" t="s">
         <v>138</v>
       </c>
@@ -7653,7 +7632,7 @@
       </c>
       <c r="E45" s="25"/>
     </row>
-    <row r="46" ht="195" spans="2:5">
+    <row r="46" ht="188.5" spans="2:5">
       <c r="B46" s="21" t="s">
         <v>141</v>
       </c>
@@ -7667,7 +7646,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="47" ht="195" spans="2:5">
+    <row r="47" ht="188.5" spans="2:5">
       <c r="B47" s="21" t="s">
         <v>145</v>
       </c>
@@ -7715,7 +7694,7 @@
       </c>
       <c r="E51" s="25"/>
     </row>
-    <row r="52" ht="150" spans="2:5">
+    <row r="52" ht="145" spans="2:5">
       <c r="B52" s="13" t="s">
         <v>154</v>
       </c>
@@ -7783,7 +7762,7 @@
       </c>
       <c r="E58" s="25"/>
     </row>
-    <row r="59" ht="180" spans="2:5">
+    <row r="59" ht="174" spans="2:5">
       <c r="B59" s="13" t="s">
         <v>168</v>
       </c>
@@ -7795,7 +7774,7 @@
       </c>
       <c r="E59" s="25"/>
     </row>
-    <row r="60" ht="255" spans="2:5">
+    <row r="60" ht="246.5" spans="2:5">
       <c r="B60" s="13" t="s">
         <v>171</v>
       </c>
@@ -7856,14 +7835,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.14285714285714" customWidth="1"/>
-    <col min="2" max="2" width="40.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="61.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="57.4285714285714" customWidth="1"/>
-    <col min="5" max="5" width="54.8571428571429" customWidth="1"/>
-    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
+    <col min="1" max="1" width="9.14545454545454" customWidth="1"/>
+    <col min="2" max="2" width="40.8545454545455" customWidth="1"/>
+    <col min="3" max="3" width="61.5727272727273" customWidth="1"/>
+    <col min="4" max="4" width="57.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="54.8545454545455" customWidth="1"/>
+    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7930,7 +7909,7 @@
       </c>
       <c r="E6" s="25"/>
     </row>
-    <row r="7" ht="45" spans="2:5">
+    <row r="7" ht="29" spans="2:5">
       <c r="B7" s="20" t="s">
         <v>184</v>
       </c>
@@ -7944,7 +7923,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="8" ht="135" spans="2:5">
+    <row r="8" ht="130.5" spans="2:5">
       <c r="B8" s="53" t="s">
         <v>188</v>
       </c>
@@ -7980,7 +7959,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="11" ht="225" spans="2:5">
+    <row r="11" ht="217.5" spans="2:5">
       <c r="B11" s="20" t="s">
         <v>197</v>
       </c>
@@ -8016,7 +7995,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="14" ht="30" spans="2:5">
+    <row r="14" ht="29" spans="2:5">
       <c r="B14" s="20" t="s">
         <v>204</v>
       </c>
@@ -8030,7 +8009,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="15" ht="135" spans="2:5">
+    <row r="15" ht="116" spans="2:5">
       <c r="B15" s="20" t="s">
         <v>208</v>
       </c>
@@ -8044,7 +8023,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="16" ht="45" spans="2:5">
+    <row r="16" ht="43.5" spans="2:5">
       <c r="B16" s="20" t="s">
         <v>212</v>
       </c>
@@ -8056,7 +8035,7 @@
       </c>
       <c r="E16" s="25"/>
     </row>
-    <row r="17" ht="60" spans="2:5">
+    <row r="17" ht="58" spans="2:5">
       <c r="B17" s="53" t="s">
         <v>215</v>
       </c>
@@ -8068,7 +8047,7 @@
       </c>
       <c r="E17" s="25"/>
     </row>
-    <row r="18" ht="60" spans="2:5">
+    <row r="18" ht="58" spans="2:5">
       <c r="B18" s="56" t="s">
         <v>218</v>
       </c>
@@ -8145,14 +8124,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="43.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="57.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
+    <col min="4" max="4" width="43.5727272727273" customWidth="1"/>
+    <col min="5" max="5" width="57.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -8211,7 +8190,7 @@
       <c r="D5" s="13"/>
       <c r="E5" s="25"/>
     </row>
-    <row r="6" ht="30" spans="2:5">
+    <row r="6" ht="29" spans="2:5">
       <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
@@ -8233,7 +8212,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" ht="75" spans="2:5">
+    <row r="8" ht="72.5" spans="2:5">
       <c r="B8" s="20" t="s">
         <v>232</v>
       </c>
@@ -8257,7 +8236,7 @@
       <c r="D9" s="13"/>
       <c r="E9" s="25"/>
     </row>
-    <row r="10" ht="75" spans="2:5">
+    <row r="10" ht="72.5" spans="2:5">
       <c r="B10" s="20" t="s">
         <v>238</v>
       </c>
@@ -8269,7 +8248,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="11" ht="120" spans="2:5">
+    <row r="11" ht="116" spans="2:5">
       <c r="B11" s="20" t="s">
         <v>241</v>
       </c>
@@ -8283,7 +8262,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="12" ht="60" spans="2:5">
+    <row r="12" ht="43.5" spans="2:5">
       <c r="B12" s="20" t="s">
         <v>245</v>
       </c>
@@ -8309,7 +8288,7 @@
       </c>
       <c r="E14" s="25"/>
     </row>
-    <row r="15" ht="75" spans="2:5">
+    <row r="15" ht="72.5" spans="2:5">
       <c r="B15" s="20" t="s">
         <v>251</v>
       </c>
@@ -8321,7 +8300,7 @@
       </c>
       <c r="E15" s="25"/>
     </row>
-    <row r="16" ht="30" spans="2:5">
+    <row r="16" ht="29" spans="2:5">
       <c r="B16" s="20" t="s">
         <v>254</v>
       </c>
@@ -8330,7 +8309,7 @@
       </c>
       <c r="E16" s="25"/>
     </row>
-    <row r="17" ht="60" spans="2:5">
+    <row r="17" ht="58" spans="2:5">
       <c r="B17" t="s">
         <v>256</v>
       </c>
@@ -8351,7 +8330,7 @@
       </c>
       <c r="E18" s="25"/>
     </row>
-    <row r="19" ht="30" spans="2:5">
+    <row r="19" ht="29" spans="2:5">
       <c r="B19" t="s">
         <v>261</v>
       </c>
@@ -8399,7 +8378,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="23" ht="30" spans="2:5">
+    <row r="23" ht="29" spans="2:5">
       <c r="B23" t="s">
         <v>271</v>
       </c>
@@ -8411,7 +8390,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="24" ht="75" spans="2:5">
+    <row r="24" ht="72.5" spans="2:5">
       <c r="B24" t="s">
         <v>273</v>
       </c>
@@ -8431,7 +8410,7 @@
       <c r="D25" s="13"/>
       <c r="E25" s="25"/>
     </row>
-    <row r="26" ht="60" spans="2:5">
+    <row r="26" ht="58" spans="2:5">
       <c r="B26" t="s">
         <v>277</v>
       </c>
@@ -8457,7 +8436,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="2:5">
+    <row r="28" ht="15" customHeight="1" spans="2:5">
       <c r="B28" s="13" t="s">
         <v>175</v>
       </c>
@@ -8469,7 +8448,7 @@
       </c>
       <c r="E28" s="25"/>
     </row>
-    <row r="29" ht="30" spans="2:5">
+    <row r="29" ht="29" spans="2:5">
       <c r="B29" s="13" t="s">
         <v>178</v>
       </c>
@@ -8494,15 +8473,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="19.4285714285714" style="31" customWidth="1"/>
+    <col min="1" max="1" width="19.4272727272727" style="31" customWidth="1"/>
     <col min="2" max="2" width="37" style="31" customWidth="1"/>
-    <col min="3" max="3" width="50.5714285714286" style="31" customWidth="1"/>
-    <col min="4" max="4" width="39.1428571428571" style="31" customWidth="1"/>
-    <col min="5" max="5" width="54.1428571428571" style="31" customWidth="1"/>
-    <col min="6" max="6" width="51.1428571428571" style="31" customWidth="1"/>
-    <col min="7" max="16384" width="9.14285714285714" style="31"/>
+    <col min="3" max="3" width="50.5727272727273" style="31" customWidth="1"/>
+    <col min="4" max="4" width="39.1454545454545" style="31" customWidth="1"/>
+    <col min="5" max="5" width="54.1454545454545" style="31" customWidth="1"/>
+    <col min="6" max="6" width="51.1454545454545" style="31" customWidth="1"/>
+    <col min="7" max="16384" width="9.14545454545454" style="31"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8560,7 +8539,7 @@
       <c r="D5" s="35"/>
       <c r="E5" s="34"/>
     </row>
-    <row r="6" ht="30" spans="2:5">
+    <row r="6" ht="29" spans="2:5">
       <c r="B6" s="35" t="s">
         <v>27</v>
       </c>
@@ -8570,7 +8549,7 @@
       <c r="D6" s="35"/>
       <c r="E6" s="34"/>
     </row>
-    <row r="7" ht="30" spans="2:6">
+    <row r="7" ht="29" spans="2:6">
       <c r="B7" s="36" t="s">
         <v>288</v>
       </c>
@@ -8583,7 +8562,7 @@
       </c>
       <c r="F7" s="38"/>
     </row>
-    <row r="8" ht="195" spans="2:5">
+    <row r="8" ht="188.5" spans="2:5">
       <c r="B8" s="31" t="s">
         <v>291</v>
       </c>
@@ -8617,7 +8596,7 @@
       <c r="D10" s="35"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" ht="30" spans="2:5">
+    <row r="11" spans="2:5">
       <c r="B11" s="35" t="s">
         <v>299</v>
       </c>
@@ -8627,7 +8606,7 @@
       <c r="D11" s="35"/>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" ht="30" spans="2:5">
+    <row r="12" spans="2:5">
       <c r="B12" s="35" t="s">
         <v>300</v>
       </c>
@@ -8637,7 +8616,7 @@
       <c r="D12" s="35"/>
       <c r="E12" s="34"/>
     </row>
-    <row r="13" ht="225" spans="2:5">
+    <row r="13" ht="217.5" spans="2:5">
       <c r="B13" s="31" t="s">
         <v>302</v>
       </c>
@@ -8671,7 +8650,7 @@
       <c r="D15" s="35"/>
       <c r="E15" s="34"/>
     </row>
-    <row r="16" ht="30" spans="2:5">
+    <row r="16" spans="2:5">
       <c r="B16" s="35" t="s">
         <v>310</v>
       </c>
@@ -8681,7 +8660,7 @@
       <c r="D16" s="35"/>
       <c r="E16" s="34"/>
     </row>
-    <row r="17" ht="30" spans="2:5">
+    <row r="17" spans="2:5">
       <c r="B17" s="35" t="s">
         <v>311</v>
       </c>
@@ -8691,7 +8670,7 @@
       <c r="D17" s="35"/>
       <c r="E17" s="34"/>
     </row>
-    <row r="18" ht="30" spans="2:5">
+    <row r="18" ht="29" spans="2:5">
       <c r="B18" s="41" t="s">
         <v>313</v>
       </c>
@@ -8705,7 +8684,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="19" ht="135" spans="2:5">
+    <row r="19" ht="130.5" spans="2:5">
       <c r="B19" s="37" t="s">
         <v>317</v>
       </c>
@@ -8717,7 +8696,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="20" ht="60" spans="2:5">
+    <row r="20" ht="58" spans="2:5">
       <c r="B20" s="35" t="s">
         <v>96</v>
       </c>
@@ -8729,7 +8708,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="21" ht="180" spans="2:5">
+    <row r="21" ht="174" spans="2:5">
       <c r="B21" s="35" t="s">
         <v>99</v>
       </c>
@@ -8741,7 +8720,7 @@
       </c>
       <c r="E21" s="34"/>
     </row>
-    <row r="22" ht="90" spans="2:6">
+    <row r="22" ht="87" spans="2:6">
       <c r="B22" s="35" t="s">
         <v>101</v>
       </c>
@@ -8754,7 +8733,7 @@
       </c>
       <c r="F22" s="47"/>
     </row>
-    <row r="23" ht="30" spans="2:5">
+    <row r="23" ht="29" spans="2:5">
       <c r="B23" s="35" t="s">
         <v>80</v>
       </c>
@@ -8766,7 +8745,7 @@
       </c>
       <c r="E23" s="34"/>
     </row>
-    <row r="24" ht="90" spans="2:6">
+    <row r="24" ht="87" spans="2:6">
       <c r="B24" s="35" t="s">
         <v>93</v>
       </c>
@@ -8779,7 +8758,7 @@
       </c>
       <c r="F24" s="47"/>
     </row>
-    <row r="25" ht="45" spans="2:5">
+    <row r="25" ht="43.5" spans="2:5">
       <c r="B25" s="35" t="s">
         <v>83</v>
       </c>
@@ -8829,7 +8808,7 @@
       <c r="D29" s="35"/>
       <c r="E29" s="34"/>
     </row>
-    <row r="30" customHeight="1" spans="2:5">
+    <row r="30" ht="15" customHeight="1" spans="2:5">
       <c r="B30" s="35" t="s">
         <v>175</v>
       </c>
@@ -8841,7 +8820,7 @@
       </c>
       <c r="E30" s="34"/>
     </row>
-    <row r="31" ht="30" spans="2:5">
+    <row r="31" ht="29" spans="2:5">
       <c r="B31" s="35" t="s">
         <v>178</v>
       </c>
@@ -8868,14 +8847,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.2190476190476" customWidth="1"/>
-    <col min="2" max="2" width="26.2857142857143" customWidth="1"/>
-    <col min="3" max="3" width="43.7142857142857" customWidth="1"/>
-    <col min="4" max="4" width="47.2857142857143" customWidth="1"/>
-    <col min="5" max="5" width="80.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
+    <col min="1" max="1" width="13.2181818181818" customWidth="1"/>
+    <col min="2" max="2" width="26.2818181818182" customWidth="1"/>
+    <col min="3" max="3" width="43.7181818181818" customWidth="1"/>
+    <col min="4" max="4" width="47.2818181818182" customWidth="1"/>
+    <col min="5" max="5" width="80.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -8931,7 +8910,7 @@
       </c>
       <c r="E5" s="13"/>
     </row>
-    <row r="6" ht="30" spans="2:5">
+    <row r="6" ht="29" spans="2:5">
       <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
@@ -8952,7 +8931,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="8" ht="74.25" spans="2:5">
+    <row r="8" ht="71.5" spans="2:5">
       <c r="B8" s="21" t="s">
         <v>184</v>
       </c>
@@ -8966,7 +8945,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="9" ht="120" spans="2:5">
+    <row r="9" ht="116" spans="2:5">
       <c r="B9" s="27" t="s">
         <v>344</v>
       </c>
@@ -8978,7 +8957,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="10" ht="45" spans="1:5">
+    <row r="10" ht="43.5" spans="1:5">
       <c r="A10" s="28"/>
       <c r="B10" s="6" t="s">
         <v>202</v>
@@ -8991,7 +8970,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="11" ht="210" spans="1:5">
+    <row r="11" ht="203" spans="1:5">
       <c r="A11" s="28"/>
       <c r="B11" s="6" t="s">
         <v>197</v>
@@ -9002,7 +8981,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="12" ht="210" spans="1:5">
+    <row r="12" ht="203" spans="1:5">
       <c r="A12" s="28"/>
       <c r="B12" s="6" t="s">
         <v>200</v>
@@ -9024,7 +9003,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="14" ht="150" spans="2:5">
+    <row r="14" ht="130.5" spans="2:5">
       <c r="B14" s="13" t="s">
         <v>353</v>
       </c>
@@ -9063,7 +9042,7 @@
       </c>
       <c r="E17" s="13"/>
     </row>
-    <row r="18" ht="105" spans="2:5">
+    <row r="18" ht="101.5" spans="2:5">
       <c r="B18" s="13" t="s">
         <v>361</v>
       </c>
@@ -9077,7 +9056,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="19" ht="30" spans="2:5">
+    <row r="19" ht="29" spans="2:5">
       <c r="B19" s="13" t="s">
         <v>365</v>
       </c>
@@ -9088,7 +9067,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="20" ht="30" spans="2:5">
+    <row r="20" ht="29" spans="2:5">
       <c r="B20" s="13" t="s">
         <v>366</v>
       </c>
@@ -9099,7 +9078,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="21" ht="75" spans="2:5">
+    <row r="21" ht="72.5" spans="2:5">
       <c r="B21" s="21" t="s">
         <v>251</v>
       </c>
@@ -9111,7 +9090,7 @@
       </c>
       <c r="E21" s="13"/>
     </row>
-    <row r="22" ht="30" spans="2:5">
+    <row r="22" ht="29" spans="2:5">
       <c r="B22" s="21" t="s">
         <v>254</v>
       </c>
@@ -9120,7 +9099,7 @@
       </c>
       <c r="E22" s="13"/>
     </row>
-    <row r="23" ht="45" spans="2:5">
+    <row r="23" ht="43.5" spans="2:5">
       <c r="B23" s="27" t="s">
         <v>369</v>
       </c>
@@ -9132,7 +9111,7 @@
       </c>
       <c r="E23" s="13"/>
     </row>
-    <row r="24" ht="30" spans="2:5">
+    <row r="24" spans="2:5">
       <c r="B24" s="21" t="s">
         <v>372</v>
       </c>
@@ -9146,7 +9125,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="25" ht="60" spans="2:5">
+    <row r="25" ht="58" spans="2:5">
       <c r="B25" s="13" t="s">
         <v>376</v>
       </c>
@@ -9158,7 +9137,7 @@
       </c>
       <c r="E25" s="13"/>
     </row>
-    <row r="26" ht="30" spans="2:5">
+    <row r="26" ht="29" spans="2:5">
       <c r="B26" s="13" t="s">
         <v>378</v>
       </c>
@@ -9213,14 +9192,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="22.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="22.2818181818182" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="70.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="47.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="49.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
+    <col min="3" max="3" width="70.2818181818182" customWidth="1"/>
+    <col min="4" max="4" width="47.1454545454545" customWidth="1"/>
+    <col min="5" max="5" width="49.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9240,7 +9219,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" ht="30" spans="1:5">
+    <row r="2" ht="29" spans="1:5">
       <c r="A2" s="24" t="s">
         <v>383</v>
       </c>
@@ -9280,7 +9259,7 @@
       <c r="D5" s="13"/>
       <c r="E5" s="25"/>
     </row>
-    <row r="6" ht="30" spans="2:5">
+    <row r="6" ht="29" spans="2:5">
       <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
@@ -9290,7 +9269,7 @@
       <c r="D6" s="13"/>
       <c r="E6" s="25"/>
     </row>
-    <row r="7" ht="74.25" spans="2:5">
+    <row r="7" ht="71.5" spans="2:5">
       <c r="B7" s="20" t="s">
         <v>184</v>
       </c>
@@ -9346,7 +9325,7 @@
       <c r="D11" s="13"/>
       <c r="E11" s="25"/>
     </row>
-    <row r="12" ht="30" spans="2:5">
+    <row r="12" ht="29" spans="2:5">
       <c r="B12" s="13" t="s">
         <v>361</v>
       </c>
@@ -9358,7 +9337,7 @@
       </c>
       <c r="E12" s="25"/>
     </row>
-    <row r="13" ht="30" spans="2:5">
+    <row r="13" ht="29" spans="2:5">
       <c r="B13" s="13" t="s">
         <v>365</v>
       </c>
@@ -9378,7 +9357,7 @@
       <c r="D14" s="13"/>
       <c r="E14" s="25"/>
     </row>
-    <row r="15" ht="45" spans="2:5">
+    <row r="15" ht="43.5" spans="2:5">
       <c r="B15" s="20" t="s">
         <v>251</v>
       </c>
@@ -9399,7 +9378,7 @@
       </c>
       <c r="E16" s="25"/>
     </row>
-    <row r="17" ht="30" spans="2:5">
+    <row r="17" ht="29" spans="2:5">
       <c r="B17" t="s">
         <v>372</v>
       </c>
@@ -9413,7 +9392,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="2:5">
+    <row r="18" ht="15" customHeight="1" spans="2:5">
       <c r="B18" s="13" t="s">
         <v>175</v>
       </c>
@@ -9450,14 +9429,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.14285714285714" customWidth="1"/>
-    <col min="2" max="2" width="23.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="34.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="25.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="33.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
+    <col min="1" max="1" width="9.14545454545454" customWidth="1"/>
+    <col min="2" max="2" width="23.1454545454545" customWidth="1"/>
+    <col min="3" max="3" width="34.2818181818182" customWidth="1"/>
+    <col min="4" max="4" width="25.1454545454545" customWidth="1"/>
+    <col min="5" max="5" width="33.4272727272727" customWidth="1"/>
+    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9513,7 +9492,7 @@
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
     </row>
-    <row r="6" ht="45" spans="2:5">
+    <row r="6" ht="29" spans="2:5">
       <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
@@ -9535,7 +9514,7 @@
       </c>
       <c r="E7" s="22"/>
     </row>
-    <row r="8" ht="165" spans="2:5">
+    <row r="8" ht="159.5" spans="2:5">
       <c r="B8" s="20" t="s">
         <v>353</v>
       </c>
@@ -9571,7 +9550,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="12" ht="90" spans="2:4">
+    <row r="12" ht="87" spans="2:4">
       <c r="B12" s="20" t="s">
         <v>251</v>
       </c>
@@ -9582,7 +9561,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="13" ht="45" spans="2:3">
+    <row r="13" ht="29" spans="2:3">
       <c r="B13" s="20" t="s">
         <v>254</v>
       </c>
@@ -9590,7 +9569,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="14" ht="75" spans="2:4">
+    <row r="14" ht="72.5" spans="2:4">
       <c r="B14" s="20" t="s">
         <v>369</v>
       </c>
@@ -9601,7 +9580,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="15" ht="90" spans="2:4">
+    <row r="15" ht="87" spans="2:4">
       <c r="B15" t="s">
         <v>410</v>
       </c>
@@ -9620,7 +9599,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="2:4">
+    <row r="17" ht="15" customHeight="1" spans="2:4">
       <c r="B17" s="13" t="s">
         <v>175</v>
       </c>
@@ -9631,7 +9610,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="18" ht="30" spans="2:4">
+    <row r="18" ht="29" spans="2:4">
       <c r="B18" s="13" t="s">
         <v>178</v>
       </c>

--- a/support/specifications/hl7/HL7v2.to.FHIR.Conversion.Spec.xlsx
+++ b/support/specifications/hl7/HL7v2.to.FHIR.Conversion.Spec.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8000" tabRatio="753" firstSheet="1" activeTab="5"/>
+    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="753" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="439">
   <si>
     <t>FHIR Resources</t>
   </si>
@@ -853,17 +853,17 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF00B050"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-H, HP, HV -&gt; home
-WP, O -&gt; work
-TMP, C -&gt; temp
-BAD -&gt; old
-All Others (DIR, PUB, AS, EC, MC, PG) -&gt; home</t>
+F, H, M, P, BDL -&gt; home
+B, O, S, SH, RH, TM -&gt; work
+V, C -&gt; temp
+BA -&gt; old
+All Others -&gt; home</t>
     </r>
   </si>
   <si>
@@ -889,27 +889,8 @@
     <t>telecom -&gt; use</t>
   </si>
   <si>
-    <t>PID.13.2, PID.14.2, PID.40.2</t>
-  </si>
-  <si>
-    <r>
-      <t>telecom -&gt; use Mapping</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-AS, DIR, PUB, WP -&gt; work
-H, HP, HV, EC -&gt; home
-MC, PG -&gt; mobile
-TMP -&gt; temp
-BAD -&gt; old</t>
-    </r>
+    <t>PID.13 -&gt; 'home'
+PID.14 and PID.40 -&gt; 'work'</t>
   </si>
   <si>
     <t>extension -&gt; extension -&gt; url</t>
@@ -3862,27 +3843,7 @@
     </r>
   </si>
   <si>
-    <t>ORC.23.2</t>
-  </si>
-  <si>
-    <r>
-      <t>telecom -&gt; use Mapping</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-AS, DIR, PUB, WP -&gt; work
-MC, PG -&gt; mobile
-TMP -&gt; temp
-BAD -&gt; old
-All others (H, HP, HV, EC) -&gt; work</t>
-    </r>
+    <t>"work"</t>
   </si>
   <si>
     <t>ORC.22.1 + OR.C22.2 + ORC.22.3 + ORC.22.4 + ORC.22.5 + ORC.22.6</t>
@@ -3908,17 +3869,17 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF00B050"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-WP -&gt; work
-BA -&gt; billing
-TMP -&gt; temp
-BAD -&gt; old
-All Others (H, HP, HV, DIR, PUB, AS, EC, MC, PG) -&gt; work</t>
+F, H, M, P, BDL -&gt; home
+B, O, S, SH, RH, TM -&gt; work
+V, C -&gt; temp
+BA -&gt; old
+All Others -&gt; work</t>
     </r>
   </si>
   <si>
@@ -5084,7 +5045,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="58">
+  <fonts count="59">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -5235,6 +5196,15 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5448,20 +5418,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -5470,6 +5433,21 @@
       <b/>
       <sz val="11"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -5488,19 +5466,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <u/>
+      <sz val="10"/>
       <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="40">
@@ -5865,151 +5835,148 @@
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
@@ -6018,17 +5985,20 @@
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6167,6 +6137,9 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -6176,7 +6149,10 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -6200,7 +6176,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -6303,7 +6279,7 @@
     <cellStyle name="Warning" xfId="59"/>
   </cellStyles>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{5E6FBFC4-12AA-4B25-8E12-E7CF585DDB12}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{E3B77C8E-14A8-4A8F-831C-BD0090FCDAAF}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -6572,68 +6548,68 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="11.8545454545455" defaultRowHeight="14.5" outlineLevelRow="7" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="11.8571428571429" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="14.2818181818182" style="66" customWidth="1"/>
+    <col min="1" max="1" width="14.2857142857143" style="68" customWidth="1"/>
     <col min="2" max="2" width="47" customWidth="1"/>
-    <col min="3" max="3" width="123.572727272727" customWidth="1"/>
+    <col min="3" max="3" width="123.571428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="62"/>
-      <c r="B2" s="62" t="s">
+      <c r="A2" s="64"/>
+      <c r="B2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="57" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="62"/>
-      <c r="B3" s="62" t="s">
+      <c r="A3" s="64"/>
+      <c r="B3" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="57" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="62"/>
-      <c r="B4" s="62" t="s">
+      <c r="A4" s="64"/>
+      <c r="B4" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="57" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="43.5" spans="1:3">
-      <c r="A5" s="62"/>
-      <c r="B5" s="62" t="s">
+    <row r="5" ht="45" spans="1:3">
+      <c r="A5" s="64"/>
+      <c r="B5" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="65" t="s">
+      <c r="C5" s="67" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="62"/>
-      <c r="B6" s="65" t="s">
+      <c r="A6" s="64"/>
+      <c r="B6" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="57" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="62"/>
-      <c r="B7" s="62" t="s">
+      <c r="A7" s="64"/>
+      <c r="B7" s="64" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="12" t="s">
@@ -6641,8 +6617,8 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="62"/>
-      <c r="B8" s="62"/>
+      <c r="A8" s="64"/>
+      <c r="B8" s="64"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1.39370078740157" bottom="1.39370078740157" header="1" footer="1"/>
@@ -6655,15 +6631,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" style="2" customWidth="1"/>
-    <col min="2" max="2" width="33.5727272727273" style="2" customWidth="1"/>
-    <col min="3" max="3" width="49.6636363636364" style="2" customWidth="1"/>
-    <col min="4" max="4" width="56.5545454545455" style="2" customWidth="1"/>
-    <col min="5" max="5" width="53.2818181818182" style="2" customWidth="1"/>
-    <col min="6" max="6" width="47.5727272727273" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.14545454545454" style="2"/>
+    <col min="1" max="1" width="14.7142857142857" style="2" customWidth="1"/>
+    <col min="2" max="2" width="33.5714285714286" style="2" customWidth="1"/>
+    <col min="3" max="3" width="49.6666666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.552380952381" style="2" customWidth="1"/>
+    <col min="5" max="5" width="53.2857142857143" style="2" customWidth="1"/>
+    <col min="6" max="6" width="47.5714285714286" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9.14285714285714" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -6674,16 +6650,16 @@
         <v>14</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="17" customHeight="1" spans="1:6">
@@ -6702,7 +6678,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:4">
@@ -6714,7 +6690,7 @@
         <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:6">
@@ -6729,12 +6705,12 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="29" spans="2:6">
+    <row r="6" s="2" customFormat="1" ht="30" spans="2:6">
       <c r="B6" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -6749,168 +6725,168 @@
         <v>53</v>
       </c>
       <c r="E7" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="74.25" spans="2:5">
+      <c r="B8" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="D8" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>422</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="71.5" spans="2:5">
-      <c r="B8" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="409" customHeight="1" spans="2:5">
       <c r="B9" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="150" spans="2:5">
+      <c r="B10" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="145" spans="2:5">
-      <c r="B10" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="E10" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="159.5" spans="2:5">
+    </row>
+    <row r="11" s="2" customFormat="1" ht="180" spans="2:5">
       <c r="B11" s="6" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="2"/>
       <c r="E11" s="11" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="145" spans="2:5">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="150" spans="2:5">
       <c r="B12" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="2"/>
       <c r="E12" s="11" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="75" spans="2:4">
+      <c r="B13" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" ht="30" spans="2:3">
+      <c r="B14" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" ht="45" spans="2:4">
+      <c r="B15" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" ht="58" spans="2:4">
-      <c r="B13" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="D13" s="5" t="s">
+    <row r="16" s="2" customFormat="1" ht="30" spans="2:5">
+      <c r="B16" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="45" spans="2:4">
+      <c r="B17" s="6" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="29" spans="2:3">
-      <c r="B14" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" ht="43.5" spans="2:4">
-      <c r="B15" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="D15" s="5" t="s">
+      <c r="C17" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>433</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="29" spans="2:5">
-      <c r="B16" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" ht="43.5" spans="2:4">
-      <c r="B17" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" spans="2:6">
       <c r="B18" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="15" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="165" spans="2:5">
+      <c r="B19" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="19" s="2" customFormat="1" ht="159.5" spans="2:5">
-      <c r="B19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="2:4">
       <c r="B20" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>176</v>
-      </c>
       <c r="D20" s="16" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" ht="46" customHeight="1" spans="2:4">
       <c r="B21" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D21" s="16"/>
     </row>
@@ -6928,26 +6904,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7181818181818" style="62" customWidth="1"/>
-    <col min="2" max="2" width="28.2818181818182" style="62" customWidth="1"/>
-    <col min="3" max="3" width="62.7272727272727" style="62" customWidth="1"/>
-    <col min="4" max="4" width="54.5454545454545" style="62" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" style="64" customWidth="1"/>
+    <col min="2" max="2" width="28.2857142857143" style="64" customWidth="1"/>
+    <col min="3" max="3" width="62.7238095238095" style="64" customWidth="1"/>
+    <col min="4" max="4" width="54.5428571428571" style="64" customWidth="1"/>
     <col min="5" max="5" width="57" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="63" t="s">
+      <c r="C1" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="63" t="s">
+      <c r="D1" s="65" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -6955,82 +6931,82 @@
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="66" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="64"/>
-      <c r="B3" s="62" t="s">
+      <c r="A3" s="66"/>
+      <c r="B3" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="C3" s="64" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="64"/>
-      <c r="B4" s="62" t="s">
+      <c r="A4" s="66"/>
+      <c r="B4" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="62" t="s">
+      <c r="D4" s="64" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" ht="61" customHeight="1" spans="2:4">
-      <c r="B5" s="62" t="s">
+      <c r="B5" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="62" t="s">
+      <c r="C5" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="65" t="s">
+      <c r="D5" s="67" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" ht="49" customHeight="1" spans="2:4">
-      <c r="B6" s="62" t="s">
+      <c r="B6" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="65"/>
+      <c r="D6" s="67"/>
     </row>
     <row r="7" ht="71" customHeight="1" spans="2:4">
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="65"/>
+      <c r="D7" s="67"/>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="62" t="s">
+      <c r="B8" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="62" t="s">
+      <c r="C8" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="65"/>
+      <c r="D8" s="67"/>
     </row>
     <row r="9" spans="2:3">
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="62" t="s">
+      <c r="C9" s="64" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" ht="29" spans="2:3">
-      <c r="B10" s="62" t="s">
+    <row r="10" ht="30" spans="2:3">
+      <c r="B10" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="65" t="s">
+      <c r="C10" s="67" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7070,13 +7046,13 @@
       <c r="C17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="50" t="s">
+      <c r="E17" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="2:5">
+      <c r="F17" s="52"/>
+      <c r="G17" s="52"/>
+    </row>
+    <row r="18" s="2" customFormat="1" ht="30" spans="2:5">
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
@@ -7094,7 +7070,7 @@
       </c>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" s="2" customFormat="1" ht="29" spans="2:5">
+    <row r="20" s="2" customFormat="1" ht="30" spans="2:5">
       <c r="B20" s="5" t="s">
         <v>44</v>
       </c>
@@ -7112,10 +7088,10 @@
       <c r="C22"/>
     </row>
     <row r="23" hidden="1" spans="2:3">
-      <c r="B23" s="62" t="s">
+      <c r="B23" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="65" t="s">
+      <c r="C23" s="67" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7135,14 +7111,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E65"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.1181818181818" customWidth="1"/>
-    <col min="2" max="2" width="39.1454545454545" style="13" customWidth="1"/>
-    <col min="3" max="3" width="61.5727272727273" style="13" customWidth="1"/>
-    <col min="4" max="4" width="66.8545454545455" style="13" customWidth="1"/>
-    <col min="5" max="5" width="64.5727272727273" style="13" customWidth="1"/>
-    <col min="6" max="256" width="11.8545454545455" customWidth="1"/>
+    <col min="1" max="1" width="13.1142857142857" customWidth="1"/>
+    <col min="2" max="2" width="39.1428571428571" style="13" customWidth="1"/>
+    <col min="3" max="3" width="61.5714285714286" style="13" customWidth="1"/>
+    <col min="4" max="4" width="66.8571428571429" style="13" customWidth="1"/>
+    <col min="5" max="5" width="64.5714285714286" style="13" customWidth="1"/>
+    <col min="6" max="256" width="11.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="19" customFormat="1" spans="1:5">
@@ -7200,7 +7176,7 @@
       </c>
       <c r="E5" s="25"/>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" ht="30" spans="2:5">
       <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
@@ -7209,7 +7185,7 @@
       </c>
       <c r="E6" s="25"/>
     </row>
-    <row r="7" ht="58" spans="2:5">
+    <row r="7" ht="60" spans="2:5">
       <c r="B7" s="13" t="s">
         <v>51</v>
       </c>
@@ -7219,11 +7195,11 @@
       <c r="D7" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="52" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" ht="58" spans="2:5">
+    <row r="8" ht="60" spans="2:5">
       <c r="B8" s="13" t="s">
         <v>55</v>
       </c>
@@ -7239,7 +7215,7 @@
       <c r="B9" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="57" t="s">
+      <c r="C9" s="59" t="s">
         <v>59</v>
       </c>
       <c r="E9" s="25"/>
@@ -7280,7 +7256,7 @@
       </c>
       <c r="E12" s="25"/>
     </row>
-    <row r="13" ht="58" spans="2:5">
+    <row r="13" ht="60" spans="2:5">
       <c r="B13" s="13" t="s">
         <v>68</v>
       </c>
@@ -7292,7 +7268,7 @@
       </c>
       <c r="E13" s="25"/>
     </row>
-    <row r="14" ht="29" spans="2:5">
+    <row r="14" ht="30" spans="2:5">
       <c r="B14" s="13" t="s">
         <v>71</v>
       </c>
@@ -7328,7 +7304,7 @@
       </c>
       <c r="E16" s="25"/>
     </row>
-    <row r="17" ht="130.5" spans="2:5">
+    <row r="17" ht="135" spans="2:5">
       <c r="B17" s="13" t="s">
         <v>80</v>
       </c>
@@ -7385,14 +7361,14 @@
       </c>
       <c r="E22" s="25"/>
     </row>
-    <row r="23" ht="87" spans="2:5">
+    <row r="23" ht="90" spans="2:5">
       <c r="B23" s="13" t="s">
         <v>93</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="46" t="s">
+      <c r="E23" s="50" t="s">
         <v>95</v>
       </c>
     </row>
@@ -7417,401 +7393,399 @@
       </c>
       <c r="E25" s="25"/>
     </row>
-    <row r="26" ht="87" spans="2:5">
+    <row r="26" ht="30" spans="2:5">
       <c r="B26" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="E26" s="46" t="s">
+      <c r="E26" s="47"/>
+    </row>
+    <row r="27" ht="45" spans="2:5">
+      <c r="B27" s="29" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="27" ht="29" spans="2:5">
-      <c r="B27" s="29" t="s">
+      <c r="C27" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="D27" s="60" t="s">
         <v>105</v>
       </c>
-      <c r="D27" s="58" t="s">
+      <c r="E27" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E27" s="8" t="s">
+    </row>
+    <row r="28" ht="30" spans="2:5">
+      <c r="B28" s="29" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="28" ht="29" spans="2:5">
-      <c r="B28" s="29" t="s">
+      <c r="C28" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="D28" s="60"/>
+      <c r="E28" s="61"/>
+    </row>
+    <row r="29" ht="30" spans="2:5">
+      <c r="B29" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="D28" s="58"/>
-      <c r="E28" s="59"/>
-    </row>
-    <row r="29" spans="2:5">
-      <c r="B29" s="29" t="s">
+      <c r="C29" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="D29" s="60"/>
+      <c r="E29" s="61"/>
+    </row>
+    <row r="30" ht="30" spans="2:5">
+      <c r="B30" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="D29" s="58"/>
-      <c r="E29" s="59"/>
-    </row>
-    <row r="30" ht="29" spans="2:5">
-      <c r="B30" s="29" t="s">
+      <c r="C30" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="C30" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="D30" s="58"/>
-      <c r="E30" s="59"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="61"/>
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="60"/>
+      <c r="E31" s="8"/>
+    </row>
+    <row r="32" ht="30" spans="2:5">
+      <c r="B32" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="60" t="s">
         <v>115</v>
       </c>
-      <c r="D31" s="58"/>
-      <c r="E31" s="8"/>
-    </row>
-    <row r="32" ht="29" spans="2:5">
-      <c r="B32" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D32" s="58" t="s">
+      <c r="E32" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="E32" s="8" t="s">
+    </row>
+    <row r="33" ht="30" spans="2:5">
+      <c r="B33" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="29" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="33" ht="29" spans="2:5">
-      <c r="B33" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="C33" s="29" t="s">
+      <c r="D33" s="60"/>
+      <c r="E33" s="61"/>
+    </row>
+    <row r="34" ht="30" spans="2:5">
+      <c r="B34" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="D33" s="58"/>
-      <c r="E33" s="59"/>
-    </row>
-    <row r="34" spans="2:5">
-      <c r="B34" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="C34" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="D34" s="58"/>
-      <c r="E34" s="59"/>
-    </row>
-    <row r="35" ht="29" spans="2:5">
+      <c r="D34" s="60"/>
+      <c r="E34" s="61"/>
+    </row>
+    <row r="35" ht="30" spans="2:5">
       <c r="B35" s="29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="D35" s="58"/>
-      <c r="E35" s="59"/>
+        <v>117</v>
+      </c>
+      <c r="D35" s="60"/>
+      <c r="E35" s="61"/>
     </row>
     <row r="36" spans="2:5">
       <c r="B36" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D36" s="58"/>
-      <c r="E36" s="59"/>
+        <v>119</v>
+      </c>
+      <c r="D36" s="60"/>
+      <c r="E36" s="61"/>
     </row>
     <row r="37" spans="2:5">
       <c r="B37" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C37" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D37" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="D37" s="58" t="s">
+      <c r="E37" s="61"/>
+    </row>
+    <row r="38" ht="45" spans="2:5">
+      <c r="B38" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="E37" s="59"/>
-    </row>
-    <row r="38" ht="43.5" spans="2:5">
-      <c r="B38" s="29" t="s">
+      <c r="C38" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="D38" s="60"/>
+      <c r="E38" s="69" t="s">
         <v>124</v>
       </c>
-      <c r="D38" s="58"/>
-      <c r="E38" s="67" t="s">
+    </row>
+    <row r="39" ht="135" spans="2:5">
+      <c r="B39" s="62" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="39" ht="130.5" spans="2:5">
-      <c r="B39" s="60" t="s">
+      <c r="C39" s="62"/>
+      <c r="D39" s="62" t="s">
         <v>126</v>
       </c>
-      <c r="C39" s="60"/>
-      <c r="D39" s="60" t="s">
+      <c r="E39" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="E39" s="25" t="s">
+    </row>
+    <row r="40" ht="135" spans="2:5">
+      <c r="B40" s="62" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="40" ht="130.5" spans="2:5">
-      <c r="B40" s="60" t="s">
+      <c r="C40" s="62"/>
+      <c r="D40" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="C40" s="60"/>
-      <c r="D40" s="60" t="s">
-        <v>130</v>
-      </c>
       <c r="E40" s="25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="2:5">
       <c r="B41" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>131</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>132</v>
       </c>
       <c r="E41" s="25"/>
     </row>
     <row r="42" spans="2:5">
       <c r="B42" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="C42" s="26" t="s">
         <v>133</v>
-      </c>
-      <c r="C42" s="26" t="s">
-        <v>134</v>
       </c>
       <c r="E42" s="25"/>
     </row>
     <row r="43" spans="2:5">
       <c r="B43" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C43" s="13" t="s">
         <v>135</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>136</v>
       </c>
       <c r="E43" s="25"/>
     </row>
     <row r="44" spans="2:5">
       <c r="B44" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E44" s="25"/>
+    </row>
+    <row r="45" ht="195" spans="2:5">
+      <c r="B45" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="C44" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E44" s="25"/>
-    </row>
-    <row r="45" ht="188.5" spans="2:5">
-      <c r="B45" s="21" t="s">
+      <c r="C45" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="D45" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="E45" s="25"/>
+    </row>
+    <row r="46" ht="195" spans="2:5">
+      <c r="B46" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="E45" s="25"/>
-    </row>
-    <row r="46" ht="188.5" spans="2:5">
-      <c r="B46" s="21" t="s">
+      <c r="C46" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="D46" s="57" t="s">
         <v>142</v>
       </c>
-      <c r="D46" s="55" t="s">
+      <c r="E46" s="52" t="s">
         <v>143</v>
       </c>
-      <c r="E46" s="50" t="s">
+    </row>
+    <row r="47" ht="195" spans="2:5">
+      <c r="B47" s="21" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="47" ht="188.5" spans="2:5">
-      <c r="B47" s="21" t="s">
+      <c r="C47" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="D47" s="13" t="s">
         <v>146</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>147</v>
       </c>
       <c r="E47" s="25"/>
     </row>
     <row r="48" spans="2:5">
       <c r="B48" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E48" s="25"/>
     </row>
     <row r="49" spans="2:5">
       <c r="B49" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="C49" s="26" t="s">
         <v>149</v>
-      </c>
-      <c r="C49" s="26" t="s">
-        <v>150</v>
       </c>
       <c r="E49" s="25"/>
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C50" s="13" t="s">
         <v>151</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>152</v>
       </c>
       <c r="E50" s="25"/>
     </row>
     <row r="51" spans="2:5">
       <c r="B51" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="E51" s="25"/>
+    </row>
+    <row r="52" ht="150" spans="2:5">
+      <c r="B52" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C51" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="E51" s="25"/>
-    </row>
-    <row r="52" ht="145" spans="2:5">
-      <c r="B52" s="13" t="s">
+      <c r="C52" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="D52" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="E52" s="8" t="s">
         <v>156</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="C53" s="26" t="s">
         <v>158</v>
-      </c>
-      <c r="C53" s="26" t="s">
-        <v>159</v>
       </c>
       <c r="E53" s="25"/>
     </row>
     <row r="54" spans="2:5">
       <c r="B54" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E54" s="25"/>
     </row>
     <row r="55" spans="2:5">
       <c r="B55" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="C55" s="26" t="s">
         <v>161</v>
-      </c>
-      <c r="C55" s="26" t="s">
-        <v>162</v>
       </c>
       <c r="E55" s="25"/>
     </row>
     <row r="56" spans="2:5">
       <c r="B56" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C56" s="13" t="s">
         <v>163</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>164</v>
       </c>
       <c r="E56" s="25"/>
     </row>
     <row r="57" spans="2:5">
       <c r="B57" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E57" s="25"/>
     </row>
     <row r="58" spans="2:5">
       <c r="B58" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C58" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="C58" s="26" t="s">
+      <c r="E58" s="25"/>
+    </row>
+    <row r="59" ht="180" spans="2:5">
+      <c r="B59" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="E58" s="25"/>
-    </row>
-    <row r="59" ht="174" spans="2:5">
-      <c r="B59" s="13" t="s">
+      <c r="C59" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="C59" s="26" t="s">
+      <c r="D59" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="D59" s="13" t="s">
+      <c r="E59" s="25"/>
+    </row>
+    <row r="60" ht="255" spans="2:5">
+      <c r="B60" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="E59" s="25"/>
-    </row>
-    <row r="60" ht="246.5" spans="2:5">
-      <c r="B60" s="13" t="s">
+      <c r="C60" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="D60" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="D60" s="13" t="s">
+      <c r="E60" s="25" t="s">
         <v>173</v>
-      </c>
-      <c r="E60" s="25" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="61" spans="2:5">
       <c r="B61" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C61" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C61" s="13" t="s">
+      <c r="D61" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="D61" s="61" t="s">
-        <v>177</v>
       </c>
       <c r="E61" s="25"/>
     </row>
     <row r="62" ht="42.95" customHeight="1" spans="2:5">
       <c r="B62" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C62" s="59" t="s">
         <v>178</v>
       </c>
-      <c r="C62" s="57" t="s">
-        <v>179</v>
-      </c>
-      <c r="D62" s="61"/>
+      <c r="D62" s="63"/>
       <c r="E62" s="25"/>
     </row>
     <row r="65" spans="3:3">
-      <c r="C65" s="57"/>
+      <c r="C65" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7835,14 +7809,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.14545454545454" customWidth="1"/>
-    <col min="2" max="2" width="40.8545454545455" customWidth="1"/>
-    <col min="3" max="3" width="61.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="57.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="54.8545454545455" customWidth="1"/>
-    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
+    <col min="1" max="1" width="9.14285714285714" customWidth="1"/>
+    <col min="2" max="2" width="40.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="61.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="57.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="54.8571428571429" customWidth="1"/>
+    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7866,19 +7840,19 @@
       <c r="A2" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
+      <c r="B2" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
     </row>
     <row r="3" spans="2:5">
       <c r="B3" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E3" s="25"/>
     </row>
@@ -7896,7 +7870,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E5" s="25"/>
     </row>
@@ -7905,206 +7879,206 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E6" s="25"/>
+    </row>
+    <row r="7" ht="45" spans="2:5">
+      <c r="B7" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="E6" s="25"/>
-    </row>
-    <row r="7" ht="29" spans="2:5">
-      <c r="B7" s="20" t="s">
+      <c r="C7" t="s">
         <v>184</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>185</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" s="54" t="s">
         <v>186</v>
       </c>
-      <c r="E7" s="52" t="s">
+    </row>
+    <row r="8" ht="135" spans="2:5">
+      <c r="B8" s="55" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="8" ht="130.5" spans="2:5">
-      <c r="B8" s="53" t="s">
+      <c r="C8" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="D8" s="56" t="s">
         <v>189</v>
       </c>
-      <c r="D8" s="54" t="s">
+      <c r="E8" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="E8" s="8" t="s">
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9" s="55" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="9" spans="2:5">
-      <c r="B9" s="53" t="s">
+      <c r="C9" s="28" t="s">
         <v>192</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>193</v>
       </c>
       <c r="D9" s="28"/>
       <c r="E9" s="25"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="53" t="s">
+      <c r="B10" s="55" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="28" t="s">
         <v>194</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>195</v>
       </c>
       <c r="D10" s="28"/>
       <c r="E10" s="25" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" ht="225" spans="2:5">
+      <c r="B11" s="20" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="11" ht="217.5" spans="2:5">
-      <c r="B11" s="20" t="s">
+      <c r="C11" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="D11" s="55" t="s">
-        <v>199</v>
-      </c>
       <c r="E11" s="25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="E12" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="E13" s="8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" ht="30" spans="2:5">
+      <c r="B14" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="14" ht="29" spans="2:5">
-      <c r="B14" s="20" t="s">
+      <c r="C14" t="s">
         <v>204</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>205</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="E14" s="25" t="s">
+    </row>
+    <row r="15" ht="135" spans="2:5">
+      <c r="B15" s="20" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="15" ht="116" spans="2:5">
-      <c r="B15" s="20" t="s">
+      <c r="C15" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="D15" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="E15" s="54" t="s">
         <v>210</v>
       </c>
-      <c r="E15" s="52" t="s">
+    </row>
+    <row r="16" ht="45" spans="2:5">
+      <c r="B16" s="20" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="16" ht="43.5" spans="2:5">
-      <c r="B16" s="20" t="s">
+      <c r="C16" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="E16" s="25"/>
+    </row>
+    <row r="17" ht="60" spans="2:5">
+      <c r="B17" s="55" t="s">
         <v>214</v>
       </c>
-      <c r="E16" s="25"/>
-    </row>
-    <row r="17" ht="58" spans="2:5">
-      <c r="B17" s="53" t="s">
+      <c r="C17" s="58" t="s">
         <v>215</v>
       </c>
-      <c r="C17" s="56" t="s">
+      <c r="D17" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="E17" s="25"/>
+    </row>
+    <row r="18" ht="60" spans="2:5">
+      <c r="B18" s="58" t="s">
         <v>217</v>
       </c>
-      <c r="E17" s="25"/>
-    </row>
-    <row r="18" ht="58" spans="2:5">
-      <c r="B18" s="56" t="s">
+      <c r="C18" s="58" t="s">
         <v>218</v>
       </c>
-      <c r="C18" s="56" t="s">
+      <c r="D18" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>220</v>
-      </c>
       <c r="E18" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="D19" s="29" t="s">
-        <v>223</v>
-      </c>
       <c r="E19" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>225</v>
       </c>
       <c r="D20" s="29"/>
       <c r="E20" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" ht="77" customHeight="1" spans="2:5">
       <c r="B21" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>176</v>
-      </c>
       <c r="D21" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E21" s="25"/>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="25"/>
@@ -8124,14 +8098,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="43.5727272727273" customWidth="1"/>
-    <col min="5" max="5" width="57.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
+    <col min="4" max="4" width="43.5714285714286" customWidth="1"/>
+    <col min="5" max="5" width="57.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -8162,7 +8136,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E3" s="25"/>
     </row>
@@ -8175,7 +8149,7 @@
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E4" s="25"/>
     </row>
@@ -8190,270 +8164,270 @@
       <c r="D5" s="13"/>
       <c r="E5" s="25"/>
     </row>
-    <row r="6" ht="29" spans="2:5">
+    <row r="6" ht="30" spans="2:5">
       <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="25"/>
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" ht="75" spans="2:5">
+      <c r="B8" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="8" ht="72.5" spans="2:5">
-      <c r="B8" s="20" t="s">
+      <c r="C8" s="51" t="s">
         <v>232</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="D8" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="E8" s="70" t="s">
         <v>234</v>
-      </c>
-      <c r="E8" s="68" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="C9" s="51" t="s">
         <v>236</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>237</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="25"/>
     </row>
-    <row r="10" ht="72.5" spans="2:5">
+    <row r="10" ht="75" spans="2:5">
       <c r="B10" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="C10" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="D10" s="13"/>
+      <c r="E10" s="70" t="s">
         <v>239</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="68" t="s">
+    </row>
+    <row r="11" ht="120" spans="2:5">
+      <c r="B11" s="20" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="11" ht="116" spans="2:5">
-      <c r="B11" s="20" t="s">
+      <c r="C11" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="D11" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="E11" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="E11" s="50" t="s">
+    </row>
+    <row r="12" ht="60" spans="2:5">
+      <c r="B12" s="20" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="12" ht="43.5" spans="2:5">
-      <c r="B12" s="20" t="s">
+      <c r="E12" s="47" t="s">
         <v>245</v>
-      </c>
-      <c r="E12" s="46" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>247</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>248</v>
       </c>
       <c r="E13" s="25"/>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" t="s">
+        <v>248</v>
+      </c>
+      <c r="C14" t="s">
         <v>249</v>
       </c>
-      <c r="C14" t="s">
+      <c r="E14" s="25"/>
+    </row>
+    <row r="15" ht="75" spans="2:5">
+      <c r="B15" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="E14" s="25"/>
-    </row>
-    <row r="15" ht="72.5" spans="2:5">
-      <c r="B15" s="20" t="s">
+      <c r="C15" t="s">
         <v>251</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="E15" s="25"/>
+    </row>
+    <row r="16" ht="30" spans="2:5">
+      <c r="B16" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="E15" s="25"/>
-    </row>
-    <row r="16" ht="29" spans="2:5">
-      <c r="B16" s="20" t="s">
+      <c r="C16" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="E16" s="25"/>
+    </row>
+    <row r="17" ht="60" spans="2:5">
+      <c r="B17" t="s">
         <v>255</v>
       </c>
-      <c r="E16" s="25"/>
-    </row>
-    <row r="17" ht="58" spans="2:5">
-      <c r="B17" t="s">
+      <c r="C17" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="D17" s="13" t="s">
         <v>257</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>258</v>
       </c>
       <c r="E17" s="25"/>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" t="s">
+        <v>258</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="E18" s="25"/>
+    </row>
+    <row r="19" ht="30" spans="2:5">
+      <c r="B19" t="s">
         <v>260</v>
       </c>
-      <c r="E18" s="25"/>
-    </row>
-    <row r="19" ht="29" spans="2:5">
-      <c r="B19" t="s">
+      <c r="C19" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="D19" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="E19" s="25" t="s">
         <v>263</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" t="s">
+        <v>264</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>265</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>266</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="25" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" t="s">
+        <v>267</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>268</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>269</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="25" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="25" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="23" ht="29" spans="2:5">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="23" ht="30" spans="2:5">
       <c r="B23" t="s">
+        <v>270</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>271</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>272</v>
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="25" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="24" ht="72.5" spans="2:5">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="24" ht="75" spans="2:5">
       <c r="B24" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E24" s="25"/>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" t="s">
+        <v>274</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>275</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>276</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="25"/>
     </row>
-    <row r="26" ht="58" spans="2:5">
+    <row r="26" ht="60" spans="2:5">
       <c r="B26" t="s">
+        <v>276</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="D26" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="E26" s="25" t="s">
         <v>279</v>
-      </c>
-      <c r="E26" s="25" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" t="s">
+        <v>280</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>281</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>282</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="25" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" spans="2:5">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="2:5">
       <c r="B28" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>176</v>
-      </c>
       <c r="D28" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E28" s="25"/>
+    </row>
+    <row r="29" ht="30" spans="2:5">
+      <c r="B29" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>283</v>
-      </c>
-      <c r="E28" s="25"/>
-    </row>
-    <row r="29" ht="29" spans="2:5">
-      <c r="B29" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>284</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="25"/>
@@ -8473,15 +8447,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="19.4272727272727" style="31" customWidth="1"/>
+    <col min="1" max="1" width="19.4285714285714" style="31" customWidth="1"/>
     <col min="2" max="2" width="37" style="31" customWidth="1"/>
-    <col min="3" max="3" width="50.5727272727273" style="31" customWidth="1"/>
-    <col min="4" max="4" width="39.1454545454545" style="31" customWidth="1"/>
-    <col min="5" max="5" width="54.1454545454545" style="31" customWidth="1"/>
-    <col min="6" max="6" width="51.1454545454545" style="31" customWidth="1"/>
-    <col min="7" max="16384" width="9.14545454545454" style="31"/>
+    <col min="3" max="3" width="50.5714285714286" style="31" customWidth="1"/>
+    <col min="4" max="4" width="39.1428571428571" style="31" customWidth="1"/>
+    <col min="5" max="5" width="54.1428571428571" style="31" customWidth="1"/>
+    <col min="6" max="6" width="51.1428571428571" style="31" customWidth="1"/>
+    <col min="7" max="16384" width="9.14285714285714" style="31"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8501,7 +8475,7 @@
         <v>17</v>
       </c>
       <c r="F1" s="33" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8515,7 +8489,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E3" s="34"/>
     </row>
@@ -8539,231 +8513,228 @@
       <c r="D5" s="35"/>
       <c r="E5" s="34"/>
     </row>
-    <row r="6" ht="29" spans="2:5">
+    <row r="6" ht="30" spans="2:5">
       <c r="B6" s="35" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D6" s="35"/>
       <c r="E6" s="34"/>
     </row>
-    <row r="7" ht="29" spans="2:6">
+    <row r="7" ht="30" spans="2:6">
       <c r="B7" s="36" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C7" s="37"/>
       <c r="D7" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="F7" s="38"/>
+    </row>
+    <row r="8" ht="195" spans="2:5">
+      <c r="B8" s="31" t="s">
         <v>290</v>
       </c>
-      <c r="F7" s="38"/>
-    </row>
-    <row r="8" ht="188.5" spans="2:5">
-      <c r="B8" s="31" t="s">
+      <c r="C8" s="39" t="s">
         <v>291</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="D8" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="E8" s="14" t="s">
         <v>293</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>295</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>296</v>
       </c>
       <c r="D9" s="35"/>
       <c r="E9" s="34"/>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="35" t="s">
+        <v>296</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>297</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>298</v>
       </c>
       <c r="D10" s="35"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="2:5">
+    <row r="11" ht="30" spans="2:5">
       <c r="B11" s="35" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="2:5">
+    <row r="12" ht="30" spans="2:5">
       <c r="B12" s="35" t="s">
+        <v>299</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>300</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>301</v>
       </c>
       <c r="D12" s="35"/>
       <c r="E12" s="34"/>
     </row>
-    <row r="13" ht="217.5" spans="2:5">
+    <row r="13" ht="225" spans="2:5">
       <c r="B13" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="C13" s="39" t="s">
         <v>302</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="D13" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="D13" s="35" t="s">
+      <c r="E13" s="40" t="s">
         <v>304</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>306</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>307</v>
       </c>
       <c r="D14" s="35"/>
       <c r="E14" s="34"/>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="35" t="s">
+        <v>307</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>308</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>309</v>
       </c>
       <c r="D15" s="35"/>
       <c r="E15" s="34"/>
     </row>
-    <row r="16" spans="2:5">
+    <row r="16" ht="30" spans="2:5">
       <c r="B16" s="35" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D16" s="35"/>
       <c r="E16" s="34"/>
     </row>
-    <row r="17" spans="2:5">
+    <row r="17" ht="30" spans="2:5">
       <c r="B17" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>311</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>312</v>
       </c>
       <c r="D17" s="35"/>
       <c r="E17" s="34"/>
     </row>
-    <row r="18" ht="29" spans="2:5">
+    <row r="18" ht="30" spans="2:5">
       <c r="B18" s="41" t="s">
+        <v>312</v>
+      </c>
+      <c r="C18" s="42" t="s">
         <v>313</v>
       </c>
-      <c r="C18" s="42" t="s">
+      <c r="D18" s="35" t="s">
         <v>314</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="E18" s="40" t="s">
         <v>315</v>
       </c>
-      <c r="E18" s="40" t="s">
+    </row>
+    <row r="19" ht="135" spans="2:5">
+      <c r="B19" s="37" t="s">
         <v>316</v>
-      </c>
-    </row>
-    <row r="19" ht="130.5" spans="2:5">
-      <c r="B19" s="37" t="s">
-        <v>317</v>
       </c>
       <c r="C19" s="43"/>
       <c r="D19" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="E19" s="34" t="s">
         <v>318</v>
       </c>
-      <c r="E19" s="34" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="20" ht="58" spans="2:5">
+    </row>
+    <row r="20" ht="60" spans="2:5">
       <c r="B20" s="35" t="s">
         <v>96</v>
       </c>
       <c r="C20" s="45" t="s">
+        <v>319</v>
+      </c>
+      <c r="D20" s="35"/>
+      <c r="E20" s="71" t="s">
         <v>320</v>
       </c>
-      <c r="D20" s="35"/>
-      <c r="E20" s="69" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="21" ht="174" spans="2:5">
+    </row>
+    <row r="21" ht="180" spans="2:5">
       <c r="B21" s="35" t="s">
         <v>99</v>
       </c>
       <c r="C21" s="45" t="s">
+        <v>321</v>
+      </c>
+      <c r="D21" s="35" t="s">
         <v>322</v>
       </c>
-      <c r="D21" s="35" t="s">
-        <v>323</v>
-      </c>
       <c r="E21" s="34"/>
     </row>
-    <row r="22" ht="87" spans="2:6">
+    <row r="22" spans="2:6">
       <c r="B22" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="45" t="s">
-        <v>324</v>
+      <c r="C22" s="46" t="s">
+        <v>323</v>
       </c>
       <c r="D22" s="35"/>
-      <c r="E22" s="46" t="s">
-        <v>325</v>
-      </c>
-      <c r="F22" s="47"/>
-    </row>
-    <row r="23" ht="29" spans="2:5">
+      <c r="E22" s="47"/>
+      <c r="F22" s="48"/>
+    </row>
+    <row r="23" ht="30" spans="2:5">
       <c r="B23" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="48" t="s">
-        <v>326</v>
+      <c r="C23" s="49" t="s">
+        <v>324</v>
       </c>
       <c r="D23" s="35" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E23" s="34"/>
     </row>
-    <row r="24" ht="87" spans="2:6">
+    <row r="24" ht="90" spans="2:5">
       <c r="B24" s="35" t="s">
         <v>93</v>
       </c>
       <c r="C24" s="45" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D24" s="35"/>
-      <c r="E24" s="46" t="s">
-        <v>329</v>
-      </c>
-      <c r="F24" s="47"/>
-    </row>
-    <row r="25" ht="43.5" spans="2:5">
+      <c r="E24" s="50" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="25" ht="45" spans="2:5">
       <c r="B25" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="48" t="s">
-        <v>330</v>
+      <c r="C25" s="49" t="s">
+        <v>328</v>
       </c>
       <c r="D25" s="35"/>
       <c r="E25" s="34"/>
@@ -8773,7 +8744,7 @@
         <v>85</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D26" s="35"/>
       <c r="E26" s="34"/>
@@ -8783,7 +8754,7 @@
         <v>87</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D27" s="35"/>
       <c r="E27" s="34"/>
@@ -8793,7 +8764,7 @@
         <v>89</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D28" s="35"/>
       <c r="E28" s="34"/>
@@ -8803,29 +8774,29 @@
         <v>91</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D29" s="35"/>
       <c r="E29" s="34"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="2:5">
+    <row r="30" customHeight="1" spans="2:5">
       <c r="B30" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="C30" s="45" t="s">
         <v>175</v>
       </c>
-      <c r="C30" s="45" t="s">
-        <v>176</v>
-      </c>
       <c r="D30" s="35" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E30" s="34"/>
     </row>
-    <row r="31" ht="29" spans="2:5">
+    <row r="31" ht="30" spans="2:5">
       <c r="B31" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="C31" s="48" t="s">
-        <v>336</v>
+        <v>177</v>
+      </c>
+      <c r="C31" s="49" t="s">
+        <v>334</v>
       </c>
       <c r="D31" s="35"/>
       <c r="E31" s="34"/>
@@ -8835,9 +8806,6 @@
     <mergeCell ref="D23:D29"/>
     <mergeCell ref="D30:D31"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="C22" r:id="rId1" display="ORC.23.2" tooltip="https://hl7-definition.caristix.com/v2/HL7v2.7.1/Fields/ORC.23.2"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
@@ -8847,14 +8815,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.2181818181818" customWidth="1"/>
-    <col min="2" max="2" width="26.2818181818182" customWidth="1"/>
-    <col min="3" max="3" width="43.7181818181818" customWidth="1"/>
-    <col min="4" max="4" width="47.2818181818182" customWidth="1"/>
-    <col min="5" max="5" width="80.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
+    <col min="1" max="1" width="13.2190476190476" customWidth="1"/>
+    <col min="2" max="2" width="26.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="43.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="47.2857142857143" customWidth="1"/>
+    <col min="5" max="5" width="80.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -8885,7 +8853,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E3" s="13"/>
     </row>
@@ -8897,7 +8865,7 @@
         <v>22</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E4" s="13"/>
     </row>
@@ -8910,12 +8878,12 @@
       </c>
       <c r="E5" s="13"/>
     </row>
-    <row r="6" ht="29" spans="2:5">
+    <row r="6" ht="30" spans="2:5">
       <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E6" s="13"/>
     </row>
@@ -8928,245 +8896,245 @@
         <v>53</v>
       </c>
       <c r="E7" s="22" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="8" ht="74.25" spans="2:5">
+      <c r="B8" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="8" ht="71.5" spans="2:5">
-      <c r="B8" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="C8" s="13" t="s">
+      <c r="E8" s="10" t="s">
         <v>341</v>
       </c>
-      <c r="D8" s="13" t="s">
+    </row>
+    <row r="9" ht="120" spans="2:5">
+      <c r="B9" s="27" t="s">
         <v>342</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="9" ht="116" spans="2:5">
-      <c r="B9" s="27" t="s">
-        <v>344</v>
       </c>
       <c r="C9" s="28"/>
       <c r="D9" s="29" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="10" ht="43.5" spans="1:5">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="10" ht="45" spans="1:5">
       <c r="A10" s="28"/>
       <c r="B10" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D10" s="29"/>
       <c r="E10" s="8" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="11" ht="203" spans="1:5">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="11" ht="210" spans="1:5">
       <c r="A11" s="28"/>
       <c r="B11" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="29"/>
       <c r="E11" s="11" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="12" ht="203" spans="1:5">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="12" ht="210" spans="1:5">
       <c r="A12" s="28"/>
       <c r="B12" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="29"/>
       <c r="E12" s="11" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="28"/>
       <c r="B13" s="6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="29"/>
       <c r="E13" s="8" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="14" ht="150" spans="2:5">
+      <c r="B14" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="14" ht="130.5" spans="2:5">
-      <c r="B14" s="13" t="s">
+      <c r="D14" s="13" t="s">
         <v>353</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>354</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>355</v>
       </c>
       <c r="E14" s="13"/>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="21" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E15" s="13"/>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="21" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E16" s="13"/>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="E17" s="13"/>
+    </row>
+    <row r="18" ht="105" spans="2:5">
+      <c r="B18" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C18" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="E17" s="13"/>
-    </row>
-    <row r="18" ht="101.5" spans="2:5">
-      <c r="B18" s="13" t="s">
+      <c r="D18" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="E18" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="D18" s="13" t="s">
+    </row>
+    <row r="19" ht="30" spans="2:5">
+      <c r="B19" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="C19" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="20" ht="30" spans="2:5">
+      <c r="B20" s="13" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="19" ht="29" spans="2:5">
-      <c r="B19" s="13" t="s">
+      <c r="C20" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="21" ht="75" spans="2:5">
+      <c r="B21" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>365</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>362</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="20" ht="29" spans="2:5">
-      <c r="B20" s="13" t="s">
+      <c r="D21" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>362</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="21" ht="72.5" spans="2:5">
-      <c r="B21" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="C21" s="12" t="s">
+      <c r="E21" s="13"/>
+    </row>
+    <row r="22" ht="30" spans="2:5">
+      <c r="B22" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="E22" s="13"/>
+    </row>
+    <row r="23" ht="45" spans="2:5">
+      <c r="B23" s="27" t="s">
         <v>367</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="C23" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="E21" s="13"/>
-    </row>
-    <row r="22" ht="29" spans="2:5">
-      <c r="B22" s="21" t="s">
-        <v>254</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="E22" s="13"/>
-    </row>
-    <row r="23" ht="43.5" spans="2:5">
-      <c r="B23" s="27" t="s">
+      <c r="D23" s="29" t="s">
         <v>369</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="E23" s="13"/>
+    </row>
+    <row r="24" ht="30" spans="2:5">
+      <c r="B24" s="21" t="s">
         <v>370</v>
       </c>
-      <c r="D23" s="29" t="s">
+      <c r="C24" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="E23" s="13"/>
-    </row>
-    <row r="24" spans="2:5">
-      <c r="B24" s="21" t="s">
+      <c r="D24" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="E24" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="D24" s="13" t="s">
+    </row>
+    <row r="25" ht="60" spans="2:5">
+      <c r="B25" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="C25" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D25" s="13" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="25" ht="58" spans="2:5">
-      <c r="B25" s="13" t="s">
+      <c r="E25" s="13"/>
+    </row>
+    <row r="26" ht="30" spans="2:5">
+      <c r="B26" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="D25" s="13" t="s">
+      <c r="C26" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="E25" s="13"/>
-    </row>
-    <row r="26" ht="29" spans="2:5">
-      <c r="B26" s="13" t="s">
+      <c r="D26" s="13" t="s">
         <v>378</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>379</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>380</v>
       </c>
       <c r="E26" s="13"/>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>176</v>
-      </c>
       <c r="D27" s="13" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E27" s="13"/>
     </row>
     <row r="28" ht="78" customHeight="1" spans="2:5">
       <c r="B28" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
@@ -9192,14 +9160,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="22.2818181818182" customWidth="1"/>
+    <col min="1" max="1" width="22.2857142857143" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="70.2818181818182" customWidth="1"/>
-    <col min="4" max="4" width="47.1454545454545" customWidth="1"/>
-    <col min="5" max="5" width="49.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
+    <col min="3" max="3" width="70.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="47.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="49.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9219,9 +9187,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" ht="29" spans="1:5">
+    <row r="2" ht="30" spans="1:5">
       <c r="A2" s="24" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E2" s="25"/>
     </row>
@@ -9231,7 +9199,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E3" s="25"/>
     </row>
@@ -9244,7 +9212,7 @@
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E4" s="25"/>
     </row>
@@ -9259,157 +9227,157 @@
       <c r="D5" s="13"/>
       <c r="E5" s="25"/>
     </row>
-    <row r="6" ht="29" spans="2:5">
+    <row r="6" ht="30" spans="2:5">
       <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="25"/>
     </row>
-    <row r="7" ht="71.5" spans="2:5">
+    <row r="7" ht="74.25" spans="2:5">
       <c r="B7" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="B8" s="20" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C8" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="25"/>
     </row>
     <row r="9" ht="42.95" customHeight="1" spans="2:5">
       <c r="B9" s="20" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C9" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E9" s="25"/>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="20" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="25"/>
     </row>
     <row r="11" ht="60.95" customHeight="1" spans="2:5">
       <c r="B11" s="20" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="25"/>
     </row>
-    <row r="12" ht="29" spans="2:5">
+    <row r="12" ht="30" spans="2:5">
       <c r="B12" s="13" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C12" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="E12" s="25"/>
+    </row>
+    <row r="13" ht="30" spans="2:5">
+      <c r="B13" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>391</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="E12" s="25"/>
-    </row>
-    <row r="13" ht="29" spans="2:5">
-      <c r="B13" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>393</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="25"/>
     </row>
     <row r="14" ht="78" customHeight="1" spans="2:5">
       <c r="B14" s="13" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="25"/>
     </row>
-    <row r="15" ht="43.5" spans="2:5">
+    <row r="15" ht="45" spans="2:5">
       <c r="B15" s="20" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E15" s="25"/>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>255</v>
-      </c>
       <c r="E16" s="25"/>
     </row>
-    <row r="17" ht="29" spans="2:5">
+    <row r="17" ht="30" spans="2:5">
       <c r="B17" t="s">
+        <v>370</v>
+      </c>
+      <c r="C17" t="s">
+        <v>394</v>
+      </c>
+      <c r="D17" t="s">
         <v>372</v>
       </c>
-      <c r="C17" t="s">
+      <c r="E17" s="25" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="2:5">
+      <c r="B18" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="D18" s="13" t="s">
         <v>396</v>
-      </c>
-      <c r="D17" t="s">
-        <v>374</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" spans="2:5">
-      <c r="B18" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>398</v>
       </c>
       <c r="E18" s="25"/>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="25"/>
@@ -9429,14 +9397,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultColWidth="9.14545454545454" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.14545454545454" customWidth="1"/>
-    <col min="2" max="2" width="23.1454545454545" customWidth="1"/>
-    <col min="3" max="3" width="34.2818181818182" customWidth="1"/>
-    <col min="4" max="4" width="25.1454545454545" customWidth="1"/>
-    <col min="5" max="5" width="33.4272727272727" customWidth="1"/>
-    <col min="6" max="6" width="9.14545454545454" customWidth="1"/>
+    <col min="1" max="1" width="9.14285714285714" customWidth="1"/>
+    <col min="2" max="2" width="23.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="34.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="25.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="33.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="9.14285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9466,7 +9434,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -9478,7 +9446,7 @@
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -9492,130 +9460,130 @@
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
     </row>
-    <row r="6" ht="29" spans="2:5">
+    <row r="6" ht="45" spans="2:5">
       <c r="B6" s="21" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C7" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="D7" t="s">
+        <v>401</v>
+      </c>
+      <c r="E7" s="22"/>
+    </row>
+    <row r="8" ht="165" spans="2:5">
+      <c r="B8" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="D7" t="s">
-        <v>403</v>
-      </c>
-      <c r="E7" s="22"/>
-    </row>
-    <row r="8" ht="159.5" spans="2:5">
-      <c r="B8" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>404</v>
-      </c>
       <c r="D8" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E8" s="23"/>
     </row>
     <row r="9" spans="2:3">
       <c r="B9" s="20" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="B10" s="20" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="B11" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C11" s="13" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="12" ht="90" spans="2:4">
+      <c r="B12" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13" ht="45" spans="2:3">
+      <c r="B13" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14" ht="75" spans="2:4">
+      <c r="B14" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="12" ht="87" spans="2:4">
-      <c r="B12" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="C12" s="13" t="s">
+    <row r="15" ht="90" spans="2:4">
+      <c r="B15" t="s">
         <v>408</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="13" ht="29" spans="2:3">
-      <c r="B13" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="14" ht="72.5" spans="2:4">
-      <c r="B14" s="20" t="s">
-        <v>369</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="D14" s="13" t="s">
+      <c r="C15" s="13" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="15" ht="87" spans="2:4">
-      <c r="B15" t="s">
+      <c r="D15" s="13" t="s">
         <v>410</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>411</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="B16" t="s">
+        <v>411</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="2:4">
+      <c r="B17" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="D17" s="13" t="s">
         <v>413</v>
       </c>
-      <c r="C16" s="13" t="s">
+    </row>
+    <row r="18" ht="30" spans="2:4">
+      <c r="B18" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>414</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" spans="2:4">
-      <c r="B17" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="18" ht="29" spans="2:4">
-      <c r="B18" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>416</v>
       </c>
       <c r="D18" s="13"/>
     </row>

--- a/support/specifications/hl7/HL7v2.to.FHIR.Conversion.Spec.xlsx
+++ b/support/specifications/hl7/HL7v2.to.FHIR.Conversion.Spec.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="439">
   <si>
     <t>FHIR Resources</t>
   </si>
@@ -878,6 +878,13 @@
 "value" : "555-120-6047",
 "use" : "home"
 }],</t>
+  </si>
+  <si>
+    <t>BP -&gt; pager
+PH, CP, SAT -&gt; phone
+FX -&gt; fax
+Internet, X.400 -&gt; email
+All Others -&gt; other</t>
   </si>
   <si>
     <t>telecom -&gt; value</t>
@@ -3704,12 +3711,6 @@
   </si>
   <si>
     <t>ORC.23.3</t>
-  </si>
-  <si>
-    <t>PH' -&gt; phone
-'FX' -&gt; fax
-'Internet' -&gt; email
-Otherwise -&gt; other</t>
   </si>
   <si>
     <t>ORC.23.1</t>
@@ -6137,6 +6138,9 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -6156,9 +6160,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6210,9 +6211,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6733,7 +6731,7 @@
     </row>
     <row r="8" s="2" customFormat="1" ht="74.25" spans="2:5">
       <c r="B8" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>421</v>
@@ -6793,7 +6791,7 @@
     </row>
     <row r="13" s="2" customFormat="1" ht="75" spans="2:4">
       <c r="B13" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>365</v>
@@ -6804,10 +6802,10 @@
     </row>
     <row r="14" s="2" customFormat="1" ht="30" spans="2:3">
       <c r="B14" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="45" spans="2:4">
@@ -6840,7 +6838,7 @@
         <v>432</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>433</v>
@@ -6872,10 +6870,10 @@
     </row>
     <row r="20" s="2" customFormat="1" spans="2:4">
       <c r="B20" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D20" s="16" t="s">
         <v>438</v>
@@ -6883,7 +6881,7 @@
     </row>
     <row r="21" s="2" customFormat="1" ht="46" customHeight="1" spans="2:4">
       <c r="B21" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>380</v>
@@ -6980,7 +6978,7 @@
       <c r="B7" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="49" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="67"/>
@@ -7046,11 +7044,11 @@
       <c r="C17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="52" t="s">
+      <c r="E17" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="F17" s="52"/>
-      <c r="G17" s="52"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="30" spans="2:5">
       <c r="B18" s="5" t="s">
@@ -7195,7 +7193,7 @@
       <c r="D7" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="52" t="s">
+      <c r="E7" s="46" t="s">
         <v>54</v>
       </c>
     </row>
@@ -7368,11 +7366,11 @@
       <c r="C23" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="50" t="s">
+      <c r="E23" s="51" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="2:5">
+    <row r="24" ht="75" spans="2:5">
       <c r="B24" s="13" t="s">
         <v>96</v>
       </c>
@@ -7382,404 +7380,406 @@
       <c r="D24" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="E24" s="25"/>
+      <c r="E24" s="46" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E25" s="25"/>
     </row>
     <row r="26" ht="30" spans="2:5">
       <c r="B26" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="E26" s="47"/>
+        <v>103</v>
+      </c>
+      <c r="E26" s="48"/>
     </row>
     <row r="27" ht="45" spans="2:5">
       <c r="B27" s="29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D27" s="60" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" ht="30" spans="2:5">
       <c r="B28" s="29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D28" s="60"/>
       <c r="E28" s="61"/>
     </row>
     <row r="29" ht="30" spans="2:5">
       <c r="B29" s="29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D29" s="60"/>
       <c r="E29" s="61"/>
     </row>
     <row r="30" ht="30" spans="2:5">
       <c r="B30" s="29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D30" s="60"/>
       <c r="E30" s="61"/>
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D31" s="60"/>
       <c r="E31" s="8"/>
     </row>
     <row r="32" ht="30" spans="2:5">
       <c r="B32" s="29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D32" s="60" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" ht="30" spans="2:5">
       <c r="B33" s="29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D33" s="60"/>
       <c r="E33" s="61"/>
     </row>
     <row r="34" ht="30" spans="2:5">
       <c r="B34" s="29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D34" s="60"/>
       <c r="E34" s="61"/>
     </row>
     <row r="35" ht="30" spans="2:5">
       <c r="B35" s="29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D35" s="60"/>
       <c r="E35" s="61"/>
     </row>
     <row r="36" spans="2:5">
       <c r="B36" s="29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D36" s="60"/>
       <c r="E36" s="61"/>
     </row>
     <row r="37" spans="2:5">
       <c r="B37" s="29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D37" s="60" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E37" s="61"/>
     </row>
     <row r="38" ht="45" spans="2:5">
       <c r="B38" s="29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D38" s="60"/>
       <c r="E38" s="69" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" ht="135" spans="2:5">
       <c r="B39" s="62" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C39" s="62"/>
       <c r="D39" s="62" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40" ht="135" spans="2:5">
       <c r="B40" s="62" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C40" s="62"/>
       <c r="D40" s="62" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E40" s="25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41" spans="2:5">
       <c r="B41" s="21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E41" s="25"/>
     </row>
     <row r="42" spans="2:5">
       <c r="B42" s="21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E42" s="25"/>
     </row>
     <row r="43" spans="2:5">
       <c r="B43" s="21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E43" s="25"/>
     </row>
     <row r="44" spans="2:5">
       <c r="B44" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" s="13" t="s">
         <v>136</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>135</v>
       </c>
       <c r="E44" s="25"/>
     </row>
     <row r="45" ht="195" spans="2:5">
       <c r="B45" s="21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E45" s="25"/>
     </row>
     <row r="46" ht="195" spans="2:5">
       <c r="B46" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D46" s="57" t="s">
-        <v>142</v>
-      </c>
-      <c r="E46" s="52" t="s">
         <v>143</v>
+      </c>
+      <c r="E46" s="46" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="47" ht="195" spans="2:5">
       <c r="B47" s="21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E47" s="25"/>
     </row>
     <row r="48" spans="2:5">
       <c r="B48" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E48" s="25"/>
     </row>
     <row r="49" spans="2:5">
       <c r="B49" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E49" s="25"/>
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E50" s="25"/>
     </row>
     <row r="51" spans="2:5">
       <c r="B51" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C51" s="13" t="s">
         <v>152</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>151</v>
       </c>
       <c r="E51" s="25"/>
     </row>
     <row r="52" ht="150" spans="2:5">
       <c r="B52" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E53" s="25"/>
     </row>
     <row r="54" spans="2:5">
       <c r="B54" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E54" s="25"/>
     </row>
     <row r="55" spans="2:5">
       <c r="B55" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E55" s="25"/>
     </row>
     <row r="56" spans="2:5">
       <c r="B56" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E56" s="25"/>
     </row>
     <row r="57" spans="2:5">
       <c r="B57" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C57" s="13" t="s">
         <v>164</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>163</v>
       </c>
       <c r="E57" s="25"/>
     </row>
     <row r="58" spans="2:5">
       <c r="B58" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E58" s="25"/>
     </row>
     <row r="59" ht="180" spans="2:5">
       <c r="B59" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E59" s="25"/>
     </row>
     <row r="60" ht="255" spans="2:5">
       <c r="B60" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E60" s="25" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="2:5">
       <c r="B61" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D61" s="63" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E61" s="25"/>
     </row>
     <row r="62" ht="42.95" customHeight="1" spans="2:5">
       <c r="B62" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C62" s="59" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D62" s="63"/>
       <c r="E62" s="25"/>
@@ -7841,7 +7841,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C2" s="53"/>
       <c r="D2" s="53"/>
@@ -7852,7 +7852,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E3" s="25"/>
     </row>
@@ -7870,7 +7870,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E5" s="25"/>
     </row>
@@ -7879,206 +7879,206 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E6" s="25"/>
     </row>
     <row r="7" ht="45" spans="2:5">
       <c r="B7" s="20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E7" s="54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" ht="135" spans="2:5">
       <c r="B8" s="55" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="55" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D9" s="28"/>
       <c r="E9" s="25"/>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="55" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D10" s="28"/>
       <c r="E10" s="25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" ht="225" spans="2:5">
       <c r="B11" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D11" s="57" t="s">
+        <v>199</v>
+      </c>
+      <c r="E11" s="25" t="s">
         <v>196</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D11" s="57" t="s">
-        <v>198</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" ht="30" spans="2:5">
       <c r="B14" s="20" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" ht="135" spans="2:5">
       <c r="B15" s="20" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E15" s="54" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" ht="45" spans="2:5">
       <c r="B16" s="20" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E16" s="25"/>
     </row>
     <row r="17" ht="60" spans="2:5">
       <c r="B17" s="55" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E17" s="25"/>
     </row>
     <row r="18" ht="60" spans="2:5">
       <c r="B18" s="58" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D20" s="29"/>
       <c r="E20" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" ht="77" customHeight="1" spans="2:5">
       <c r="B21" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E21" s="25"/>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="25"/>
@@ -8136,7 +8136,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E3" s="25"/>
     </row>
@@ -8149,7 +8149,7 @@
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E4" s="25"/>
     </row>
@@ -8169,265 +8169,265 @@
         <v>27</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="25"/>
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" ht="75" spans="2:5">
       <c r="B8" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="C8" s="51" t="s">
         <v>232</v>
       </c>
+      <c r="C8" s="52" t="s">
+        <v>233</v>
+      </c>
       <c r="D8" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E8" s="70" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="C9" s="51" t="s">
         <v>236</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>237</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="25"/>
     </row>
     <row r="10" ht="75" spans="2:5">
       <c r="B10" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="C10" s="51" t="s">
         <v>238</v>
+      </c>
+      <c r="C10" s="52" t="s">
+        <v>239</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="70" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" ht="120" spans="2:5">
       <c r="B11" s="20" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="E11" s="52" t="s">
         <v>243</v>
+      </c>
+      <c r="E11" s="46" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="12" ht="60" spans="2:5">
       <c r="B12" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="E12" s="47" t="s">
         <v>245</v>
+      </c>
+      <c r="E12" s="48" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="20" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E13" s="25"/>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E14" s="25"/>
     </row>
     <row r="15" ht="75" spans="2:5">
       <c r="B15" s="20" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E15" s="25"/>
     </row>
     <row r="16" ht="30" spans="2:5">
       <c r="B16" s="20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E16" s="25"/>
     </row>
     <row r="17" ht="60" spans="2:5">
       <c r="B17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E17" s="25"/>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E18" s="25"/>
     </row>
     <row r="19" ht="30" spans="2:5">
       <c r="B19" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" ht="30" spans="2:5">
       <c r="B23" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24" ht="75" spans="2:5">
       <c r="B24" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E24" s="25"/>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="25"/>
     </row>
     <row r="26" ht="60" spans="2:5">
       <c r="B26" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="25" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:5">
       <c r="B28" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E28" s="25"/>
     </row>
     <row r="29" ht="30" spans="2:5">
       <c r="B29" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="25"/>
@@ -8475,7 +8475,7 @@
         <v>17</v>
       </c>
       <c r="F1" s="33" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8489,7 +8489,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E3" s="34"/>
     </row>
@@ -8518,173 +8518,173 @@
         <v>27</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D6" s="35"/>
       <c r="E6" s="34"/>
     </row>
     <row r="7" ht="30" spans="2:6">
       <c r="B7" s="36" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C7" s="37"/>
       <c r="D7" s="37" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F7" s="38"/>
     </row>
     <row r="8" ht="195" spans="2:5">
       <c r="B8" s="31" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D9" s="35"/>
       <c r="E9" s="34"/>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D10" s="35"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" ht="30" spans="2:5">
       <c r="B11" s="35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="34"/>
     </row>
     <row r="12" ht="30" spans="2:5">
       <c r="B12" s="35" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D12" s="35"/>
       <c r="E12" s="34"/>
     </row>
     <row r="13" ht="225" spans="2:5">
       <c r="B13" s="31" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="31" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D14" s="35"/>
       <c r="E14" s="34"/>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="35" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D15" s="35"/>
       <c r="E15" s="34"/>
     </row>
     <row r="16" ht="30" spans="2:5">
       <c r="B16" s="35" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D16" s="35"/>
       <c r="E16" s="34"/>
     </row>
     <row r="17" ht="30" spans="2:5">
       <c r="B17" s="35" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D17" s="35"/>
       <c r="E17" s="34"/>
     </row>
     <row r="18" ht="30" spans="2:5">
       <c r="B18" s="41" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="19" ht="135" spans="2:5">
       <c r="B19" s="37" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C19" s="43"/>
       <c r="D19" s="44" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="20" ht="60" spans="2:5">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="20" ht="75" spans="2:5">
       <c r="B20" s="35" t="s">
         <v>96</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D20" s="35"/>
-      <c r="E20" s="71" t="s">
-        <v>320</v>
+      <c r="E20" s="46" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="21" ht="180" spans="2:5">
       <c r="B21" s="35" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C21" s="45" t="s">
         <v>321</v>
@@ -8696,20 +8696,20 @@
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="47" t="s">
         <v>323</v>
       </c>
       <c r="D22" s="35"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="49"/>
     </row>
     <row r="23" ht="30" spans="2:5">
       <c r="B23" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="50" t="s">
         <v>324</v>
       </c>
       <c r="D23" s="35" t="s">
@@ -8725,7 +8725,7 @@
         <v>326</v>
       </c>
       <c r="D24" s="35"/>
-      <c r="E24" s="50" t="s">
+      <c r="E24" s="51" t="s">
         <v>327</v>
       </c>
     </row>
@@ -8733,7 +8733,7 @@
       <c r="B25" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="49" t="s">
+      <c r="C25" s="50" t="s">
         <v>328</v>
       </c>
       <c r="D25" s="35"/>
@@ -8781,10 +8781,10 @@
     </row>
     <row r="30" customHeight="1" spans="2:5">
       <c r="B30" s="35" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D30" s="35" t="s">
         <v>333</v>
@@ -8793,9 +8793,9 @@
     </row>
     <row r="31" ht="30" spans="2:5">
       <c r="B31" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="C31" s="49" t="s">
+        <v>178</v>
+      </c>
+      <c r="C31" s="50" t="s">
         <v>334</v>
       </c>
       <c r="D31" s="35"/>
@@ -8901,7 +8901,7 @@
     </row>
     <row r="8" ht="74.25" spans="2:5">
       <c r="B8" s="21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>339</v>
@@ -8928,7 +8928,7 @@
     <row r="10" ht="45" spans="1:5">
       <c r="A10" s="28"/>
       <c r="B10" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>345</v>
@@ -8941,7 +8941,7 @@
     <row r="11" ht="210" spans="1:5">
       <c r="A11" s="28"/>
       <c r="B11" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="29"/>
@@ -8952,7 +8952,7 @@
     <row r="12" ht="210" spans="1:5">
       <c r="A12" s="28"/>
       <c r="B12" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="29"/>
@@ -8997,7 +8997,7 @@
         <v>356</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E16" s="13"/>
     </row>
@@ -9048,7 +9048,7 @@
     </row>
     <row r="21" ht="75" spans="2:5">
       <c r="B21" s="21" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>365</v>
@@ -9060,10 +9060,10 @@
     </row>
     <row r="22" ht="30" spans="2:5">
       <c r="B22" s="21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E22" s="13"/>
     </row>
@@ -9098,7 +9098,7 @@
         <v>374</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>375</v>
@@ -9119,10 +9119,10 @@
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>379</v>
@@ -9131,7 +9131,7 @@
     </row>
     <row r="28" ht="78" customHeight="1" spans="2:5">
       <c r="B28" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C28" s="30" t="s">
         <v>380</v>
@@ -9239,7 +9239,7 @@
     </row>
     <row r="7" ht="74.25" spans="2:5">
       <c r="B7" s="20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C7" t="s">
         <v>384</v>
@@ -9278,7 +9278,7 @@
         <v>356</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="25"/>
@@ -9327,7 +9327,7 @@
     </row>
     <row r="15" ht="45" spans="2:5">
       <c r="B15" s="20" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>365</v>
@@ -9339,10 +9339,10 @@
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E16" s="25"/>
     </row>
@@ -9362,10 +9362,10 @@
     </row>
     <row r="18" customHeight="1" spans="2:5">
       <c r="B18" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>396</v>
@@ -9374,7 +9374,7 @@
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>380</v>
@@ -9472,7 +9472,7 @@
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>400</v>
@@ -9490,7 +9490,7 @@
         <v>402</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E8" s="23"/>
     </row>
@@ -9520,21 +9520,21 @@
     </row>
     <row r="12" ht="90" spans="2:4">
       <c r="B12" s="20" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>406</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" ht="45" spans="2:3">
       <c r="B13" s="20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" ht="75" spans="2:4">
@@ -9569,10 +9569,10 @@
     </row>
     <row r="17" customHeight="1" spans="2:4">
       <c r="B17" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>413</v>
@@ -9580,7 +9580,7 @@
     </row>
     <row r="18" ht="30" spans="2:4">
       <c r="B18" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>414</v>

--- a/support/specifications/hl7/HL7v2.to.FHIR.Conversion.Spec.xlsx
+++ b/support/specifications/hl7/HL7v2.to.FHIR.Conversion.Spec.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="753" firstSheet="1" activeTab="6"/>
+    <workbookView windowWidth="28800" windowHeight="12180" tabRatio="753" firstSheet="1" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="477">
   <si>
     <t>FHIR Resources</t>
   </si>
@@ -1890,6 +1890,107 @@
     <t>The HL7 file shared does not contain the NK1 segment.</t>
   </si>
   <si>
+    <t>maritalStatus -&gt; coding -&gt; system</t>
+  </si>
+  <si>
+    <t>If maritalStatus code is "UNK" then "http://terminology.hl7.org/CodeSystem/v3-NullFlavor", otherwise "http://terminology.hl7.org/CodeSystem/v3-MaritalStatus".</t>
+  </si>
+  <si>
+    <t>maritalStatus -&gt; coding -&gt; code</t>
+  </si>
+  <si>
+    <t>PID.16.1</t>
+  </si>
+  <si>
+    <t>maritalStatus -&gt; coding -&gt; display</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>maritalStatusCode.code -&gt;  maritalStatus.display Mapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+M -&gt; married  
+S -&gt; never married  
+A -&gt; annulled  
+D -&gt; divorced  
+I -&gt; interlocutory  
+L -&gt; legally separated  
+C -&gt; common law  
+P -&gt; polygamous  
+T -&gt; domestic partner  
+U -&gt; unmarried  
+W -&gt; widowed  
+All Others -&gt; unknown</t>
+    </r>
+  </si>
+  <si>
+    <t>deceasedBoolean</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If PID.30.1 is "Y" then </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> else </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
     <t>request -&gt; method</t>
   </si>
   <si>
@@ -4347,6 +4448,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Question Code -&gt; Category Display Mapping</t>
     </r>
     <r>
@@ -4605,6 +4714,15 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Interpretation Code -&gt; Interpretation Display Mapping</t>
     </r>
     <r>
@@ -5823,6 +5941,36 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color indexed="10"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -5836,42 +5984,12 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5888,12 +6006,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E6E6"/>
         <bgColor rgb="FFE7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -6239,7 +6351,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6263,16 +6375,16 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -6281,100 +6393,100 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="45" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="45" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
@@ -6396,7 +6508,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6511,10 +6623,10 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6532,11 +6644,14 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -6574,6 +6689,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -6583,7 +6701,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -6680,7 +6810,7 @@
     <cellStyle name="Warning" xfId="59"/>
   </cellStyles>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{58ECC587-4D15-4AA1-90CF-3197D7A288C3}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{A0F109D3-22A3-4D89-8C49-8EB962CB3793}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -6951,66 +7081,66 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="11.8571428571429" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="14.2857142857143" style="70" customWidth="1"/>
+    <col min="1" max="1" width="14.2857142857143" style="76" customWidth="1"/>
     <col min="2" max="2" width="47" customWidth="1"/>
     <col min="3" max="3" width="123.571428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="65"/>
-      <c r="B2" s="65" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="58" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="65"/>
-      <c r="B3" s="65" t="s">
+      <c r="A3" s="71"/>
+      <c r="B3" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="58" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="65"/>
-      <c r="B4" s="65" t="s">
+      <c r="A4" s="71"/>
+      <c r="B4" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="58" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:3">
-      <c r="A5" s="65"/>
-      <c r="B5" s="65" t="s">
+      <c r="A5" s="71"/>
+      <c r="B5" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="69" t="s">
+      <c r="C5" s="75" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="65"/>
-      <c r="B6" s="69" t="s">
+      <c r="A6" s="71"/>
+      <c r="B6" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="57" t="s">
+      <c r="C6" s="58" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="65"/>
-      <c r="B7" s="65" t="s">
+      <c r="A7" s="71"/>
+      <c r="B7" s="71" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="13" t="s">
@@ -7018,8 +7148,8 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="65"/>
-      <c r="B8" s="65" t="s">
+      <c r="A8" s="71"/>
+      <c r="B8" s="71" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="13" t="s">
@@ -7056,16 +7186,16 @@
         <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="17" customHeight="1" spans="1:6">
@@ -7084,7 +7214,7 @@
         <v>21</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" ht="180" spans="1:6">
@@ -7093,10 +7223,10 @@
         <v>23</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:6">
@@ -7116,7 +7246,7 @@
         <v>29</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -7131,201 +7261,201 @@
         <v>56</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="74.25" spans="1:6">
       <c r="B8" s="6" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="409" customHeight="1" spans="1:6">
       <c r="B9" s="6" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="5" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="150" spans="1:6">
       <c r="B10" s="6" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="180" spans="1:6">
       <c r="B11" s="6" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="2"/>
       <c r="E11" s="12" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="150" spans="1:6">
       <c r="B12" s="6" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="2"/>
       <c r="E12" s="12" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="75" spans="1:6">
       <c r="B13" s="6" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" ht="30" spans="1:6">
       <c r="B14" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="45" spans="1:6">
       <c r="B15" s="6" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="30" spans="1:6">
       <c r="B16" s="6" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="45" spans="2:6">
       <c r="B17" s="6" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="30" spans="2:6">
       <c r="B18" s="6" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="30" spans="2:6">
       <c r="B19" s="6" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="270" spans="2:6">
       <c r="B20" s="6" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="15" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="16" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" ht="165" spans="2:6">
       <c r="B22" s="2" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" spans="2:6">
       <c r="B23" s="5" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" ht="46" customHeight="1" spans="2:6">
       <c r="B24" s="5" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="D24" s="17"/>
     </row>
@@ -7346,24 +7476,24 @@
   <dimension ref="A1:G23"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" style="65" customWidth="1"/>
-    <col min="2" max="2" width="28.2857142857143" style="65" customWidth="1"/>
-    <col min="3" max="3" width="62.7238095238095" style="65" customWidth="1"/>
-    <col min="4" max="4" width="54.5428571428571" style="65" customWidth="1"/>
+    <col min="1" max="1" width="14.7142857142857" style="71" customWidth="1"/>
+    <col min="2" max="2" width="28.2857142857143" style="71" customWidth="1"/>
+    <col min="3" max="3" width="62.7238095238095" style="71" customWidth="1"/>
+    <col min="4" max="4" width="54.5428571428571" style="71" customWidth="1"/>
     <col min="5" max="5" width="57" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="D1" s="72" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -7371,32 +7501,32 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="73" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="67"/>
-      <c r="B3" s="65" t="s">
+      <c r="A3" s="73"/>
+      <c r="B3" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="65" t="s">
+      <c r="C3" s="71" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="67"/>
-      <c r="B4" s="65" t="s">
+      <c r="A4" s="73"/>
+      <c r="B4" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="68" t="s">
+      <c r="C4" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="65" t="s">
+      <c r="D4" s="71" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" s="64" customFormat="1" ht="61" customHeight="1" spans="1:5">
+    <row r="5" s="70" customFormat="1" ht="61" customHeight="1" spans="1:5">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>26</v>
@@ -7408,7 +7538,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" s="64" customFormat="1" ht="49" customHeight="1" spans="1:5">
+    <row r="6" s="70" customFormat="1" ht="49" customHeight="1" spans="1:5">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>29</v>
@@ -7418,7 +7548,7 @@
       </c>
       <c r="D6" s="5"/>
     </row>
-    <row r="7" s="64" customFormat="1" ht="316" customHeight="1" spans="1:5">
+    <row r="7" s="70" customFormat="1" ht="316" customHeight="1" spans="1:5">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>31</v>
@@ -7429,27 +7559,27 @@
       <c r="D7" s="5"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="B8" s="65" t="s">
+      <c r="B8" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="65" t="s">
+      <c r="C8" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="69"/>
+      <c r="D8" s="75"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="B9" s="65" t="s">
+      <c r="B9" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="65" t="s">
+      <c r="C9" s="71" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" ht="30" spans="1:5">
-      <c r="B10" s="65" t="s">
+      <c r="B10" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="69" t="s">
+      <c r="C10" s="75" t="s">
         <v>38</v>
       </c>
     </row>
@@ -7489,11 +7619,11 @@
       <c r="C17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="48" t="s">
+      <c r="E17" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="49"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="30" spans="1:7">
       <c r="B18" s="5" t="s">
@@ -7531,10 +7661,10 @@
       <c r="C22"/>
     </row>
     <row r="23" hidden="1" spans="1:7">
-      <c r="B23" s="65" t="s">
+      <c r="B23" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="69" t="s">
+      <c r="C23" s="75" t="s">
         <v>48</v>
       </c>
     </row>
@@ -7553,8 +7683,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E65"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <dimension ref="A1:F69"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13.1142857142857" customWidth="1"/>
     <col min="2" max="2" width="39.1428571428571" style="14" customWidth="1"/>
@@ -7601,7 +7731,7 @@
       <c r="B4" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="48" t="s">
+      <c r="C4" s="49" t="s">
         <v>50</v>
       </c>
       <c r="D4" s="14" t="s">
@@ -7638,7 +7768,7 @@
       <c r="D7" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="49" t="s">
         <v>57</v>
       </c>
     </row>
@@ -7658,7 +7788,7 @@
       <c r="B9" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="61" t="s">
         <v>62</v>
       </c>
       <c r="E9" s="26"/>
@@ -7825,7 +7955,7 @@
       <c r="D24" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="E24" s="48" t="s">
+      <c r="E24" s="49" t="s">
         <v>102</v>
       </c>
     </row>
@@ -7854,7 +7984,7 @@
       <c r="C27" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="D27" s="60" t="s">
+      <c r="D27" s="62" t="s">
         <v>109</v>
       </c>
       <c r="E27" s="9" t="s">
@@ -7868,8 +7998,8 @@
       <c r="C28" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="D28" s="60"/>
-      <c r="E28" s="61"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="63"/>
     </row>
     <row r="29" ht="30" spans="2:5">
       <c r="B29" s="30" t="s">
@@ -7878,8 +8008,8 @@
       <c r="C29" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="60"/>
-      <c r="E29" s="61"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="63"/>
     </row>
     <row r="30" ht="30" spans="2:5">
       <c r="B30" s="30" t="s">
@@ -7888,8 +8018,8 @@
       <c r="C30" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="D30" s="60"/>
-      <c r="E30" s="61"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="63"/>
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="30" t="s">
@@ -7898,7 +8028,7 @@
       <c r="C31" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D31" s="60"/>
+      <c r="D31" s="62"/>
       <c r="E31" s="9"/>
     </row>
     <row r="32" ht="30" spans="2:5">
@@ -7908,7 +8038,7 @@
       <c r="C32" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="60" t="s">
+      <c r="D32" s="62" t="s">
         <v>119</v>
       </c>
       <c r="E32" s="9" t="s">
@@ -7922,8 +8052,8 @@
       <c r="C33" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="D33" s="60"/>
-      <c r="E33" s="61"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="63"/>
     </row>
     <row r="34" ht="30" spans="2:5">
       <c r="B34" s="30" t="s">
@@ -7932,8 +8062,8 @@
       <c r="C34" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="D34" s="60"/>
-      <c r="E34" s="61"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="63"/>
     </row>
     <row r="35" ht="30" spans="2:5">
       <c r="B35" s="30" t="s">
@@ -7942,8 +8072,8 @@
       <c r="C35" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="D35" s="60"/>
-      <c r="E35" s="61"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="63"/>
     </row>
     <row r="36" spans="2:5">
       <c r="B36" s="30" t="s">
@@ -7952,8 +8082,8 @@
       <c r="C36" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="60"/>
-      <c r="E36" s="61"/>
+      <c r="D36" s="62"/>
+      <c r="E36" s="63"/>
     </row>
     <row r="37" spans="2:5">
       <c r="B37" s="30" t="s">
@@ -7962,10 +8092,10 @@
       <c r="C37" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="D37" s="60" t="s">
+      <c r="D37" s="62" t="s">
         <v>125</v>
       </c>
-      <c r="E37" s="61"/>
+      <c r="E37" s="63"/>
     </row>
     <row r="38" ht="45" spans="2:5">
       <c r="B38" s="30" t="s">
@@ -7974,32 +8104,32 @@
       <c r="C38" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="D38" s="60"/>
-      <c r="E38" s="71" t="s">
+      <c r="D38" s="62"/>
+      <c r="E38" s="77" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="39" ht="135" spans="2:5">
-      <c r="B39" s="62" t="s">
+      <c r="B39" s="64" t="s">
         <v>129</v>
       </c>
-      <c r="C39" s="62"/>
-      <c r="D39" s="62" t="s">
+      <c r="C39" s="64"/>
+      <c r="D39" s="64" t="s">
         <v>130</v>
       </c>
-      <c r="E39" s="26" t="s">
+      <c r="E39" s="65" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="40" ht="135" spans="2:5">
-      <c r="B40" s="62" t="s">
+      <c r="B40" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="C40" s="62"/>
-      <c r="D40" s="62" t="s">
+      <c r="C40" s="64"/>
+      <c r="D40" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="E40" s="26" t="s">
+      <c r="E40" s="65" t="s">
         <v>131</v>
       </c>
     </row>
@@ -8058,10 +8188,10 @@
       <c r="C46" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="D46" s="57" t="s">
+      <c r="D46" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="E46" s="48" t="s">
+      <c r="E46" s="49" t="s">
         <v>147</v>
       </c>
     </row>
@@ -8086,7 +8216,7 @@
       </c>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" spans="2:5">
+    <row r="49" spans="2:6">
       <c r="B49" s="14" t="s">
         <v>152</v>
       </c>
@@ -8095,7 +8225,7 @@
       </c>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" spans="2:5">
+    <row r="50" spans="2:6">
       <c r="B50" s="14" t="s">
         <v>154</v>
       </c>
@@ -8104,7 +8234,7 @@
       </c>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" spans="2:5">
+    <row r="51" spans="2:6">
       <c r="B51" s="14" t="s">
         <v>156</v>
       </c>
@@ -8113,7 +8243,7 @@
       </c>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" ht="150" spans="2:5">
+    <row r="52" ht="150" spans="2:6">
       <c r="B52" s="14" t="s">
         <v>157</v>
       </c>
@@ -8127,7 +8257,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="53" spans="2:5">
+    <row r="53" spans="2:6">
       <c r="B53" s="14" t="s">
         <v>161</v>
       </c>
@@ -8136,7 +8266,7 @@
       </c>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" spans="2:5">
+    <row r="54" spans="2:6">
       <c r="B54" s="14" t="s">
         <v>163</v>
       </c>
@@ -8145,7 +8275,7 @@
       </c>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" spans="2:5">
+    <row r="55" spans="2:6">
       <c r="B55" s="14" t="s">
         <v>164</v>
       </c>
@@ -8154,7 +8284,7 @@
       </c>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" spans="2:5">
+    <row r="56" spans="2:6">
       <c r="B56" s="14" t="s">
         <v>166</v>
       </c>
@@ -8163,7 +8293,7 @@
       </c>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" spans="2:5">
+    <row r="57" spans="2:6">
       <c r="B57" s="14" t="s">
         <v>168</v>
       </c>
@@ -8172,7 +8302,7 @@
       </c>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" spans="2:5">
+    <row r="58" spans="2:6">
       <c r="B58" s="14" t="s">
         <v>169</v>
       </c>
@@ -8181,7 +8311,7 @@
       </c>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" ht="180" spans="2:5">
+    <row r="59" ht="180" spans="2:6">
       <c r="B59" s="14" t="s">
         <v>171</v>
       </c>
@@ -8193,7 +8323,7 @@
       </c>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" ht="255" spans="2:5">
+    <row r="60" ht="255" spans="2:6">
       <c r="B60" s="14" t="s">
         <v>174</v>
       </c>
@@ -8207,30 +8337,74 @@
         <v>177</v>
       </c>
     </row>
-    <row r="61" spans="2:5">
-      <c r="B61" s="14" t="s">
+    <row r="61" s="60" customFormat="1" ht="45" spans="2:6">
+      <c r="B61" s="66" t="s">
         <v>178</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="66" t="s">
         <v>179</v>
       </c>
-      <c r="D61" s="63" t="s">
+      <c r="D61" s="67"/>
+      <c r="E61" s="66"/>
+      <c r="F61" s="66"/>
+    </row>
+    <row r="62" s="60" customFormat="1" spans="2:6">
+      <c r="B62" s="66" t="s">
         <v>180</v>
       </c>
-      <c r="E61" s="26"/>
-    </row>
-    <row r="62" ht="42.95" customHeight="1" spans="2:5">
-      <c r="B62" s="14" t="s">
+      <c r="C62" s="66" t="s">
         <v>181</v>
       </c>
-      <c r="C62" s="59" t="s">
+      <c r="D62" s="67"/>
+      <c r="E62" s="66"/>
+      <c r="F62" s="66"/>
+    </row>
+    <row r="63" s="60" customFormat="1" ht="195" spans="2:6">
+      <c r="B63" s="66" t="s">
         <v>182</v>
       </c>
-      <c r="D62" s="63"/>
-      <c r="E62" s="26"/>
-    </row>
-    <row r="65" spans="3:3">
-      <c r="C65" s="59"/>
+      <c r="C63" s="66"/>
+      <c r="D63" s="67"/>
+      <c r="E63" s="68" t="s">
+        <v>183</v>
+      </c>
+      <c r="F63" s="66"/>
+    </row>
+    <row r="64" s="60" customFormat="1" spans="2:6">
+      <c r="B64" s="66" t="s">
+        <v>184</v>
+      </c>
+      <c r="C64" s="67" t="s">
+        <v>185</v>
+      </c>
+      <c r="D64" s="67"/>
+      <c r="E64" s="68"/>
+      <c r="F64" s="66"/>
+    </row>
+    <row r="65" spans="2:5">
+      <c r="B65" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="D65" s="69" t="s">
+        <v>188</v>
+      </c>
+      <c r="E65" s="26"/>
+    </row>
+    <row r="66" ht="42.95" customHeight="1" spans="2:5">
+      <c r="B66" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="C66" s="61" t="s">
+        <v>190</v>
+      </c>
+      <c r="D66" s="69"/>
+      <c r="E66" s="26"/>
+    </row>
+    <row r="69" spans="2:5">
+      <c r="C69" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -8238,11 +8412,11 @@
     <mergeCell ref="D27:D31"/>
     <mergeCell ref="D32:D36"/>
     <mergeCell ref="D37:D38"/>
-    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="D65:D66"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C9" r:id="rId1" display="&quot;http://shinny.org/us/ny/hrsn/StructureDefinition/middle-name&quot;" tooltip="http://shinny.org/us/ny/hrsn/StructureDefinition/middle-name"/>
-    <hyperlink ref="C62" r:id="rId2" display="&quot;http://shinny.org/us/ny/hrsn/Patient/&lt;id&gt;&quot;" tooltip="http://shinny.org/us/ny/hrsn/Patient/PID.3.1"/>
+    <hyperlink ref="C66" r:id="rId2" display="&quot;http://shinny.org/us/ny/hrsn/Patient/&lt;id&gt;&quot;" tooltip="http://shinny.org/us/ny/hrsn/Patient/PID.3.1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1.39370078740157" bottom="1.39370078740157" header="1" footer="1"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
@@ -8285,19 +8459,19 @@
       <c r="A2" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="53" t="s">
-        <v>183</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
+      <c r="B2" s="54" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
     </row>
     <row r="3" spans="1:5">
       <c r="B3" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="E3" s="26"/>
     </row>
@@ -8305,11 +8479,11 @@
       <c r="B4" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="54" t="s">
-        <v>185</v>
+      <c r="C4" s="55" t="s">
+        <v>193</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="E4" s="26"/>
     </row>
@@ -8318,7 +8492,7 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="E5" s="26"/>
     </row>
@@ -8327,206 +8501,206 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="E6" s="26"/>
     </row>
     <row r="7" ht="45" spans="1:5">
       <c r="B7" s="21" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E7" s="54" t="s">
-        <v>192</v>
+        <v>199</v>
+      </c>
+      <c r="E7" s="55" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="8" ht="135" spans="1:5">
-      <c r="B8" s="55" t="s">
-        <v>193</v>
+      <c r="B8" s="56" t="s">
+        <v>201</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="D8" s="56" t="s">
-        <v>195</v>
+        <v>202</v>
+      </c>
+      <c r="D8" s="57" t="s">
+        <v>203</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="B9" s="55" t="s">
-        <v>197</v>
+      <c r="B9" s="56" t="s">
+        <v>205</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D9" s="29"/>
       <c r="E9" s="26"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="B10" s="55" t="s">
-        <v>199</v>
+      <c r="B10" s="56" t="s">
+        <v>207</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D10" s="29"/>
       <c r="E10" s="26" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" ht="225" spans="1:5">
       <c r="B11" s="21" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D11" s="57" t="s">
-        <v>204</v>
+        <v>211</v>
+      </c>
+      <c r="D11" s="58" t="s">
+        <v>212</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="B12" s="21" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="B13" s="21" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:5">
       <c r="B14" s="21" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C14" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D14" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" ht="135" spans="1:5">
       <c r="B15" s="21" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="E15" s="54" t="s">
-        <v>216</v>
+        <v>223</v>
+      </c>
+      <c r="E15" s="55" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="16" ht="45" spans="1:5">
       <c r="B16" s="21" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="E16" s="26"/>
     </row>
     <row r="17" ht="60" spans="2:5">
-      <c r="B17" s="55" t="s">
-        <v>220</v>
-      </c>
-      <c r="C17" s="58" t="s">
-        <v>221</v>
+      <c r="B17" s="56" t="s">
+        <v>228</v>
+      </c>
+      <c r="C17" s="59" t="s">
+        <v>229</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="E17" s="26"/>
     </row>
     <row r="18" ht="60" spans="2:5">
-      <c r="B18" s="58" t="s">
-        <v>223</v>
-      </c>
-      <c r="C18" s="58" t="s">
-        <v>224</v>
+      <c r="B18" s="59" t="s">
+        <v>231</v>
+      </c>
+      <c r="C18" s="59" t="s">
+        <v>232</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="6" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D20" s="30"/>
       <c r="E20" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" ht="77" customHeight="1" spans="2:5">
       <c r="B21" s="14" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="E21" s="26"/>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="14" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="26"/>
@@ -8584,7 +8758,7 @@
         <v>21</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="E3" s="26"/>
     </row>
@@ -8593,11 +8767,11 @@
       <c r="B4" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="48" t="s">
-        <v>234</v>
+      <c r="C4" s="49" t="s">
+        <v>242</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="E4" s="26"/>
     </row>
@@ -8617,265 +8791,265 @@
         <v>29</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="26"/>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="21" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" ht="75" spans="1:5">
       <c r="B8" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="C8" s="52" t="s">
-        <v>239</v>
+        <v>246</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>247</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="E8" s="72" t="s">
-        <v>241</v>
+        <v>248</v>
+      </c>
+      <c r="E8" s="78" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="C9" s="52" t="s">
-        <v>243</v>
+        <v>250</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>251</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="26"/>
     </row>
     <row r="10" ht="75" spans="1:5">
       <c r="B10" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="C10" s="52" t="s">
-        <v>245</v>
+        <v>252</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>253</v>
       </c>
       <c r="D10" s="14"/>
-      <c r="E10" s="72" t="s">
-        <v>246</v>
+      <c r="E10" s="78" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="11" ht="120" spans="1:5">
       <c r="B11" s="21" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="E11" s="48" t="s">
-        <v>250</v>
+        <v>257</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="12" ht="60" spans="1:5">
       <c r="B12" s="21" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="B13" s="21" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5">
       <c r="B14" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="C14" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E14" s="26"/>
     </row>
     <row r="15" ht="75" spans="1:5">
       <c r="B15" s="21" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C15" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="E15" s="26"/>
     </row>
     <row r="16" ht="30" spans="1:5">
       <c r="B16" s="21" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E16" s="26"/>
     </row>
     <row r="17" ht="60" spans="2:5">
       <c r="B17" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="E17" s="26"/>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="E18" s="26"/>
     </row>
     <row r="19" ht="30" spans="2:5">
       <c r="B19" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="26" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D21" s="14"/>
       <c r="E21" s="26" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
       <c r="E22" s="26" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" ht="30" spans="2:5">
       <c r="B23" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="26" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" ht="75" spans="2:5">
       <c r="B24" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E24" s="26"/>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="26"/>
     </row>
     <row r="26" ht="60" spans="2:5">
       <c r="B26" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="26" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:5">
       <c r="B28" s="14" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="E28" s="26"/>
     </row>
     <row r="29" ht="30" spans="2:5">
       <c r="B29" s="14" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="26"/>
@@ -8923,7 +9097,7 @@
         <v>19</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8937,7 +9111,7 @@
         <v>21</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="E3" s="36"/>
     </row>
@@ -8946,10 +9120,10 @@
         <v>23</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="E4" s="36"/>
     </row>
@@ -8969,61 +9143,61 @@
         <v>29</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="D6" s="37"/>
       <c r="E6" s="36"/>
     </row>
     <row r="7" ht="30" spans="1:6">
       <c r="B7" s="38" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C7" s="39"/>
       <c r="D7" s="39" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F7" s="40"/>
     </row>
     <row r="8" ht="195" spans="1:6">
       <c r="B8" s="33" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" s="33" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D9" s="37"/>
       <c r="E9" s="36"/>
     </row>
     <row r="10" spans="1:6">
       <c r="B10" s="37" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="D10" s="37"/>
       <c r="E10" s="36"/>
     </row>
     <row r="11" ht="30" spans="1:6">
       <c r="B11" s="37" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>135</v>
@@ -9033,51 +9207,51 @@
     </row>
     <row r="12" ht="30" spans="1:6">
       <c r="B12" s="37" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="D12" s="37"/>
       <c r="E12" s="36"/>
     </row>
     <row r="13" ht="225" spans="1:6">
       <c r="B13" s="33" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="E13" s="42" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="B14" s="33" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="36"/>
     </row>
     <row r="15" spans="1:6">
       <c r="B15" s="37" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="36"/>
     </row>
     <row r="16" ht="30" spans="1:6">
       <c r="B16" s="37" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>135</v>
@@ -9087,49 +9261,49 @@
     </row>
     <row r="17" ht="30" spans="2:6">
       <c r="B17" s="37" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="36"/>
     </row>
     <row r="18" ht="30" spans="2:6">
       <c r="B18" s="43" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="C18" s="44" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="E18" s="42" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19" ht="135" spans="2:6">
       <c r="B19" s="39" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C19" s="45"/>
       <c r="D19" s="46" t="s">
-        <v>326</v>
-      </c>
-      <c r="E19" s="36" t="s">
-        <v>327</v>
+        <v>334</v>
+      </c>
+      <c r="E19" s="47" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="20" ht="75" spans="2:6">
       <c r="B20" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="C20" s="47" t="s">
-        <v>328</v>
+      <c r="C20" s="48" t="s">
+        <v>336</v>
       </c>
       <c r="D20" s="37"/>
-      <c r="E20" s="48" t="s">
+      <c r="E20" s="49" t="s">
         <v>102</v>
       </c>
     </row>
@@ -9137,11 +9311,11 @@
       <c r="B21" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="C21" s="47" t="s">
-        <v>329</v>
+      <c r="C21" s="48" t="s">
+        <v>337</v>
       </c>
       <c r="D21" s="37" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="E21" s="36"/>
     </row>
@@ -9149,22 +9323,22 @@
       <c r="B22" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="C22" s="49" t="s">
-        <v>331</v>
+      <c r="C22" s="50" t="s">
+        <v>339</v>
       </c>
       <c r="D22" s="37"/>
       <c r="E22" s="15"/>
-      <c r="F22" s="50"/>
+      <c r="F22" s="51"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="51" t="s">
-        <v>332</v>
+      <c r="C23" s="52" t="s">
+        <v>340</v>
       </c>
       <c r="D23" s="37" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="E23" s="36"/>
     </row>
@@ -9172,20 +9346,20 @@
       <c r="B24" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="47" t="s">
-        <v>334</v>
+      <c r="C24" s="48" t="s">
+        <v>342</v>
       </c>
       <c r="D24" s="37"/>
       <c r="E24" s="31" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="25" ht="30" spans="2:6">
       <c r="B25" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="51" t="s">
-        <v>336</v>
+      <c r="C25" s="52" t="s">
+        <v>344</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="36"/>
@@ -9194,8 +9368,8 @@
       <c r="B26" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="C26" s="47" t="s">
-        <v>337</v>
+      <c r="C26" s="48" t="s">
+        <v>345</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="36"/>
@@ -9204,8 +9378,8 @@
       <c r="B27" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="47" t="s">
-        <v>338</v>
+      <c r="C27" s="48" t="s">
+        <v>346</v>
       </c>
       <c r="D27" s="37"/>
       <c r="E27" s="36"/>
@@ -9214,8 +9388,8 @@
       <c r="B28" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="47" t="s">
-        <v>339</v>
+      <c r="C28" s="48" t="s">
+        <v>347</v>
       </c>
       <c r="D28" s="37"/>
       <c r="E28" s="36"/>
@@ -9224,30 +9398,30 @@
       <c r="B29" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="47" t="s">
-        <v>340</v>
+      <c r="C29" s="48" t="s">
+        <v>348</v>
       </c>
       <c r="D29" s="37"/>
       <c r="E29" s="36"/>
     </row>
     <row r="30" customHeight="1" spans="2:6">
       <c r="B30" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="C30" s="47" t="s">
-        <v>179</v>
+        <v>186</v>
+      </c>
+      <c r="C30" s="48" t="s">
+        <v>187</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="E30" s="36"/>
     </row>
     <row r="31" ht="30" spans="2:6">
       <c r="B31" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="C31" s="51" t="s">
-        <v>342</v>
+        <v>189</v>
+      </c>
+      <c r="C31" s="52" t="s">
+        <v>350</v>
       </c>
       <c r="D31" s="37"/>
       <c r="E31" s="36"/>
@@ -9304,7 +9478,7 @@
         <v>21</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E3" s="14"/>
     </row>
@@ -9313,10 +9487,10 @@
         <v>23</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E4" s="14"/>
     </row>
@@ -9334,7 +9508,7 @@
         <v>29</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="E6" s="14"/>
     </row>
@@ -9347,310 +9521,310 @@
         <v>56</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" ht="74.25" spans="1:5">
       <c r="B8" s="22" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" ht="120" spans="1:5">
       <c r="B9" s="28" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C9" s="29"/>
       <c r="D9" s="30" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10" ht="45" spans="1:5">
       <c r="A10" s="29"/>
       <c r="B10" s="6" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D10" s="30"/>
       <c r="E10" s="9" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11" ht="210" spans="1:5">
       <c r="A11" s="29"/>
       <c r="B11" s="6" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="30"/>
       <c r="E11" s="12" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="12" ht="210" spans="1:5">
       <c r="A12" s="29"/>
       <c r="B12" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="30"/>
       <c r="E12" s="12" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="29"/>
       <c r="B13" s="6" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="30"/>
       <c r="E13" s="9" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" ht="150" spans="1:5">
       <c r="B14" s="14" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:5">
       <c r="B15" s="22" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="E15" s="14"/>
     </row>
     <row r="16" spans="1:5">
       <c r="B16" s="22" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="E16" s="14"/>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="14" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="E17" s="14"/>
     </row>
     <row r="18" ht="105" spans="2:5">
       <c r="B18" s="14" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="19" ht="30" spans="2:5">
       <c r="B19" s="14" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="20" ht="30" spans="2:5">
       <c r="B20" s="14" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" ht="37" customHeight="1" spans="2:5">
       <c r="B21" s="8" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="E21" s="9"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="45" spans="2:5">
       <c r="B22" s="8" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="D22" s="17"/>
       <c r="E22" s="31" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" ht="45" spans="2:5">
       <c r="B23" s="8" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="17"/>
       <c r="E23" s="12" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="24" ht="75" spans="2:5">
       <c r="B24" s="22" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="E24" s="14"/>
     </row>
     <row r="25" ht="30" spans="2:5">
       <c r="B25" s="22" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E25" s="14"/>
     </row>
     <row r="26" ht="45" spans="2:5">
       <c r="B26" s="28" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="E26" s="14"/>
     </row>
     <row r="27" ht="30" spans="2:5">
       <c r="B27" s="22" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="28" ht="60" spans="2:5">
       <c r="B28" s="14" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="E28" s="14"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="30" spans="2:5">
       <c r="B29" s="6" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" spans="2:5">
       <c r="B30" s="6" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="270" spans="2:5">
       <c r="B31" s="6" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="15" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="32" ht="30" spans="2:5">
       <c r="B32" s="14" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="E32" s="14"/>
     </row>
     <row r="33" spans="2:5">
       <c r="B33" s="14" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="E33" s="14"/>
     </row>
     <row r="34" ht="78" customHeight="1" spans="2:5">
       <c r="B34" s="14" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C34" s="32" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
@@ -9707,7 +9881,7 @@
     </row>
     <row r="2" ht="30" spans="1:5">
       <c r="A2" s="25" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="E2" s="26"/>
     </row>
@@ -9717,7 +9891,7 @@
         <v>21</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E3" s="26"/>
     </row>
@@ -9727,10 +9901,10 @@
         <v>23</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="E4" s="26"/>
     </row>
@@ -9750,152 +9924,152 @@
         <v>29</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="26"/>
     </row>
     <row r="7" ht="74.25" spans="1:5">
       <c r="B7" s="21" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C7" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="D7" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="21" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C8" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="26"/>
     </row>
     <row r="9" ht="42.95" customHeight="1" spans="1:5">
       <c r="B9" s="21" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C9" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="E9" s="26"/>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="21" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D10" s="14"/>
       <c r="E10" s="26"/>
     </row>
     <row r="11" ht="60.95" customHeight="1" spans="1:5">
       <c r="B11" s="21" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="26"/>
     </row>
     <row r="12" ht="30" spans="1:5">
       <c r="B12" s="14" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="E12" s="26"/>
     </row>
     <row r="13" ht="30" spans="1:5">
       <c r="B13" s="14" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="26"/>
     </row>
     <row r="14" ht="78" customHeight="1" spans="1:5">
       <c r="B14" s="14" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="26"/>
     </row>
     <row r="15" ht="45" spans="1:5">
       <c r="B15" s="21" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="E15" s="26"/>
     </row>
     <row r="16" spans="1:5">
       <c r="B16" s="21" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E16" s="26"/>
     </row>
     <row r="17" ht="30" spans="2:5">
       <c r="B17" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C17" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="D17" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:5">
       <c r="B18" s="14" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="E18" s="26"/>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="14" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="26"/>
@@ -9952,7 +10126,7 @@
         <v>21</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -9961,10 +10135,10 @@
         <v>23</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D4" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -9983,125 +10157,125 @@
         <v>29</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="21" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="D7" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E7" s="23"/>
     </row>
     <row r="8" ht="165" spans="1:5">
       <c r="B8" s="21" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="E8" s="24"/>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="21" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="21" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
     </row>
     <row r="12" ht="90" spans="1:5">
       <c r="B12" s="21" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" ht="45" spans="1:5">
       <c r="B13" s="21" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" ht="75" spans="1:5">
       <c r="B14" s="21" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15" ht="90" spans="1:5">
       <c r="B15" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="B16" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:4">
       <c r="B17" s="14" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
     </row>
     <row r="18" ht="30" spans="2:4">
       <c r="B18" s="14" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="D18" s="14"/>
     </row>
